--- a/docs/Kubernetesクラスタ_パラメータシート.xlsx
+++ b/docs/Kubernetesクラスタ_パラメータシート.xlsx
@@ -9075,8 +9075,8 @@
     <mergeCell ref="B9:W9"/>
     <mergeCell ref="X11:AK11"/>
     <mergeCell ref="AL11:AV11"/>
+    <mergeCell ref="X23:AK23"/>
     <mergeCell ref="B6:W6"/>
-    <mergeCell ref="X23:AK23"/>
     <mergeCell ref="X8:AK8"/>
     <mergeCell ref="B20:W20"/>
     <mergeCell ref="B24:W24"/>
@@ -9129,7 +9129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AV64"/>
+  <dimension ref="B1:AV64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.6" defaultRowHeight="15"/>
   <cols>
     <col width="16.9" customWidth="1" style="412" min="30" max="30"/>
@@ -9137,6 +9137,7 @@
     <col width="16.9" customWidth="1" style="412" min="48" max="48"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="460" t="inlineStr">
         <is>
@@ -9144,6 +9145,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="467" t="inlineStr">
         <is>
@@ -9209,6 +9212,7 @@
       <c r="AU5" s="463" t="n"/>
       <c r="AV5" s="464" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="461" t="inlineStr">
         <is>
@@ -9476,6 +9480,7 @@
       <c r="AU11" s="463" t="n"/>
       <c r="AV11" s="464" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="461" t="inlineStr">
         <is>
@@ -9869,6 +9874,7 @@
       <c r="AU19" s="463" t="n"/>
       <c r="AV19" s="464" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="B21" s="461" t="inlineStr">
         <is>
@@ -10201,6 +10207,7 @@
       <c r="AU26" s="463" t="n"/>
       <c r="AV26" s="464" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="461" t="inlineStr">
         <is>
@@ -10403,6 +10410,7 @@
       <c r="AU31" s="463" t="n"/>
       <c r="AV31" s="464" t="n"/>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="B33" s="461" t="inlineStr">
         <is>
@@ -10605,6 +10613,7 @@
       <c r="AU36" s="463" t="n"/>
       <c r="AV36" s="464" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="B38" s="461" t="inlineStr">
         <is>
@@ -10742,6 +10751,7 @@
       <c r="AU40" s="463" t="n"/>
       <c r="AV40" s="464" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="B42" s="461" t="inlineStr">
         <is>
@@ -10944,6 +10954,7 @@
       <c r="AU45" s="463" t="n"/>
       <c r="AV45" s="464" t="n"/>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="B47" s="461" t="inlineStr">
         <is>
@@ -11279,6 +11290,7 @@
       <c r="AU52" s="463" t="n"/>
       <c r="AV52" s="464" t="n"/>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="B54" s="461" t="inlineStr">
         <is>
@@ -11380,7 +11392,7 @@
       <c r="W56" s="464" t="n"/>
       <c r="X56" s="465" t="inlineStr">
         <is>
-          <t>v1.32.x（pkgs.k8s.ioリポジトリ）</t>
+          <t>v1.35.x（pkgs.k8s.ioリポジトリ）</t>
         </is>
       </c>
       <c r="Y56" s="463" t="n"/>
@@ -11402,7 +11414,7 @@
       <c r="AK56" s="464" t="n"/>
       <c r="AL56" s="465" t="inlineStr">
         <is>
-          <t>apt-mark holdでバージョン固定。マイナーバージョンは構築時に確定</t>
+          <t>apt-mark holdでバージョン固定。2026/7時点の推奨系統（v1.32はEOL）</t>
         </is>
       </c>
       <c r="AM56" s="463" t="n"/>
@@ -11510,7 +11522,7 @@
       <c r="W58" s="464" t="n"/>
       <c r="X58" s="465" t="inlineStr">
         <is>
-          <t>v3.x</t>
+          <t>v4.2.x</t>
         </is>
       </c>
       <c r="Y58" s="463" t="n"/>
@@ -11532,7 +11544,7 @@
       <c r="AK58" s="464" t="n"/>
       <c r="AL58" s="465" t="inlineStr">
         <is>
-          <t>監視スタック等のデプロイに使用</t>
+          <t>2026/7時点の最新安定版（Helm v4系）。既存Chart/CI連携がv3前提の場合は互換性を事前確認</t>
         </is>
       </c>
       <c r="AM58" s="463" t="n"/>
@@ -11707,8 +11719,8 @@
     <mergeCell ref="AE9:AK9"/>
     <mergeCell ref="B9:W9"/>
     <mergeCell ref="AL36:AV36"/>
+    <mergeCell ref="AE49:AK49"/>
     <mergeCell ref="AL11:AV11"/>
-    <mergeCell ref="AE49:AK49"/>
     <mergeCell ref="AE36:AK36"/>
     <mergeCell ref="B36:W36"/>
     <mergeCell ref="AE45:AK45"/>
@@ -11975,7 +11987,7 @@
       <c r="W7" s="464" t="n"/>
       <c r="X7" s="465" t="inlineStr">
         <is>
-          <t>v1.32.x（コミュニティ版/kubeadm構築）</t>
+          <t>v1.35.x（コミュニティ版/kubeadm構築）</t>
         </is>
       </c>
       <c r="Y7" s="463" t="n"/>
@@ -11993,7 +12005,7 @@
       <c r="AK7" s="464" t="n"/>
       <c r="AL7" s="465" t="inlineStr">
         <is>
-          <t>マイナーバージョンは構築時に確定</t>
+          <t>マイナーバージョンは構築時に最新パッチへ再確認（2026/7時点の推奨: v1.35系。v1.34は2026/10、v1.32は既にEOLのため非推奨）</t>
         </is>
       </c>
       <c r="AM7" s="463" t="n"/>
@@ -12036,7 +12048,7 @@
       <c r="W8" s="464" t="n"/>
       <c r="X8" s="465" t="inlineStr">
         <is>
-          <t>containerd 2.x</t>
+          <t>containerd 2.3.x LTS</t>
         </is>
       </c>
       <c r="Y8" s="463" t="n"/>
@@ -12054,7 +12066,7 @@
       <c r="AK8" s="464" t="n"/>
       <c r="AL8" s="465" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>2026/7時点の最新LTS系統</t>
         </is>
       </c>
       <c r="AM8" s="463" t="n"/>
@@ -12097,7 +12109,7 @@
       <c r="W9" s="464" t="n"/>
       <c r="X9" s="465" t="inlineStr">
         <is>
-          <t>Calico v3.xx</t>
+          <t>Calico v3.32.x</t>
         </is>
       </c>
       <c r="Y9" s="463" t="n"/>
@@ -12115,7 +12127,7 @@
       <c r="AK9" s="464" t="n"/>
       <c r="AL9" s="465" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>2026/7時点の最新安定版</t>
         </is>
       </c>
       <c r="AM9" s="463" t="n"/>
@@ -12158,7 +12170,7 @@
       <c r="W10" s="464" t="n"/>
       <c r="X10" s="465" t="inlineStr">
         <is>
-          <t>NetApp Trident vXX.XX</t>
+          <t>NetApp Trident v26.06</t>
         </is>
       </c>
       <c r="Y10" s="463" t="n"/>
@@ -12176,7 +12188,7 @@
       <c r="AK10" s="464" t="n"/>
       <c r="AL10" s="465" t="inlineStr">
         <is>
-          <t>バージョンは構築時に確定</t>
+          <t>2026/7時点の最新版。Kubernetes 1.35/1.36対応</t>
         </is>
       </c>
       <c r="AM10" s="463" t="n"/>
@@ -12619,7 +12631,7 @@
       <c r="W21" s="464" t="n"/>
       <c r="X21" s="465" t="inlineStr">
         <is>
-          <t>v1.32.x</t>
+          <t>v1.35.x</t>
         </is>
       </c>
       <c r="Y21" s="463" t="n"/>
@@ -16218,8 +16230,8 @@
     <mergeCell ref="AE78:AK78"/>
     <mergeCell ref="AL48:AV48"/>
     <mergeCell ref="AL54:AV54"/>
+    <mergeCell ref="AE87:AK87"/>
     <mergeCell ref="B78:W78"/>
-    <mergeCell ref="AE87:AK87"/>
     <mergeCell ref="AL10:AV10"/>
     <mergeCell ref="B87:W87"/>
     <mergeCell ref="AE48:AK48"/>
@@ -16739,8 +16751,8 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="AL5:AV5"/>
+    <mergeCell ref="X9:AK9"/>
     <mergeCell ref="X8:AK8"/>
-    <mergeCell ref="X9:AK9"/>
     <mergeCell ref="B2:AV2"/>
     <mergeCell ref="AL8:AV8"/>
     <mergeCell ref="B5:W5"/>

--- a/docs/Kubernetesクラスタ_パラメータシート.xlsx
+++ b/docs/Kubernetesクラスタ_パラメータシート.xlsx
@@ -198,7 +198,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -244,6 +244,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00CCECFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F9F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1284,7 +1289,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="468">
+  <cellXfs count="471">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2682,6 +2687,11 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6013,29 +6023,45 @@
     </row>
     <row r="13" ht="18" customHeight="1" s="412">
       <c r="B13" s="14" t="n"/>
-      <c r="D13" s="447" t="n"/>
+      <c r="D13" s="447" t="n">
+        <v>2</v>
+      </c>
       <c r="E13" s="437" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="438" t="n"/>
-      <c r="H13" s="440" t="n"/>
+      <c r="H13" s="440" t="n">
+        <v>46234</v>
+      </c>
       <c r="I13" s="437" t="n"/>
       <c r="J13" s="437" t="n"/>
       <c r="K13" s="437" t="n"/>
       <c r="L13" s="437" t="n"/>
       <c r="M13" s="438" t="n"/>
-      <c r="N13" s="173" t="n"/>
+      <c r="N13" s="173" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
       <c r="O13" s="437" t="n"/>
       <c r="P13" s="437" t="n"/>
       <c r="Q13" s="437" t="n"/>
       <c r="R13" s="437" t="n"/>
       <c r="S13" s="438" t="n"/>
-      <c r="T13" s="173" t="n"/>
+      <c r="T13" s="173" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
       <c r="U13" s="437" t="n"/>
       <c r="V13" s="437" t="n"/>
       <c r="W13" s="437" t="n"/>
       <c r="X13" s="437" t="n"/>
       <c r="Y13" s="438" t="n"/>
-      <c r="Z13" s="448" t="n"/>
+      <c r="Z13" s="448" t="inlineStr">
+        <is>
+          <t>「目的・解説（なぜこの設定が必要か）」列を追加</t>
+        </is>
+      </c>
       <c r="AA13" s="437" t="n"/>
       <c r="AB13" s="437" t="n"/>
       <c r="AC13" s="437" t="n"/>
@@ -7106,7 +7132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AV22"/>
+  <dimension ref="B2:AV23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.6" defaultRowHeight="15"/>
   <cols>
     <col width="16.9" customWidth="1" style="412" min="30" max="30"/>
@@ -7563,8 +7589,12 @@
       <c r="H14" s="463" t="n"/>
       <c r="I14" s="463" t="n"/>
       <c r="J14" s="463" t="n"/>
-      <c r="K14" s="463" t="n"/>
-      <c r="L14" s="463" t="n"/>
+      <c r="K14" s="464" t="n"/>
+      <c r="L14" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M14" s="463" t="n"/>
       <c r="N14" s="463" t="n"/>
       <c r="O14" s="463" t="n"/>
@@ -7610,7 +7640,7 @@
       <c r="AU14" s="463" t="n"/>
       <c r="AV14" s="464" t="n"/>
     </row>
-    <row r="15" ht="29" customHeight="1" s="412">
+    <row r="15" ht="87" customHeight="1" s="412">
       <c r="B15" s="465" t="inlineStr">
         <is>
           <t>controlPlaneEndpoint（kube-apiserver VIP）</t>
@@ -7624,19 +7654,23 @@
       <c r="H15" s="463" t="n"/>
       <c r="I15" s="463" t="n"/>
       <c r="J15" s="463" t="n"/>
-      <c r="K15" s="463" t="n"/>
-      <c r="L15" s="463" t="n"/>
-      <c r="M15" s="463" t="n"/>
-      <c r="N15" s="463" t="n"/>
-      <c r="O15" s="463" t="n"/>
-      <c r="P15" s="463" t="n"/>
-      <c r="Q15" s="463" t="n"/>
-      <c r="R15" s="463" t="n"/>
-      <c r="S15" s="463" t="n"/>
-      <c r="T15" s="463" t="n"/>
-      <c r="U15" s="463" t="n"/>
-      <c r="V15" s="463" t="n"/>
-      <c r="W15" s="464" t="n"/>
+      <c r="K15" s="464" t="n"/>
+      <c r="L15" s="466" t="inlineStr">
+        <is>
+          <t>kubeadmでHA構成のControl Planeを構築する際、全ノード・全kubectlクライアントが参照する共通のAPIサーバーアドレスとなる。個別ノードのIPを直接指定すると、そのノード障害時にクラスタへアクセスできなくなるため、外部LB経由の単一アドレスに固定する。</t>
+        </is>
+      </c>
+      <c r="M15" s="467" t="n"/>
+      <c r="N15" s="467" t="n"/>
+      <c r="O15" s="467" t="n"/>
+      <c r="P15" s="467" t="n"/>
+      <c r="Q15" s="467" t="n"/>
+      <c r="R15" s="467" t="n"/>
+      <c r="S15" s="467" t="n"/>
+      <c r="T15" s="467" t="n"/>
+      <c r="U15" s="467" t="n"/>
+      <c r="V15" s="467" t="n"/>
+      <c r="W15" s="468" t="n"/>
       <c r="X15" s="465" t="inlineStr">
         <is>
           <t>※要決定（外部LB VIP:6443）</t>
@@ -7671,7 +7705,7 @@
       <c r="AU15" s="463" t="n"/>
       <c r="AV15" s="464" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="58" customHeight="1" s="412">
       <c r="B16" s="465" t="inlineStr">
         <is>
           <t>NTPサーバー</t>
@@ -7685,19 +7719,23 @@
       <c r="H16" s="463" t="n"/>
       <c r="I16" s="463" t="n"/>
       <c r="J16" s="463" t="n"/>
-      <c r="K16" s="463" t="n"/>
-      <c r="L16" s="463" t="n"/>
-      <c r="M16" s="463" t="n"/>
-      <c r="N16" s="463" t="n"/>
-      <c r="O16" s="463" t="n"/>
-      <c r="P16" s="463" t="n"/>
-      <c r="Q16" s="463" t="n"/>
-      <c r="R16" s="463" t="n"/>
-      <c r="S16" s="463" t="n"/>
-      <c r="T16" s="463" t="n"/>
-      <c r="U16" s="463" t="n"/>
-      <c r="V16" s="463" t="n"/>
-      <c r="W16" s="464" t="n"/>
+      <c r="K16" s="464" t="n"/>
+      <c r="L16" s="466" t="inlineStr">
+        <is>
+          <t>etcdの分散合意やTLS証明書の有効期限検証はノード間の時刻同期を前提とする。時刻がずれた状態で構築すると、原因究明が困難な障害につながるため。</t>
+        </is>
+      </c>
+      <c r="M16" s="467" t="n"/>
+      <c r="N16" s="467" t="n"/>
+      <c r="O16" s="467" t="n"/>
+      <c r="P16" s="467" t="n"/>
+      <c r="Q16" s="467" t="n"/>
+      <c r="R16" s="467" t="n"/>
+      <c r="S16" s="467" t="n"/>
+      <c r="T16" s="467" t="n"/>
+      <c r="U16" s="467" t="n"/>
+      <c r="V16" s="467" t="n"/>
+      <c r="W16" s="468" t="n"/>
       <c r="X16" s="465" t="inlineStr">
         <is>
           <t>※要決定</t>
@@ -7732,7 +7770,7 @@
       <c r="AU16" s="463" t="n"/>
       <c r="AV16" s="464" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="29" customHeight="1" s="412">
       <c r="B17" s="465" t="inlineStr">
         <is>
           <t>DNSサーバー</t>
@@ -7746,19 +7784,23 @@
       <c r="H17" s="463" t="n"/>
       <c r="I17" s="463" t="n"/>
       <c r="J17" s="463" t="n"/>
-      <c r="K17" s="463" t="n"/>
-      <c r="L17" s="463" t="n"/>
-      <c r="M17" s="463" t="n"/>
-      <c r="N17" s="463" t="n"/>
-      <c r="O17" s="463" t="n"/>
-      <c r="P17" s="463" t="n"/>
-      <c r="Q17" s="463" t="n"/>
-      <c r="R17" s="463" t="n"/>
-      <c r="S17" s="463" t="n"/>
-      <c r="T17" s="463" t="n"/>
-      <c r="U17" s="463" t="n"/>
-      <c r="V17" s="463" t="n"/>
-      <c r="W17" s="464" t="n"/>
+      <c r="K17" s="464" t="n"/>
+      <c r="L17" s="466" t="inlineStr">
+        <is>
+          <t>ホスト名ベースでの運用や証明書設定等、名前解決を前提とする箇所があるため。</t>
+        </is>
+      </c>
+      <c r="M17" s="467" t="n"/>
+      <c r="N17" s="467" t="n"/>
+      <c r="O17" s="467" t="n"/>
+      <c r="P17" s="467" t="n"/>
+      <c r="Q17" s="467" t="n"/>
+      <c r="R17" s="467" t="n"/>
+      <c r="S17" s="467" t="n"/>
+      <c r="T17" s="467" t="n"/>
+      <c r="U17" s="467" t="n"/>
+      <c r="V17" s="467" t="n"/>
+      <c r="W17" s="468" t="n"/>
       <c r="X17" s="465" t="inlineStr">
         <is>
           <t>※要決定</t>
@@ -7793,7 +7835,7 @@
       <c r="AU17" s="463" t="n"/>
       <c r="AV17" s="464" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="58" customHeight="1" s="412">
       <c r="B18" s="465" t="inlineStr">
         <is>
           <t>ノード用ネットワーク（セグメント/GW）</t>
@@ -7807,19 +7849,23 @@
       <c r="H18" s="463" t="n"/>
       <c r="I18" s="463" t="n"/>
       <c r="J18" s="463" t="n"/>
-      <c r="K18" s="463" t="n"/>
-      <c r="L18" s="463" t="n"/>
-      <c r="M18" s="463" t="n"/>
-      <c r="N18" s="463" t="n"/>
-      <c r="O18" s="463" t="n"/>
-      <c r="P18" s="463" t="n"/>
-      <c r="Q18" s="463" t="n"/>
-      <c r="R18" s="463" t="n"/>
-      <c r="S18" s="463" t="n"/>
-      <c r="T18" s="463" t="n"/>
-      <c r="U18" s="463" t="n"/>
-      <c r="V18" s="463" t="n"/>
-      <c r="W18" s="464" t="n"/>
+      <c r="K18" s="464" t="n"/>
+      <c r="L18" s="466" t="inlineStr">
+        <is>
+          <t>全ノードが同一L2セグメントに属するかどうかは、CalicoのIPカプセル化方式の選定等ネットワーク設計全体に影響するため、事前に確定する必要がある。</t>
+        </is>
+      </c>
+      <c r="M18" s="467" t="n"/>
+      <c r="N18" s="467" t="n"/>
+      <c r="O18" s="467" t="n"/>
+      <c r="P18" s="467" t="n"/>
+      <c r="Q18" s="467" t="n"/>
+      <c r="R18" s="467" t="n"/>
+      <c r="S18" s="467" t="n"/>
+      <c r="T18" s="467" t="n"/>
+      <c r="U18" s="467" t="n"/>
+      <c r="V18" s="467" t="n"/>
+      <c r="W18" s="468" t="n"/>
       <c r="X18" s="465" t="inlineStr">
         <is>
           <t>※要決定</t>
@@ -7862,28 +7908,38 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="466" t="inlineStr">
+      <c r="B21" s="469" t="inlineStr">
         <is>
           <t>ホスト名は例示。命名規約が別途ある場合はそれに従い読み替えること。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="466" t="inlineStr">
+      <c r="B22" s="469" t="inlineStr">
         <is>
           <t>IPアドレス・VIPはネットワーク設計確定後に記入する。</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" s="469" t="inlineStr">
+        <is>
+          <t>Control Plane 3台構成の理由は基本設計書4.1.1（可用性設計）、Worker 2台・GPU搭載の理由は基本設計書3.2.1/3.8（リソース設計・GPU設計）を参照。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="51">
     <mergeCell ref="Q7:X7"/>
     <mergeCell ref="I6:P6"/>
     <mergeCell ref="B9:H9"/>
+    <mergeCell ref="L15:W15"/>
+    <mergeCell ref="L18:W18"/>
+    <mergeCell ref="L14:W14"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="I11:P11"/>
+    <mergeCell ref="B15:K15"/>
     <mergeCell ref="AL15:AV15"/>
-    <mergeCell ref="B15:W15"/>
     <mergeCell ref="Y9:AF9"/>
     <mergeCell ref="X17:AK17"/>
     <mergeCell ref="Q8:X8"/>
@@ -7893,32 +7949,34 @@
     <mergeCell ref="Y11:AF11"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="Y10:AF10"/>
+    <mergeCell ref="B16:K16"/>
     <mergeCell ref="AL16:AV16"/>
     <mergeCell ref="Q10:X10"/>
-    <mergeCell ref="B16:W16"/>
     <mergeCell ref="X18:AK18"/>
     <mergeCell ref="AG10:AV10"/>
     <mergeCell ref="B2:AV2"/>
     <mergeCell ref="AL18:AV18"/>
+    <mergeCell ref="B18:K18"/>
     <mergeCell ref="Y7:AF7"/>
     <mergeCell ref="X15:AK15"/>
     <mergeCell ref="Q6:X6"/>
     <mergeCell ref="Y6:AF6"/>
     <mergeCell ref="AG9:AV9"/>
-    <mergeCell ref="B18:W18"/>
     <mergeCell ref="Q9:X9"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="X14:AK14"/>
     <mergeCell ref="AG6:AV6"/>
     <mergeCell ref="I8:P8"/>
     <mergeCell ref="AL14:AV14"/>
+    <mergeCell ref="L17:W17"/>
     <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B14:K14"/>
     <mergeCell ref="AG11:AV11"/>
-    <mergeCell ref="B14:W14"/>
+    <mergeCell ref="L16:W16"/>
     <mergeCell ref="Q11:X11"/>
+    <mergeCell ref="B17:K17"/>
     <mergeCell ref="AL17:AV17"/>
     <mergeCell ref="I10:P10"/>
-    <mergeCell ref="B17:W17"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="AG7:AV7"/>
     <mergeCell ref="I9:P9"/>
@@ -7970,8 +8028,12 @@
       <c r="H6" s="463" t="n"/>
       <c r="I6" s="463" t="n"/>
       <c r="J6" s="463" t="n"/>
-      <c r="K6" s="463" t="n"/>
-      <c r="L6" s="463" t="n"/>
+      <c r="K6" s="464" t="n"/>
+      <c r="L6" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M6" s="463" t="n"/>
       <c r="N6" s="463" t="n"/>
       <c r="O6" s="463" t="n"/>
@@ -8017,7 +8079,7 @@
       <c r="AU6" s="463" t="n"/>
       <c r="AV6" s="464" t="n"/>
     </row>
-    <row r="7" ht="29" customHeight="1" s="412">
+    <row r="7" ht="43.5" customHeight="1" s="412">
       <c r="B7" s="465" t="inlineStr">
         <is>
           <t>CPU</t>
@@ -8031,19 +8093,23 @@
       <c r="H7" s="463" t="n"/>
       <c r="I7" s="463" t="n"/>
       <c r="J7" s="463" t="n"/>
-      <c r="K7" s="463" t="n"/>
-      <c r="L7" s="463" t="n"/>
-      <c r="M7" s="463" t="n"/>
-      <c r="N7" s="463" t="n"/>
-      <c r="O7" s="463" t="n"/>
-      <c r="P7" s="463" t="n"/>
-      <c r="Q7" s="463" t="n"/>
-      <c r="R7" s="463" t="n"/>
-      <c r="S7" s="463" t="n"/>
-      <c r="T7" s="463" t="n"/>
-      <c r="U7" s="463" t="n"/>
-      <c r="V7" s="463" t="n"/>
-      <c r="W7" s="464" t="n"/>
+      <c r="K7" s="464" t="n"/>
+      <c r="L7" s="466" t="inlineStr">
+        <is>
+          <t>AI学習/分析基盤の想定ワークロード積算（基本設計書3.2.1）から算出した必要CPUコア数を満たすため。</t>
+        </is>
+      </c>
+      <c r="M7" s="467" t="n"/>
+      <c r="N7" s="467" t="n"/>
+      <c r="O7" s="467" t="n"/>
+      <c r="P7" s="467" t="n"/>
+      <c r="Q7" s="467" t="n"/>
+      <c r="R7" s="467" t="n"/>
+      <c r="S7" s="467" t="n"/>
+      <c r="T7" s="467" t="n"/>
+      <c r="U7" s="467" t="n"/>
+      <c r="V7" s="467" t="n"/>
+      <c r="W7" s="468" t="n"/>
       <c r="X7" s="465" t="inlineStr">
         <is>
           <t>Intel Xeon Silver 4514Y（16コア 2.0GHz）×1</t>
@@ -8092,19 +8158,23 @@
       <c r="H8" s="463" t="n"/>
       <c r="I8" s="463" t="n"/>
       <c r="J8" s="463" t="n"/>
-      <c r="K8" s="463" t="n"/>
-      <c r="L8" s="463" t="n"/>
-      <c r="M8" s="463" t="n"/>
-      <c r="N8" s="463" t="n"/>
-      <c r="O8" s="463" t="n"/>
-      <c r="P8" s="463" t="n"/>
-      <c r="Q8" s="463" t="n"/>
-      <c r="R8" s="463" t="n"/>
-      <c r="S8" s="463" t="n"/>
-      <c r="T8" s="463" t="n"/>
-      <c r="U8" s="463" t="n"/>
-      <c r="V8" s="463" t="n"/>
-      <c r="W8" s="464" t="n"/>
+      <c r="K8" s="464" t="n"/>
+      <c r="L8" s="466" t="inlineStr">
+        <is>
+          <t>同上の積算に基づく必要メモリ量を満たすため。</t>
+        </is>
+      </c>
+      <c r="M8" s="467" t="n"/>
+      <c r="N8" s="467" t="n"/>
+      <c r="O8" s="467" t="n"/>
+      <c r="P8" s="467" t="n"/>
+      <c r="Q8" s="467" t="n"/>
+      <c r="R8" s="467" t="n"/>
+      <c r="S8" s="467" t="n"/>
+      <c r="T8" s="467" t="n"/>
+      <c r="U8" s="467" t="n"/>
+      <c r="V8" s="467" t="n"/>
+      <c r="W8" s="468" t="n"/>
       <c r="X8" s="465" t="inlineStr">
         <is>
           <t>64GB（32GB×2枚）</t>
@@ -8139,7 +8209,7 @@
       <c r="AU8" s="463" t="n"/>
       <c r="AV8" s="464" t="n"/>
     </row>
-    <row r="9" ht="29" customHeight="1" s="412">
+    <row r="9" ht="43.5" customHeight="1" s="412">
       <c r="B9" s="465" t="inlineStr">
         <is>
           <t>Bootドライブ</t>
@@ -8153,19 +8223,23 @@
       <c r="H9" s="463" t="n"/>
       <c r="I9" s="463" t="n"/>
       <c r="J9" s="463" t="n"/>
-      <c r="K9" s="463" t="n"/>
-      <c r="L9" s="463" t="n"/>
-      <c r="M9" s="463" t="n"/>
-      <c r="N9" s="463" t="n"/>
-      <c r="O9" s="463" t="n"/>
-      <c r="P9" s="463" t="n"/>
-      <c r="Q9" s="463" t="n"/>
-      <c r="R9" s="463" t="n"/>
-      <c r="S9" s="463" t="n"/>
-      <c r="T9" s="463" t="n"/>
-      <c r="U9" s="463" t="n"/>
-      <c r="V9" s="463" t="n"/>
-      <c r="W9" s="464" t="n"/>
+      <c r="K9" s="464" t="n"/>
+      <c r="L9" s="466" t="inlineStr">
+        <is>
+          <t>OS/etcd/コンテナイメージを冗長化して格納し、単一ディスク故障時にもControl Planeが継続稼働できるようにするため。</t>
+        </is>
+      </c>
+      <c r="M9" s="467" t="n"/>
+      <c r="N9" s="467" t="n"/>
+      <c r="O9" s="467" t="n"/>
+      <c r="P9" s="467" t="n"/>
+      <c r="Q9" s="467" t="n"/>
+      <c r="R9" s="467" t="n"/>
+      <c r="S9" s="467" t="n"/>
+      <c r="T9" s="467" t="n"/>
+      <c r="U9" s="467" t="n"/>
+      <c r="V9" s="467" t="n"/>
+      <c r="W9" s="468" t="n"/>
       <c r="X9" s="465" t="inlineStr">
         <is>
           <t>960GB SATA SSD ×2（RAID1）</t>
@@ -8214,19 +8288,23 @@
       <c r="H10" s="463" t="n"/>
       <c r="I10" s="463" t="n"/>
       <c r="J10" s="463" t="n"/>
-      <c r="K10" s="463" t="n"/>
-      <c r="L10" s="463" t="n"/>
-      <c r="M10" s="463" t="n"/>
-      <c r="N10" s="463" t="n"/>
-      <c r="O10" s="463" t="n"/>
-      <c r="P10" s="463" t="n"/>
-      <c r="Q10" s="463" t="n"/>
-      <c r="R10" s="463" t="n"/>
-      <c r="S10" s="463" t="n"/>
-      <c r="T10" s="463" t="n"/>
-      <c r="U10" s="463" t="n"/>
-      <c r="V10" s="463" t="n"/>
-      <c r="W10" s="464" t="n"/>
+      <c r="K10" s="464" t="n"/>
+      <c r="L10" s="466" t="inlineStr">
+        <is>
+          <t>kube-apiserver等クラスタ制御通信、外部LBとの接続に必要な帯域を確保するため。</t>
+        </is>
+      </c>
+      <c r="M10" s="467" t="n"/>
+      <c r="N10" s="467" t="n"/>
+      <c r="O10" s="467" t="n"/>
+      <c r="P10" s="467" t="n"/>
+      <c r="Q10" s="467" t="n"/>
+      <c r="R10" s="467" t="n"/>
+      <c r="S10" s="467" t="n"/>
+      <c r="T10" s="467" t="n"/>
+      <c r="U10" s="467" t="n"/>
+      <c r="V10" s="467" t="n"/>
+      <c r="W10" s="468" t="n"/>
       <c r="X10" s="465" t="inlineStr">
         <is>
           <t>Broadcom 2ポート 10GBASE-T ×1枚</t>
@@ -8261,7 +8339,7 @@
       <c r="AU10" s="463" t="n"/>
       <c r="AV10" s="464" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="29" customHeight="1" s="412">
       <c r="B11" s="465" t="inlineStr">
         <is>
           <t>電源ユニット</t>
@@ -8275,19 +8353,23 @@
       <c r="H11" s="463" t="n"/>
       <c r="I11" s="463" t="n"/>
       <c r="J11" s="463" t="n"/>
-      <c r="K11" s="463" t="n"/>
-      <c r="L11" s="463" t="n"/>
-      <c r="M11" s="463" t="n"/>
-      <c r="N11" s="463" t="n"/>
-      <c r="O11" s="463" t="n"/>
-      <c r="P11" s="463" t="n"/>
-      <c r="Q11" s="463" t="n"/>
-      <c r="R11" s="463" t="n"/>
-      <c r="S11" s="463" t="n"/>
-      <c r="T11" s="463" t="n"/>
-      <c r="U11" s="463" t="n"/>
-      <c r="V11" s="463" t="n"/>
-      <c r="W11" s="464" t="n"/>
+      <c r="K11" s="464" t="n"/>
+      <c r="L11" s="466" t="inlineStr">
+        <is>
+          <t>電源ユニット単体故障時にもノードが停止しないようにする、可用性設計上の要件。</t>
+        </is>
+      </c>
+      <c r="M11" s="467" t="n"/>
+      <c r="N11" s="467" t="n"/>
+      <c r="O11" s="467" t="n"/>
+      <c r="P11" s="467" t="n"/>
+      <c r="Q11" s="467" t="n"/>
+      <c r="R11" s="467" t="n"/>
+      <c r="S11" s="467" t="n"/>
+      <c r="T11" s="467" t="n"/>
+      <c r="U11" s="467" t="n"/>
+      <c r="V11" s="467" t="n"/>
+      <c r="W11" s="468" t="n"/>
       <c r="X11" s="465" t="inlineStr">
         <is>
           <t>ホットプラグ対応 ×2（冗長構成）</t>
@@ -8336,19 +8418,23 @@
       <c r="H12" s="463" t="n"/>
       <c r="I12" s="463" t="n"/>
       <c r="J12" s="463" t="n"/>
-      <c r="K12" s="463" t="n"/>
-      <c r="L12" s="463" t="n"/>
-      <c r="M12" s="463" t="n"/>
-      <c r="N12" s="463" t="n"/>
-      <c r="O12" s="463" t="n"/>
-      <c r="P12" s="463" t="n"/>
-      <c r="Q12" s="463" t="n"/>
-      <c r="R12" s="463" t="n"/>
-      <c r="S12" s="463" t="n"/>
-      <c r="T12" s="463" t="n"/>
-      <c r="U12" s="463" t="n"/>
-      <c r="V12" s="463" t="n"/>
-      <c r="W12" s="464" t="n"/>
+      <c r="K12" s="464" t="n"/>
+      <c r="L12" s="466" t="inlineStr">
+        <is>
+          <t>ラック設計・電力設計上の前提情報として記載。</t>
+        </is>
+      </c>
+      <c r="M12" s="467" t="n"/>
+      <c r="N12" s="467" t="n"/>
+      <c r="O12" s="467" t="n"/>
+      <c r="P12" s="467" t="n"/>
+      <c r="Q12" s="467" t="n"/>
+      <c r="R12" s="467" t="n"/>
+      <c r="S12" s="467" t="n"/>
+      <c r="T12" s="467" t="n"/>
+      <c r="U12" s="467" t="n"/>
+      <c r="V12" s="467" t="n"/>
+      <c r="W12" s="468" t="n"/>
       <c r="X12" s="465" t="inlineStr">
         <is>
           <t>1U</t>
@@ -8383,7 +8469,7 @@
       <c r="AU12" s="463" t="n"/>
       <c r="AV12" s="464" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="29" customHeight="1" s="412">
       <c r="B13" s="465" t="inlineStr">
         <is>
           <t>サーバ管理モジュール</t>
@@ -8397,19 +8483,23 @@
       <c r="H13" s="463" t="n"/>
       <c r="I13" s="463" t="n"/>
       <c r="J13" s="463" t="n"/>
-      <c r="K13" s="463" t="n"/>
-      <c r="L13" s="463" t="n"/>
-      <c r="M13" s="463" t="n"/>
-      <c r="N13" s="463" t="n"/>
-      <c r="O13" s="463" t="n"/>
-      <c r="P13" s="463" t="n"/>
-      <c r="Q13" s="463" t="n"/>
-      <c r="R13" s="463" t="n"/>
-      <c r="S13" s="463" t="n"/>
-      <c r="T13" s="463" t="n"/>
-      <c r="U13" s="463" t="n"/>
-      <c r="V13" s="463" t="n"/>
-      <c r="W13" s="464" t="n"/>
+      <c r="K13" s="464" t="n"/>
+      <c r="L13" s="466" t="inlineStr">
+        <is>
+          <t>リモートからの電源操作・コンソールアクセス・障害監視を行うために必要。</t>
+        </is>
+      </c>
+      <c r="M13" s="467" t="n"/>
+      <c r="N13" s="467" t="n"/>
+      <c r="O13" s="467" t="n"/>
+      <c r="P13" s="467" t="n"/>
+      <c r="Q13" s="467" t="n"/>
+      <c r="R13" s="467" t="n"/>
+      <c r="S13" s="467" t="n"/>
+      <c r="T13" s="467" t="n"/>
+      <c r="U13" s="467" t="n"/>
+      <c r="V13" s="467" t="n"/>
+      <c r="W13" s="468" t="n"/>
       <c r="X13" s="465" t="inlineStr">
         <is>
           <t>HPE iLO6（1GbE 1ポート）</t>
@@ -8465,8 +8555,12 @@
       <c r="H16" s="463" t="n"/>
       <c r="I16" s="463" t="n"/>
       <c r="J16" s="463" t="n"/>
-      <c r="K16" s="463" t="n"/>
-      <c r="L16" s="463" t="n"/>
+      <c r="K16" s="464" t="n"/>
+      <c r="L16" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M16" s="463" t="n"/>
       <c r="N16" s="463" t="n"/>
       <c r="O16" s="463" t="n"/>
@@ -8512,7 +8606,7 @@
       <c r="AU16" s="463" t="n"/>
       <c r="AV16" s="464" t="n"/>
     </row>
-    <row r="17" ht="29" customHeight="1" s="412">
+    <row r="17" ht="43.5" customHeight="1" s="412">
       <c r="B17" s="465" t="inlineStr">
         <is>
           <t>CPU</t>
@@ -8526,19 +8620,23 @@
       <c r="H17" s="463" t="n"/>
       <c r="I17" s="463" t="n"/>
       <c r="J17" s="463" t="n"/>
-      <c r="K17" s="463" t="n"/>
-      <c r="L17" s="463" t="n"/>
-      <c r="M17" s="463" t="n"/>
-      <c r="N17" s="463" t="n"/>
-      <c r="O17" s="463" t="n"/>
-      <c r="P17" s="463" t="n"/>
-      <c r="Q17" s="463" t="n"/>
-      <c r="R17" s="463" t="n"/>
-      <c r="S17" s="463" t="n"/>
-      <c r="T17" s="463" t="n"/>
-      <c r="U17" s="463" t="n"/>
-      <c r="V17" s="463" t="n"/>
-      <c r="W17" s="464" t="n"/>
+      <c r="K17" s="464" t="n"/>
+      <c r="L17" s="466" t="inlineStr">
+        <is>
+          <t>AI学習ジョブ・分析ワークロードの必要CPUコア数（基本設計書3.2.1）を、Worker2台で満たすため。</t>
+        </is>
+      </c>
+      <c r="M17" s="467" t="n"/>
+      <c r="N17" s="467" t="n"/>
+      <c r="O17" s="467" t="n"/>
+      <c r="P17" s="467" t="n"/>
+      <c r="Q17" s="467" t="n"/>
+      <c r="R17" s="467" t="n"/>
+      <c r="S17" s="467" t="n"/>
+      <c r="T17" s="467" t="n"/>
+      <c r="U17" s="467" t="n"/>
+      <c r="V17" s="467" t="n"/>
+      <c r="W17" s="468" t="n"/>
       <c r="X17" s="465" t="inlineStr">
         <is>
           <t>Intel Xeon Gold 6530（32コア 2.1GHz）×2（64コア/ノード）</t>
@@ -8573,7 +8671,7 @@
       <c r="AU17" s="463" t="n"/>
       <c r="AV17" s="464" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="29" customHeight="1" s="412">
       <c r="B18" s="465" t="inlineStr">
         <is>
           <t>メモリ</t>
@@ -8587,19 +8685,23 @@
       <c r="H18" s="463" t="n"/>
       <c r="I18" s="463" t="n"/>
       <c r="J18" s="463" t="n"/>
-      <c r="K18" s="463" t="n"/>
-      <c r="L18" s="463" t="n"/>
-      <c r="M18" s="463" t="n"/>
-      <c r="N18" s="463" t="n"/>
-      <c r="O18" s="463" t="n"/>
-      <c r="P18" s="463" t="n"/>
-      <c r="Q18" s="463" t="n"/>
-      <c r="R18" s="463" t="n"/>
-      <c r="S18" s="463" t="n"/>
-      <c r="T18" s="463" t="n"/>
-      <c r="U18" s="463" t="n"/>
-      <c r="V18" s="463" t="n"/>
-      <c r="W18" s="464" t="n"/>
+      <c r="K18" s="464" t="n"/>
+      <c r="L18" s="466" t="inlineStr">
+        <is>
+          <t>同上の積算に基づく必要メモリ量を、Worker2台で満たすため。</t>
+        </is>
+      </c>
+      <c r="M18" s="467" t="n"/>
+      <c r="N18" s="467" t="n"/>
+      <c r="O18" s="467" t="n"/>
+      <c r="P18" s="467" t="n"/>
+      <c r="Q18" s="467" t="n"/>
+      <c r="R18" s="467" t="n"/>
+      <c r="S18" s="467" t="n"/>
+      <c r="T18" s="467" t="n"/>
+      <c r="U18" s="467" t="n"/>
+      <c r="V18" s="467" t="n"/>
+      <c r="W18" s="468" t="n"/>
       <c r="X18" s="465" t="inlineStr">
         <is>
           <t>512GB（64GB×8枚）</t>
@@ -8648,19 +8750,23 @@
       <c r="H19" s="463" t="n"/>
       <c r="I19" s="463" t="n"/>
       <c r="J19" s="463" t="n"/>
-      <c r="K19" s="463" t="n"/>
-      <c r="L19" s="463" t="n"/>
-      <c r="M19" s="463" t="n"/>
-      <c r="N19" s="463" t="n"/>
-      <c r="O19" s="463" t="n"/>
-      <c r="P19" s="463" t="n"/>
-      <c r="Q19" s="463" t="n"/>
-      <c r="R19" s="463" t="n"/>
-      <c r="S19" s="463" t="n"/>
-      <c r="T19" s="463" t="n"/>
-      <c r="U19" s="463" t="n"/>
-      <c r="V19" s="463" t="n"/>
-      <c r="W19" s="464" t="n"/>
+      <c r="K19" s="464" t="n"/>
+      <c r="L19" s="466" t="inlineStr">
+        <is>
+          <t>OS領域を冗長化し、単一ディスク故障時にもノードが継続稼働できるようにするため。</t>
+        </is>
+      </c>
+      <c r="M19" s="467" t="n"/>
+      <c r="N19" s="467" t="n"/>
+      <c r="O19" s="467" t="n"/>
+      <c r="P19" s="467" t="n"/>
+      <c r="Q19" s="467" t="n"/>
+      <c r="R19" s="467" t="n"/>
+      <c r="S19" s="467" t="n"/>
+      <c r="T19" s="467" t="n"/>
+      <c r="U19" s="467" t="n"/>
+      <c r="V19" s="467" t="n"/>
+      <c r="W19" s="468" t="n"/>
       <c r="X19" s="465" t="inlineStr">
         <is>
           <t>480GB SATA SSD ×2（RAID1）</t>
@@ -8709,19 +8815,23 @@
       <c r="H20" s="463" t="n"/>
       <c r="I20" s="463" t="n"/>
       <c r="J20" s="463" t="n"/>
-      <c r="K20" s="463" t="n"/>
-      <c r="L20" s="463" t="n"/>
-      <c r="M20" s="463" t="n"/>
-      <c r="N20" s="463" t="n"/>
-      <c r="O20" s="463" t="n"/>
-      <c r="P20" s="463" t="n"/>
-      <c r="Q20" s="463" t="n"/>
-      <c r="R20" s="463" t="n"/>
-      <c r="S20" s="463" t="n"/>
-      <c r="T20" s="463" t="n"/>
-      <c r="U20" s="463" t="n"/>
-      <c r="V20" s="463" t="n"/>
-      <c r="W20" s="464" t="n"/>
+      <c r="K20" s="464" t="n"/>
+      <c r="L20" s="466" t="inlineStr">
+        <is>
+          <t>コンテナイメージ・学習データキャッシュの読み書き性能とディスク故障時の可用性（RAID10）を両立するため。</t>
+        </is>
+      </c>
+      <c r="M20" s="467" t="n"/>
+      <c r="N20" s="467" t="n"/>
+      <c r="O20" s="467" t="n"/>
+      <c r="P20" s="467" t="n"/>
+      <c r="Q20" s="467" t="n"/>
+      <c r="R20" s="467" t="n"/>
+      <c r="S20" s="467" t="n"/>
+      <c r="T20" s="467" t="n"/>
+      <c r="U20" s="467" t="n"/>
+      <c r="V20" s="467" t="n"/>
+      <c r="W20" s="468" t="n"/>
       <c r="X20" s="465" t="inlineStr">
         <is>
           <t>3.84TB Mixed Use SAS SSD ×4（RAID10/実効約7.68TB）</t>
@@ -8756,7 +8866,7 @@
       <c r="AU20" s="463" t="n"/>
       <c r="AV20" s="464" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="43.5" customHeight="1" s="412">
       <c r="B21" s="465" t="inlineStr">
         <is>
           <t>GPUカード</t>
@@ -8770,19 +8880,23 @@
       <c r="H21" s="463" t="n"/>
       <c r="I21" s="463" t="n"/>
       <c r="J21" s="463" t="n"/>
-      <c r="K21" s="463" t="n"/>
-      <c r="L21" s="463" t="n"/>
-      <c r="M21" s="463" t="n"/>
-      <c r="N21" s="463" t="n"/>
-      <c r="O21" s="463" t="n"/>
-      <c r="P21" s="463" t="n"/>
-      <c r="Q21" s="463" t="n"/>
-      <c r="R21" s="463" t="n"/>
-      <c r="S21" s="463" t="n"/>
-      <c r="T21" s="463" t="n"/>
-      <c r="U21" s="463" t="n"/>
-      <c r="V21" s="463" t="n"/>
-      <c r="W21" s="464" t="n"/>
+      <c r="K21" s="464" t="n"/>
+      <c r="L21" s="466" t="inlineStr">
+        <is>
+          <t>AIモデルの学習・推論処理をGPUで高速化するため、基本設計書のGPU設計（3.8）に基づき搭載。</t>
+        </is>
+      </c>
+      <c r="M21" s="467" t="n"/>
+      <c r="N21" s="467" t="n"/>
+      <c r="O21" s="467" t="n"/>
+      <c r="P21" s="467" t="n"/>
+      <c r="Q21" s="467" t="n"/>
+      <c r="R21" s="467" t="n"/>
+      <c r="S21" s="467" t="n"/>
+      <c r="T21" s="467" t="n"/>
+      <c r="U21" s="467" t="n"/>
+      <c r="V21" s="467" t="n"/>
+      <c r="W21" s="468" t="n"/>
       <c r="X21" s="465" t="inlineStr">
         <is>
           <t>NVIDIA H100 NVL ×1枚</t>
@@ -8831,19 +8945,23 @@
       <c r="H22" s="463" t="n"/>
       <c r="I22" s="463" t="n"/>
       <c r="J22" s="463" t="n"/>
-      <c r="K22" s="463" t="n"/>
-      <c r="L22" s="463" t="n"/>
-      <c r="M22" s="463" t="n"/>
-      <c r="N22" s="463" t="n"/>
-      <c r="O22" s="463" t="n"/>
-      <c r="P22" s="463" t="n"/>
-      <c r="Q22" s="463" t="n"/>
-      <c r="R22" s="463" t="n"/>
-      <c r="S22" s="463" t="n"/>
-      <c r="T22" s="463" t="n"/>
-      <c r="U22" s="463" t="n"/>
-      <c r="V22" s="463" t="n"/>
-      <c r="W22" s="464" t="n"/>
+      <c r="K22" s="464" t="n"/>
+      <c r="L22" s="466" t="inlineStr">
+        <is>
+          <t>学習データの転送量が大きいAI基盤の特性上、CPノードより高い帯域を確保するため。</t>
+        </is>
+      </c>
+      <c r="M22" s="467" t="n"/>
+      <c r="N22" s="467" t="n"/>
+      <c r="O22" s="467" t="n"/>
+      <c r="P22" s="467" t="n"/>
+      <c r="Q22" s="467" t="n"/>
+      <c r="R22" s="467" t="n"/>
+      <c r="S22" s="467" t="n"/>
+      <c r="T22" s="467" t="n"/>
+      <c r="U22" s="467" t="n"/>
+      <c r="V22" s="467" t="n"/>
+      <c r="W22" s="468" t="n"/>
       <c r="X22" s="465" t="inlineStr">
         <is>
           <t>Broadcom 2ポート 10GBASE-T ×2枚</t>
@@ -8878,7 +8996,7 @@
       <c r="AU22" s="463" t="n"/>
       <c r="AV22" s="464" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="29" customHeight="1" s="412">
       <c r="B23" s="465" t="inlineStr">
         <is>
           <t>電源ユニット</t>
@@ -8892,19 +9010,23 @@
       <c r="H23" s="463" t="n"/>
       <c r="I23" s="463" t="n"/>
       <c r="J23" s="463" t="n"/>
-      <c r="K23" s="463" t="n"/>
-      <c r="L23" s="463" t="n"/>
-      <c r="M23" s="463" t="n"/>
-      <c r="N23" s="463" t="n"/>
-      <c r="O23" s="463" t="n"/>
-      <c r="P23" s="463" t="n"/>
-      <c r="Q23" s="463" t="n"/>
-      <c r="R23" s="463" t="n"/>
-      <c r="S23" s="463" t="n"/>
-      <c r="T23" s="463" t="n"/>
-      <c r="U23" s="463" t="n"/>
-      <c r="V23" s="463" t="n"/>
-      <c r="W23" s="464" t="n"/>
+      <c r="K23" s="464" t="n"/>
+      <c r="L23" s="466" t="inlineStr">
+        <is>
+          <t>電源ユニット単体故障時にもノードが停止しないようにする、可用性設計上の要件。</t>
+        </is>
+      </c>
+      <c r="M23" s="467" t="n"/>
+      <c r="N23" s="467" t="n"/>
+      <c r="O23" s="467" t="n"/>
+      <c r="P23" s="467" t="n"/>
+      <c r="Q23" s="467" t="n"/>
+      <c r="R23" s="467" t="n"/>
+      <c r="S23" s="467" t="n"/>
+      <c r="T23" s="467" t="n"/>
+      <c r="U23" s="467" t="n"/>
+      <c r="V23" s="467" t="n"/>
+      <c r="W23" s="468" t="n"/>
       <c r="X23" s="465" t="inlineStr">
         <is>
           <t>ホットプラグ対応 1600W ×2（冗長構成）</t>
@@ -8953,19 +9075,23 @@
       <c r="H24" s="463" t="n"/>
       <c r="I24" s="463" t="n"/>
       <c r="J24" s="463" t="n"/>
-      <c r="K24" s="463" t="n"/>
-      <c r="L24" s="463" t="n"/>
-      <c r="M24" s="463" t="n"/>
-      <c r="N24" s="463" t="n"/>
-      <c r="O24" s="463" t="n"/>
-      <c r="P24" s="463" t="n"/>
-      <c r="Q24" s="463" t="n"/>
-      <c r="R24" s="463" t="n"/>
-      <c r="S24" s="463" t="n"/>
-      <c r="T24" s="463" t="n"/>
-      <c r="U24" s="463" t="n"/>
-      <c r="V24" s="463" t="n"/>
-      <c r="W24" s="464" t="n"/>
+      <c r="K24" s="464" t="n"/>
+      <c r="L24" s="466" t="inlineStr">
+        <is>
+          <t>ラック設計・電力設計上の前提情報として記載。</t>
+        </is>
+      </c>
+      <c r="M24" s="467" t="n"/>
+      <c r="N24" s="467" t="n"/>
+      <c r="O24" s="467" t="n"/>
+      <c r="P24" s="467" t="n"/>
+      <c r="Q24" s="467" t="n"/>
+      <c r="R24" s="467" t="n"/>
+      <c r="S24" s="467" t="n"/>
+      <c r="T24" s="467" t="n"/>
+      <c r="U24" s="467" t="n"/>
+      <c r="V24" s="467" t="n"/>
+      <c r="W24" s="468" t="n"/>
       <c r="X24" s="465" t="inlineStr">
         <is>
           <t>2U</t>
@@ -9000,7 +9126,7 @@
       <c r="AU24" s="463" t="n"/>
       <c r="AV24" s="464" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="29" customHeight="1" s="412">
       <c r="B25" s="465" t="inlineStr">
         <is>
           <t>サーバ管理モジュール</t>
@@ -9014,19 +9140,23 @@
       <c r="H25" s="463" t="n"/>
       <c r="I25" s="463" t="n"/>
       <c r="J25" s="463" t="n"/>
-      <c r="K25" s="463" t="n"/>
-      <c r="L25" s="463" t="n"/>
-      <c r="M25" s="463" t="n"/>
-      <c r="N25" s="463" t="n"/>
-      <c r="O25" s="463" t="n"/>
-      <c r="P25" s="463" t="n"/>
-      <c r="Q25" s="463" t="n"/>
-      <c r="R25" s="463" t="n"/>
-      <c r="S25" s="463" t="n"/>
-      <c r="T25" s="463" t="n"/>
-      <c r="U25" s="463" t="n"/>
-      <c r="V25" s="463" t="n"/>
-      <c r="W25" s="464" t="n"/>
+      <c r="K25" s="464" t="n"/>
+      <c r="L25" s="466" t="inlineStr">
+        <is>
+          <t>リモートからの電源操作・コンソールアクセス・障害監視を行うために必要。</t>
+        </is>
+      </c>
+      <c r="M25" s="467" t="n"/>
+      <c r="N25" s="467" t="n"/>
+      <c r="O25" s="467" t="n"/>
+      <c r="P25" s="467" t="n"/>
+      <c r="Q25" s="467" t="n"/>
+      <c r="R25" s="467" t="n"/>
+      <c r="S25" s="467" t="n"/>
+      <c r="T25" s="467" t="n"/>
+      <c r="U25" s="467" t="n"/>
+      <c r="V25" s="467" t="n"/>
+      <c r="W25" s="468" t="n"/>
       <c r="X25" s="465" t="inlineStr">
         <is>
           <t>HPE iLO6（1GbE 1ポート）</t>
@@ -9062,62 +9192,80 @@
       <c r="AV25" s="464" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="73">
     <mergeCell ref="X22:AK22"/>
     <mergeCell ref="X9:AK9"/>
-    <mergeCell ref="B10:W10"/>
-    <mergeCell ref="B19:W19"/>
     <mergeCell ref="AL22:AV22"/>
     <mergeCell ref="AL9:AV9"/>
+    <mergeCell ref="B9:K9"/>
     <mergeCell ref="X21:AK21"/>
     <mergeCell ref="X12:AK12"/>
+    <mergeCell ref="L18:W18"/>
+    <mergeCell ref="L24:W24"/>
     <mergeCell ref="AL6:AV6"/>
-    <mergeCell ref="B9:W9"/>
+    <mergeCell ref="B6:K6"/>
     <mergeCell ref="X11:AK11"/>
+    <mergeCell ref="L8:W8"/>
+    <mergeCell ref="B20:K20"/>
+    <mergeCell ref="L23:W23"/>
+    <mergeCell ref="B24:K24"/>
     <mergeCell ref="AL11:AV11"/>
     <mergeCell ref="X23:AK23"/>
-    <mergeCell ref="B6:W6"/>
     <mergeCell ref="X8:AK8"/>
-    <mergeCell ref="B20:W20"/>
-    <mergeCell ref="B24:W24"/>
     <mergeCell ref="X17:AK17"/>
+    <mergeCell ref="L20:W20"/>
     <mergeCell ref="X13:AK13"/>
+    <mergeCell ref="L25:W25"/>
     <mergeCell ref="X7:AK7"/>
+    <mergeCell ref="L10:W10"/>
     <mergeCell ref="X16:AK16"/>
     <mergeCell ref="AL7:AV7"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B25:K25"/>
     <mergeCell ref="AL25:AV25"/>
     <mergeCell ref="AL16:AV16"/>
+    <mergeCell ref="B16:K16"/>
     <mergeCell ref="X19:AK19"/>
-    <mergeCell ref="B7:W7"/>
-    <mergeCell ref="B25:W25"/>
-    <mergeCell ref="B16:W16"/>
+    <mergeCell ref="L22:W22"/>
+    <mergeCell ref="L9:W9"/>
     <mergeCell ref="AL13:AV13"/>
     <mergeCell ref="X18:AK18"/>
     <mergeCell ref="B2:AV2"/>
+    <mergeCell ref="L21:W21"/>
+    <mergeCell ref="L6:W6"/>
+    <mergeCell ref="B22:K22"/>
     <mergeCell ref="AL12:AV12"/>
+    <mergeCell ref="B18:K18"/>
     <mergeCell ref="AL18:AV18"/>
     <mergeCell ref="AL21:AV21"/>
-    <mergeCell ref="B22:W22"/>
+    <mergeCell ref="B21:K21"/>
     <mergeCell ref="X6:AK6"/>
+    <mergeCell ref="L11:W11"/>
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="X20:AK20"/>
     <mergeCell ref="X24:AK24"/>
-    <mergeCell ref="X20:AK20"/>
-    <mergeCell ref="B18:W18"/>
-    <mergeCell ref="B21:W21"/>
     <mergeCell ref="AL24:AV24"/>
-    <mergeCell ref="B12:W12"/>
+    <mergeCell ref="B11:K11"/>
+    <mergeCell ref="L17:W17"/>
     <mergeCell ref="AL23:AV23"/>
-    <mergeCell ref="B11:W11"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="L7:W7"/>
     <mergeCell ref="AL8:AV8"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="L16:W16"/>
     <mergeCell ref="AL17:AV17"/>
-    <mergeCell ref="B23:W23"/>
-    <mergeCell ref="B8:W8"/>
+    <mergeCell ref="B17:K17"/>
+    <mergeCell ref="B13:K13"/>
     <mergeCell ref="X10:AK10"/>
-    <mergeCell ref="B17:W17"/>
+    <mergeCell ref="L13:W13"/>
+    <mergeCell ref="L19:W19"/>
     <mergeCell ref="AL20:AV20"/>
-    <mergeCell ref="B13:W13"/>
     <mergeCell ref="X25:AK25"/>
     <mergeCell ref="AL10:AV10"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="L12:W12"/>
     <mergeCell ref="AL19:AV19"/>
+    <mergeCell ref="B19:K19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9129,7 +9277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AV64"/>
+  <dimension ref="B2:AV64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.6" defaultRowHeight="15"/>
   <cols>
     <col width="16.9" customWidth="1" style="412" min="30" max="30"/>
@@ -9137,7 +9285,6 @@
     <col width="16.9" customWidth="1" style="412" min="48" max="48"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="460" t="inlineStr">
         <is>
@@ -9145,10 +9292,8 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
-      <c r="B5" s="467" t="inlineStr">
+      <c r="B5" s="470" t="inlineStr">
         <is>
           <t>対象ノード</t>
         </is>
@@ -9178,7 +9323,7 @@
       <c r="U5" s="463" t="n"/>
       <c r="V5" s="463" t="n"/>
       <c r="W5" s="464" t="n"/>
-      <c r="X5" s="467" t="inlineStr">
+      <c r="X5" s="470" t="inlineStr">
         <is>
           <t>OSバージョン</t>
         </is>
@@ -9212,7 +9357,6 @@
       <c r="AU5" s="463" t="n"/>
       <c r="AV5" s="464" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="461" t="inlineStr">
         <is>
@@ -9234,8 +9378,12 @@
       <c r="H8" s="463" t="n"/>
       <c r="I8" s="463" t="n"/>
       <c r="J8" s="463" t="n"/>
-      <c r="K8" s="463" t="n"/>
-      <c r="L8" s="463" t="n"/>
+      <c r="K8" s="464" t="n"/>
+      <c r="L8" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M8" s="463" t="n"/>
       <c r="N8" s="463" t="n"/>
       <c r="O8" s="463" t="n"/>
@@ -9285,7 +9433,7 @@
       <c r="AU8" s="463" t="n"/>
       <c r="AV8" s="464" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="58" customHeight="1" s="412">
       <c r="B9" s="465" t="inlineStr">
         <is>
           <t>インストール言語</t>
@@ -9299,19 +9447,23 @@
       <c r="H9" s="463" t="n"/>
       <c r="I9" s="463" t="n"/>
       <c r="J9" s="463" t="n"/>
-      <c r="K9" s="463" t="n"/>
-      <c r="L9" s="463" t="n"/>
-      <c r="M9" s="463" t="n"/>
-      <c r="N9" s="463" t="n"/>
-      <c r="O9" s="463" t="n"/>
-      <c r="P9" s="463" t="n"/>
-      <c r="Q9" s="463" t="n"/>
-      <c r="R9" s="463" t="n"/>
-      <c r="S9" s="463" t="n"/>
-      <c r="T9" s="463" t="n"/>
-      <c r="U9" s="463" t="n"/>
-      <c r="V9" s="463" t="n"/>
-      <c r="W9" s="464" t="n"/>
+      <c r="K9" s="464" t="n"/>
+      <c r="L9" s="466" t="inlineStr">
+        <is>
+          <t>ログ・エラーメッセージを英語で統一することで、公式ドキュメント・コミュニティの技術情報と照合しやすくし、トラブルシューティング効率を高めるため。</t>
+        </is>
+      </c>
+      <c r="M9" s="467" t="n"/>
+      <c r="N9" s="467" t="n"/>
+      <c r="O9" s="467" t="n"/>
+      <c r="P9" s="467" t="n"/>
+      <c r="Q9" s="467" t="n"/>
+      <c r="R9" s="467" t="n"/>
+      <c r="S9" s="467" t="n"/>
+      <c r="T9" s="467" t="n"/>
+      <c r="U9" s="467" t="n"/>
+      <c r="V9" s="467" t="n"/>
+      <c r="W9" s="468" t="n"/>
       <c r="X9" s="465" t="inlineStr">
         <is>
           <t>English</t>
@@ -9350,7 +9502,7 @@
       <c r="AU9" s="463" t="n"/>
       <c r="AV9" s="464" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="43.5" customHeight="1" s="412">
       <c r="B10" s="465" t="inlineStr">
         <is>
           <t>タイムゾーン</t>
@@ -9364,19 +9516,23 @@
       <c r="H10" s="463" t="n"/>
       <c r="I10" s="463" t="n"/>
       <c r="J10" s="463" t="n"/>
-      <c r="K10" s="463" t="n"/>
-      <c r="L10" s="463" t="n"/>
-      <c r="M10" s="463" t="n"/>
-      <c r="N10" s="463" t="n"/>
-      <c r="O10" s="463" t="n"/>
-      <c r="P10" s="463" t="n"/>
-      <c r="Q10" s="463" t="n"/>
-      <c r="R10" s="463" t="n"/>
-      <c r="S10" s="463" t="n"/>
-      <c r="T10" s="463" t="n"/>
-      <c r="U10" s="463" t="n"/>
-      <c r="V10" s="463" t="n"/>
-      <c r="W10" s="464" t="n"/>
+      <c r="K10" s="464" t="n"/>
+      <c r="L10" s="466" t="inlineStr">
+        <is>
+          <t>運用担当者の業務時間（日本時間）とログのタイムスタンプを一致させ、障害調査時の時系列把握を容易にするため。</t>
+        </is>
+      </c>
+      <c r="M10" s="467" t="n"/>
+      <c r="N10" s="467" t="n"/>
+      <c r="O10" s="467" t="n"/>
+      <c r="P10" s="467" t="n"/>
+      <c r="Q10" s="467" t="n"/>
+      <c r="R10" s="467" t="n"/>
+      <c r="S10" s="467" t="n"/>
+      <c r="T10" s="467" t="n"/>
+      <c r="U10" s="467" t="n"/>
+      <c r="V10" s="467" t="n"/>
+      <c r="W10" s="468" t="n"/>
       <c r="X10" s="465" t="inlineStr">
         <is>
           <t>Asia/Tokyo</t>
@@ -9415,7 +9571,7 @@
       <c r="AU10" s="463" t="n"/>
       <c r="AV10" s="464" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="29" customHeight="1" s="412">
       <c r="B11" s="465" t="inlineStr">
         <is>
           <t>キーボードレイアウト</t>
@@ -9429,19 +9585,23 @@
       <c r="H11" s="463" t="n"/>
       <c r="I11" s="463" t="n"/>
       <c r="J11" s="463" t="n"/>
-      <c r="K11" s="463" t="n"/>
-      <c r="L11" s="463" t="n"/>
-      <c r="M11" s="463" t="n"/>
-      <c r="N11" s="463" t="n"/>
-      <c r="O11" s="463" t="n"/>
-      <c r="P11" s="463" t="n"/>
-      <c r="Q11" s="463" t="n"/>
-      <c r="R11" s="463" t="n"/>
-      <c r="S11" s="463" t="n"/>
-      <c r="T11" s="463" t="n"/>
-      <c r="U11" s="463" t="n"/>
-      <c r="V11" s="463" t="n"/>
-      <c r="W11" s="464" t="n"/>
+      <c r="K11" s="464" t="n"/>
+      <c r="L11" s="466" t="inlineStr">
+        <is>
+          <t>運用担当者が日本語キーボードでコンソール作業を行うことを想定しているため。</t>
+        </is>
+      </c>
+      <c r="M11" s="467" t="n"/>
+      <c r="N11" s="467" t="n"/>
+      <c r="O11" s="467" t="n"/>
+      <c r="P11" s="467" t="n"/>
+      <c r="Q11" s="467" t="n"/>
+      <c r="R11" s="467" t="n"/>
+      <c r="S11" s="467" t="n"/>
+      <c r="T11" s="467" t="n"/>
+      <c r="U11" s="467" t="n"/>
+      <c r="V11" s="467" t="n"/>
+      <c r="W11" s="468" t="n"/>
       <c r="X11" s="465" t="inlineStr">
         <is>
           <t>Japanese</t>
@@ -9480,7 +9640,6 @@
       <c r="AU11" s="463" t="n"/>
       <c r="AV11" s="464" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="B13" s="461" t="inlineStr">
         <is>
@@ -9502,8 +9661,12 @@
       <c r="H14" s="463" t="n"/>
       <c r="I14" s="463" t="n"/>
       <c r="J14" s="463" t="n"/>
-      <c r="K14" s="463" t="n"/>
-      <c r="L14" s="463" t="n"/>
+      <c r="K14" s="464" t="n"/>
+      <c r="L14" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M14" s="463" t="n"/>
       <c r="N14" s="463" t="n"/>
       <c r="O14" s="463" t="n"/>
@@ -9553,7 +9716,7 @@
       <c r="AU14" s="463" t="n"/>
       <c r="AV14" s="464" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="43.5" customHeight="1" s="412">
       <c r="B15" s="465" t="inlineStr">
         <is>
           <t>パーティション構成</t>
@@ -9567,19 +9730,23 @@
       <c r="H15" s="463" t="n"/>
       <c r="I15" s="463" t="n"/>
       <c r="J15" s="463" t="n"/>
-      <c r="K15" s="463" t="n"/>
-      <c r="L15" s="463" t="n"/>
-      <c r="M15" s="463" t="n"/>
-      <c r="N15" s="463" t="n"/>
-      <c r="O15" s="463" t="n"/>
-      <c r="P15" s="463" t="n"/>
-      <c r="Q15" s="463" t="n"/>
-      <c r="R15" s="463" t="n"/>
-      <c r="S15" s="463" t="n"/>
-      <c r="T15" s="463" t="n"/>
-      <c r="U15" s="463" t="n"/>
-      <c r="V15" s="463" t="n"/>
-      <c r="W15" s="464" t="n"/>
+      <c r="K15" s="464" t="n"/>
+      <c r="L15" s="466" t="inlineStr">
+        <is>
+          <t>自動構成ではswap領域が自動的に作成されてしまうため、Kubernetes要件（swap無効化）を満たすには手動構成が必要。</t>
+        </is>
+      </c>
+      <c r="M15" s="467" t="n"/>
+      <c r="N15" s="467" t="n"/>
+      <c r="O15" s="467" t="n"/>
+      <c r="P15" s="467" t="n"/>
+      <c r="Q15" s="467" t="n"/>
+      <c r="R15" s="467" t="n"/>
+      <c r="S15" s="467" t="n"/>
+      <c r="T15" s="467" t="n"/>
+      <c r="U15" s="467" t="n"/>
+      <c r="V15" s="467" t="n"/>
+      <c r="W15" s="468" t="n"/>
       <c r="X15" s="465" t="inlineStr">
         <is>
           <t>■手動構成　□自動構成</t>
@@ -9618,7 +9785,7 @@
       <c r="AU15" s="463" t="n"/>
       <c r="AV15" s="464" t="n"/>
     </row>
-    <row r="16" ht="29" customHeight="1" s="412">
+    <row r="16" ht="43.5" customHeight="1" s="412">
       <c r="C16" s="465" t="inlineStr">
         <is>
           <t>マウントポイント /</t>
@@ -9631,19 +9798,23 @@
       <c r="H16" s="463" t="n"/>
       <c r="I16" s="463" t="n"/>
       <c r="J16" s="463" t="n"/>
-      <c r="K16" s="463" t="n"/>
-      <c r="L16" s="463" t="n"/>
-      <c r="M16" s="463" t="n"/>
-      <c r="N16" s="463" t="n"/>
-      <c r="O16" s="463" t="n"/>
-      <c r="P16" s="463" t="n"/>
-      <c r="Q16" s="463" t="n"/>
-      <c r="R16" s="463" t="n"/>
-      <c r="S16" s="463" t="n"/>
-      <c r="T16" s="463" t="n"/>
-      <c r="U16" s="463" t="n"/>
-      <c r="V16" s="463" t="n"/>
-      <c r="W16" s="464" t="n"/>
+      <c r="K16" s="464" t="n"/>
+      <c r="L16" s="466" t="inlineStr">
+        <is>
+          <t>OS・ミドルウェアの格納領域。残容量を割り当てることで、将来的な増設に対する余裕を持たせるため。</t>
+        </is>
+      </c>
+      <c r="M16" s="467" t="n"/>
+      <c r="N16" s="467" t="n"/>
+      <c r="O16" s="467" t="n"/>
+      <c r="P16" s="467" t="n"/>
+      <c r="Q16" s="467" t="n"/>
+      <c r="R16" s="467" t="n"/>
+      <c r="S16" s="467" t="n"/>
+      <c r="T16" s="467" t="n"/>
+      <c r="U16" s="467" t="n"/>
+      <c r="V16" s="467" t="n"/>
+      <c r="W16" s="468" t="n"/>
       <c r="X16" s="465" t="inlineStr">
         <is>
           <t>LVM / ext4 / Bootドライブ残容量</t>
@@ -9695,19 +9866,23 @@
       <c r="H17" s="463" t="n"/>
       <c r="I17" s="463" t="n"/>
       <c r="J17" s="463" t="n"/>
-      <c r="K17" s="463" t="n"/>
-      <c r="L17" s="463" t="n"/>
-      <c r="M17" s="463" t="n"/>
-      <c r="N17" s="463" t="n"/>
-      <c r="O17" s="463" t="n"/>
-      <c r="P17" s="463" t="n"/>
-      <c r="Q17" s="463" t="n"/>
-      <c r="R17" s="463" t="n"/>
-      <c r="S17" s="463" t="n"/>
-      <c r="T17" s="463" t="n"/>
-      <c r="U17" s="463" t="n"/>
-      <c r="V17" s="463" t="n"/>
-      <c r="W17" s="464" t="n"/>
+      <c r="K17" s="464" t="n"/>
+      <c r="L17" s="466" t="inlineStr">
+        <is>
+          <t>UEFIブートに必要な起動用パーティション。</t>
+        </is>
+      </c>
+      <c r="M17" s="467" t="n"/>
+      <c r="N17" s="467" t="n"/>
+      <c r="O17" s="467" t="n"/>
+      <c r="P17" s="467" t="n"/>
+      <c r="Q17" s="467" t="n"/>
+      <c r="R17" s="467" t="n"/>
+      <c r="S17" s="467" t="n"/>
+      <c r="T17" s="467" t="n"/>
+      <c r="U17" s="467" t="n"/>
+      <c r="V17" s="467" t="n"/>
+      <c r="W17" s="468" t="n"/>
       <c r="X17" s="465" t="inlineStr">
         <is>
           <t>EFI System Partition / 1GB</t>
@@ -9759,19 +9934,23 @@
       <c r="H18" s="463" t="n"/>
       <c r="I18" s="463" t="n"/>
       <c r="J18" s="463" t="n"/>
-      <c r="K18" s="463" t="n"/>
-      <c r="L18" s="463" t="n"/>
-      <c r="M18" s="463" t="n"/>
-      <c r="N18" s="463" t="n"/>
-      <c r="O18" s="463" t="n"/>
-      <c r="P18" s="463" t="n"/>
-      <c r="Q18" s="463" t="n"/>
-      <c r="R18" s="463" t="n"/>
-      <c r="S18" s="463" t="n"/>
-      <c r="T18" s="463" t="n"/>
-      <c r="U18" s="463" t="n"/>
-      <c r="V18" s="463" t="n"/>
-      <c r="W18" s="464" t="n"/>
+      <c r="K18" s="464" t="n"/>
+      <c r="L18" s="466" t="inlineStr">
+        <is>
+          <t>kubeletはswapが有効なノードでは起動しない（Kubernetesの既定要件）ため。</t>
+        </is>
+      </c>
+      <c r="M18" s="467" t="n"/>
+      <c r="N18" s="467" t="n"/>
+      <c r="O18" s="467" t="n"/>
+      <c r="P18" s="467" t="n"/>
+      <c r="Q18" s="467" t="n"/>
+      <c r="R18" s="467" t="n"/>
+      <c r="S18" s="467" t="n"/>
+      <c r="T18" s="467" t="n"/>
+      <c r="U18" s="467" t="n"/>
+      <c r="V18" s="467" t="n"/>
+      <c r="W18" s="468" t="n"/>
       <c r="X18" s="465" t="inlineStr">
         <is>
           <t>作成しない</t>
@@ -9810,7 +9989,7 @@
       <c r="AU18" s="463" t="n"/>
       <c r="AV18" s="464" t="n"/>
     </row>
-    <row r="19" ht="43.5" customHeight="1" s="412">
+    <row r="19" ht="58" customHeight="1" s="412">
       <c r="C19" s="465" t="inlineStr">
         <is>
           <t>データ領域（Worker Nodeのみ）</t>
@@ -9823,19 +10002,23 @@
       <c r="H19" s="463" t="n"/>
       <c r="I19" s="463" t="n"/>
       <c r="J19" s="463" t="n"/>
-      <c r="K19" s="463" t="n"/>
-      <c r="L19" s="463" t="n"/>
-      <c r="M19" s="463" t="n"/>
-      <c r="N19" s="463" t="n"/>
-      <c r="O19" s="463" t="n"/>
-      <c r="P19" s="463" t="n"/>
-      <c r="Q19" s="463" t="n"/>
-      <c r="R19" s="463" t="n"/>
-      <c r="S19" s="463" t="n"/>
-      <c r="T19" s="463" t="n"/>
-      <c r="U19" s="463" t="n"/>
-      <c r="V19" s="463" t="n"/>
-      <c r="W19" s="464" t="n"/>
+      <c r="K19" s="464" t="n"/>
+      <c r="L19" s="466" t="inlineStr">
+        <is>
+          <t>コンテナイメージやkubeletの一時領域が/上に混在するとOS領域を圧迫し、ノード不安定化につながるため、独立した高速・大容量ボリュームに分離する。</t>
+        </is>
+      </c>
+      <c r="M19" s="467" t="n"/>
+      <c r="N19" s="467" t="n"/>
+      <c r="O19" s="467" t="n"/>
+      <c r="P19" s="467" t="n"/>
+      <c r="Q19" s="467" t="n"/>
+      <c r="R19" s="467" t="n"/>
+      <c r="S19" s="467" t="n"/>
+      <c r="T19" s="467" t="n"/>
+      <c r="U19" s="467" t="n"/>
+      <c r="V19" s="467" t="n"/>
+      <c r="W19" s="468" t="n"/>
       <c r="X19" s="465" t="inlineStr">
         <is>
           <t>/var/lib/containerd ほか / ext4 / RAID10ボリューム（約7.68TB）</t>
@@ -9874,7 +10057,6 @@
       <c r="AU19" s="463" t="n"/>
       <c r="AV19" s="464" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="B21" s="461" t="inlineStr">
         <is>
@@ -9896,8 +10078,12 @@
       <c r="H22" s="463" t="n"/>
       <c r="I22" s="463" t="n"/>
       <c r="J22" s="463" t="n"/>
-      <c r="K22" s="463" t="n"/>
-      <c r="L22" s="463" t="n"/>
+      <c r="K22" s="464" t="n"/>
+      <c r="L22" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M22" s="463" t="n"/>
       <c r="N22" s="463" t="n"/>
       <c r="O22" s="463" t="n"/>
@@ -9947,7 +10133,7 @@
       <c r="AU22" s="463" t="n"/>
       <c r="AV22" s="464" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="43.5" customHeight="1" s="412">
       <c r="B23" s="465" t="inlineStr">
         <is>
           <t>IPv4 方式</t>
@@ -9961,19 +10147,23 @@
       <c r="H23" s="463" t="n"/>
       <c r="I23" s="463" t="n"/>
       <c r="J23" s="463" t="n"/>
-      <c r="K23" s="463" t="n"/>
-      <c r="L23" s="463" t="n"/>
-      <c r="M23" s="463" t="n"/>
-      <c r="N23" s="463" t="n"/>
-      <c r="O23" s="463" t="n"/>
-      <c r="P23" s="463" t="n"/>
-      <c r="Q23" s="463" t="n"/>
-      <c r="R23" s="463" t="n"/>
-      <c r="S23" s="463" t="n"/>
-      <c r="T23" s="463" t="n"/>
-      <c r="U23" s="463" t="n"/>
-      <c r="V23" s="463" t="n"/>
-      <c r="W23" s="464" t="n"/>
+      <c r="K23" s="464" t="n"/>
+      <c r="L23" s="466" t="inlineStr">
+        <is>
+          <t>kubeadmやCalico、外部LBとの通信は固定IPを前提として設計されているため、DHCPではなく静的IPとする。</t>
+        </is>
+      </c>
+      <c r="M23" s="467" t="n"/>
+      <c r="N23" s="467" t="n"/>
+      <c r="O23" s="467" t="n"/>
+      <c r="P23" s="467" t="n"/>
+      <c r="Q23" s="467" t="n"/>
+      <c r="R23" s="467" t="n"/>
+      <c r="S23" s="467" t="n"/>
+      <c r="T23" s="467" t="n"/>
+      <c r="U23" s="467" t="n"/>
+      <c r="V23" s="467" t="n"/>
+      <c r="W23" s="468" t="n"/>
       <c r="X23" s="465" t="inlineStr">
         <is>
           <t>手動（静的）</t>
@@ -10026,19 +10216,23 @@
       <c r="H24" s="463" t="n"/>
       <c r="I24" s="463" t="n"/>
       <c r="J24" s="463" t="n"/>
-      <c r="K24" s="463" t="n"/>
-      <c r="L24" s="463" t="n"/>
-      <c r="M24" s="463" t="n"/>
-      <c r="N24" s="463" t="n"/>
-      <c r="O24" s="463" t="n"/>
-      <c r="P24" s="463" t="n"/>
-      <c r="Q24" s="463" t="n"/>
-      <c r="R24" s="463" t="n"/>
-      <c r="S24" s="463" t="n"/>
-      <c r="T24" s="463" t="n"/>
-      <c r="U24" s="463" t="n"/>
-      <c r="V24" s="463" t="n"/>
-      <c r="W24" s="464" t="n"/>
+      <c r="K24" s="464" t="n"/>
+      <c r="L24" s="466" t="inlineStr">
+        <is>
+          <t>パッケージ取得・名前解決に必要。</t>
+        </is>
+      </c>
+      <c r="M24" s="467" t="n"/>
+      <c r="N24" s="467" t="n"/>
+      <c r="O24" s="467" t="n"/>
+      <c r="P24" s="467" t="n"/>
+      <c r="Q24" s="467" t="n"/>
+      <c r="R24" s="467" t="n"/>
+      <c r="S24" s="467" t="n"/>
+      <c r="T24" s="467" t="n"/>
+      <c r="U24" s="467" t="n"/>
+      <c r="V24" s="467" t="n"/>
+      <c r="W24" s="468" t="n"/>
       <c r="X24" s="465" t="inlineStr">
         <is>
           <t>※要決定</t>
@@ -10077,7 +10271,7 @@
       <c r="AU24" s="463" t="n"/>
       <c r="AV24" s="464" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="29" customHeight="1" s="412">
       <c r="B25" s="465" t="inlineStr">
         <is>
           <t>IPv6</t>
@@ -10091,19 +10285,23 @@
       <c r="H25" s="463" t="n"/>
       <c r="I25" s="463" t="n"/>
       <c r="J25" s="463" t="n"/>
-      <c r="K25" s="463" t="n"/>
-      <c r="L25" s="463" t="n"/>
-      <c r="M25" s="463" t="n"/>
-      <c r="N25" s="463" t="n"/>
-      <c r="O25" s="463" t="n"/>
-      <c r="P25" s="463" t="n"/>
-      <c r="Q25" s="463" t="n"/>
-      <c r="R25" s="463" t="n"/>
-      <c r="S25" s="463" t="n"/>
-      <c r="T25" s="463" t="n"/>
-      <c r="U25" s="463" t="n"/>
-      <c r="V25" s="463" t="n"/>
-      <c r="W25" s="464" t="n"/>
+      <c r="K25" s="464" t="n"/>
+      <c r="L25" s="466" t="inlineStr">
+        <is>
+          <t>本設計はIPv4のみで構成しており、意図しない経路として動作しないよう明示的に無効化する。</t>
+        </is>
+      </c>
+      <c r="M25" s="467" t="n"/>
+      <c r="N25" s="467" t="n"/>
+      <c r="O25" s="467" t="n"/>
+      <c r="P25" s="467" t="n"/>
+      <c r="Q25" s="467" t="n"/>
+      <c r="R25" s="467" t="n"/>
+      <c r="S25" s="467" t="n"/>
+      <c r="T25" s="467" t="n"/>
+      <c r="U25" s="467" t="n"/>
+      <c r="V25" s="467" t="n"/>
+      <c r="W25" s="468" t="n"/>
       <c r="X25" s="465" t="inlineStr">
         <is>
           <t>無効</t>
@@ -10142,7 +10340,7 @@
       <c r="AU25" s="463" t="n"/>
       <c r="AV25" s="464" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="29" customHeight="1" s="412">
       <c r="B26" s="465" t="inlineStr">
         <is>
           <t>ホスト名</t>
@@ -10156,19 +10354,23 @@
       <c r="H26" s="463" t="n"/>
       <c r="I26" s="463" t="n"/>
       <c r="J26" s="463" t="n"/>
-      <c r="K26" s="463" t="n"/>
-      <c r="L26" s="463" t="n"/>
-      <c r="M26" s="463" t="n"/>
-      <c r="N26" s="463" t="n"/>
-      <c r="O26" s="463" t="n"/>
-      <c r="P26" s="463" t="n"/>
-      <c r="Q26" s="463" t="n"/>
-      <c r="R26" s="463" t="n"/>
-      <c r="S26" s="463" t="n"/>
-      <c r="T26" s="463" t="n"/>
-      <c r="U26" s="463" t="n"/>
-      <c r="V26" s="463" t="n"/>
-      <c r="W26" s="464" t="n"/>
+      <c r="K26" s="464" t="n"/>
+      <c r="L26" s="466" t="inlineStr">
+        <is>
+          <t>クラスタ参加後にホスト名を変更するとノード識別が壊れるため、事前に確定し変更しない前提とする。</t>
+        </is>
+      </c>
+      <c r="M26" s="467" t="n"/>
+      <c r="N26" s="467" t="n"/>
+      <c r="O26" s="467" t="n"/>
+      <c r="P26" s="467" t="n"/>
+      <c r="Q26" s="467" t="n"/>
+      <c r="R26" s="467" t="n"/>
+      <c r="S26" s="467" t="n"/>
+      <c r="T26" s="467" t="n"/>
+      <c r="U26" s="467" t="n"/>
+      <c r="V26" s="467" t="n"/>
+      <c r="W26" s="468" t="n"/>
       <c r="X26" s="465" t="inlineStr">
         <is>
           <t>「ノード構成」シート参照</t>
@@ -10207,7 +10409,6 @@
       <c r="AU26" s="463" t="n"/>
       <c r="AV26" s="464" t="n"/>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="B28" s="461" t="inlineStr">
         <is>
@@ -10229,8 +10430,12 @@
       <c r="H29" s="463" t="n"/>
       <c r="I29" s="463" t="n"/>
       <c r="J29" s="463" t="n"/>
-      <c r="K29" s="463" t="n"/>
-      <c r="L29" s="463" t="n"/>
+      <c r="K29" s="464" t="n"/>
+      <c r="L29" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M29" s="463" t="n"/>
       <c r="N29" s="463" t="n"/>
       <c r="O29" s="463" t="n"/>
@@ -10294,19 +10499,23 @@
       <c r="H30" s="463" t="n"/>
       <c r="I30" s="463" t="n"/>
       <c r="J30" s="463" t="n"/>
-      <c r="K30" s="463" t="n"/>
-      <c r="L30" s="463" t="n"/>
-      <c r="M30" s="463" t="n"/>
-      <c r="N30" s="463" t="n"/>
-      <c r="O30" s="463" t="n"/>
-      <c r="P30" s="463" t="n"/>
-      <c r="Q30" s="463" t="n"/>
-      <c r="R30" s="463" t="n"/>
-      <c r="S30" s="463" t="n"/>
-      <c r="T30" s="463" t="n"/>
-      <c r="U30" s="463" t="n"/>
-      <c r="V30" s="463" t="n"/>
-      <c r="W30" s="464" t="n"/>
+      <c r="K30" s="464" t="n"/>
+      <c r="L30" s="466" t="inlineStr">
+        <is>
+          <t>root直接ログインを避け、sudoによる操作履歴を残すことで運用の監査性を確保するため。</t>
+        </is>
+      </c>
+      <c r="M30" s="467" t="n"/>
+      <c r="N30" s="467" t="n"/>
+      <c r="O30" s="467" t="n"/>
+      <c r="P30" s="467" t="n"/>
+      <c r="Q30" s="467" t="n"/>
+      <c r="R30" s="467" t="n"/>
+      <c r="S30" s="467" t="n"/>
+      <c r="T30" s="467" t="n"/>
+      <c r="U30" s="467" t="n"/>
+      <c r="V30" s="467" t="n"/>
+      <c r="W30" s="468" t="n"/>
       <c r="X30" s="465" t="inlineStr">
         <is>
           <t>※要決定</t>
@@ -10345,7 +10554,7 @@
       <c r="AU30" s="463" t="n"/>
       <c r="AV30" s="464" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="29" customHeight="1" s="412">
       <c r="B31" s="465" t="inlineStr">
         <is>
           <t>rootログイン</t>
@@ -10359,19 +10568,23 @@
       <c r="H31" s="463" t="n"/>
       <c r="I31" s="463" t="n"/>
       <c r="J31" s="463" t="n"/>
-      <c r="K31" s="463" t="n"/>
-      <c r="L31" s="463" t="n"/>
-      <c r="M31" s="463" t="n"/>
-      <c r="N31" s="463" t="n"/>
-      <c r="O31" s="463" t="n"/>
-      <c r="P31" s="463" t="n"/>
-      <c r="Q31" s="463" t="n"/>
-      <c r="R31" s="463" t="n"/>
-      <c r="S31" s="463" t="n"/>
-      <c r="T31" s="463" t="n"/>
-      <c r="U31" s="463" t="n"/>
-      <c r="V31" s="463" t="n"/>
-      <c r="W31" s="464" t="n"/>
+      <c r="K31" s="464" t="n"/>
+      <c r="L31" s="466" t="inlineStr">
+        <is>
+          <t>直接rootでの操作を防ぎ、意図しない誤操作・セキュリティリスクを低減するため。</t>
+        </is>
+      </c>
+      <c r="M31" s="467" t="n"/>
+      <c r="N31" s="467" t="n"/>
+      <c r="O31" s="467" t="n"/>
+      <c r="P31" s="467" t="n"/>
+      <c r="Q31" s="467" t="n"/>
+      <c r="R31" s="467" t="n"/>
+      <c r="S31" s="467" t="n"/>
+      <c r="T31" s="467" t="n"/>
+      <c r="U31" s="467" t="n"/>
+      <c r="V31" s="467" t="n"/>
+      <c r="W31" s="468" t="n"/>
       <c r="X31" s="465" t="inlineStr">
         <is>
           <t>無効（sudo利用）</t>
@@ -10410,7 +10623,6 @@
       <c r="AU31" s="463" t="n"/>
       <c r="AV31" s="464" t="n"/>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="B33" s="461" t="inlineStr">
         <is>
@@ -10432,8 +10644,12 @@
       <c r="H34" s="463" t="n"/>
       <c r="I34" s="463" t="n"/>
       <c r="J34" s="463" t="n"/>
-      <c r="K34" s="463" t="n"/>
-      <c r="L34" s="463" t="n"/>
+      <c r="K34" s="464" t="n"/>
+      <c r="L34" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M34" s="463" t="n"/>
       <c r="N34" s="463" t="n"/>
       <c r="O34" s="463" t="n"/>
@@ -10483,7 +10699,7 @@
       <c r="AU34" s="463" t="n"/>
       <c r="AV34" s="464" t="n"/>
     </row>
-    <row r="35" ht="29" customHeight="1" s="412">
+    <row r="35" ht="72.5" customHeight="1" s="412">
       <c r="B35" s="465" t="inlineStr">
         <is>
           <t>ファイアーウォール（ufw）</t>
@@ -10497,19 +10713,23 @@
       <c r="H35" s="463" t="n"/>
       <c r="I35" s="463" t="n"/>
       <c r="J35" s="463" t="n"/>
-      <c r="K35" s="463" t="n"/>
-      <c r="L35" s="463" t="n"/>
-      <c r="M35" s="463" t="n"/>
-      <c r="N35" s="463" t="n"/>
-      <c r="O35" s="463" t="n"/>
-      <c r="P35" s="463" t="n"/>
-      <c r="Q35" s="463" t="n"/>
-      <c r="R35" s="463" t="n"/>
-      <c r="S35" s="463" t="n"/>
-      <c r="T35" s="463" t="n"/>
-      <c r="U35" s="463" t="n"/>
-      <c r="V35" s="463" t="n"/>
-      <c r="W35" s="464" t="n"/>
+      <c r="K35" s="464" t="n"/>
+      <c r="L35" s="466" t="inlineStr">
+        <is>
+          <t>Kubernetes/CNI（Calico）はPod間通信制御のため独自にiptables/nftablesルールを動的に書き換える。ufwが同時に稼働するとルールが競合しPod通信が意図せず遮断されるおそれがあるため無効化する。</t>
+        </is>
+      </c>
+      <c r="M35" s="467" t="n"/>
+      <c r="N35" s="467" t="n"/>
+      <c r="O35" s="467" t="n"/>
+      <c r="P35" s="467" t="n"/>
+      <c r="Q35" s="467" t="n"/>
+      <c r="R35" s="467" t="n"/>
+      <c r="S35" s="467" t="n"/>
+      <c r="T35" s="467" t="n"/>
+      <c r="U35" s="467" t="n"/>
+      <c r="V35" s="467" t="n"/>
+      <c r="W35" s="468" t="n"/>
       <c r="X35" s="465" t="inlineStr">
         <is>
           <t>□有効　■無効</t>
@@ -10548,7 +10768,7 @@
       <c r="AU35" s="463" t="n"/>
       <c r="AV35" s="464" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="43.5" customHeight="1" s="412">
       <c r="B36" s="465" t="inlineStr">
         <is>
           <t>AppArmor</t>
@@ -10562,19 +10782,23 @@
       <c r="H36" s="463" t="n"/>
       <c r="I36" s="463" t="n"/>
       <c r="J36" s="463" t="n"/>
-      <c r="K36" s="463" t="n"/>
-      <c r="L36" s="463" t="n"/>
-      <c r="M36" s="463" t="n"/>
-      <c r="N36" s="463" t="n"/>
-      <c r="O36" s="463" t="n"/>
-      <c r="P36" s="463" t="n"/>
-      <c r="Q36" s="463" t="n"/>
-      <c r="R36" s="463" t="n"/>
-      <c r="S36" s="463" t="n"/>
-      <c r="T36" s="463" t="n"/>
-      <c r="U36" s="463" t="n"/>
-      <c r="V36" s="463" t="n"/>
-      <c r="W36" s="464" t="n"/>
+      <c r="K36" s="464" t="n"/>
+      <c r="L36" s="466" t="inlineStr">
+        <is>
+          <t>Ubuntu既定のセキュリティ機構であり、Kubernetesの動作に支障が無いためデフォルト維持する。</t>
+        </is>
+      </c>
+      <c r="M36" s="467" t="n"/>
+      <c r="N36" s="467" t="n"/>
+      <c r="O36" s="467" t="n"/>
+      <c r="P36" s="467" t="n"/>
+      <c r="Q36" s="467" t="n"/>
+      <c r="R36" s="467" t="n"/>
+      <c r="S36" s="467" t="n"/>
+      <c r="T36" s="467" t="n"/>
+      <c r="U36" s="467" t="n"/>
+      <c r="V36" s="467" t="n"/>
+      <c r="W36" s="468" t="n"/>
       <c r="X36" s="465" t="inlineStr">
         <is>
           <t>■有効　□無効</t>
@@ -10613,7 +10837,6 @@
       <c r="AU36" s="463" t="n"/>
       <c r="AV36" s="464" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="B38" s="461" t="inlineStr">
         <is>
@@ -10635,8 +10858,12 @@
       <c r="H39" s="463" t="n"/>
       <c r="I39" s="463" t="n"/>
       <c r="J39" s="463" t="n"/>
-      <c r="K39" s="463" t="n"/>
-      <c r="L39" s="463" t="n"/>
+      <c r="K39" s="464" t="n"/>
+      <c r="L39" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M39" s="463" t="n"/>
       <c r="N39" s="463" t="n"/>
       <c r="O39" s="463" t="n"/>
@@ -10700,19 +10927,23 @@
       <c r="H40" s="463" t="n"/>
       <c r="I40" s="463" t="n"/>
       <c r="J40" s="463" t="n"/>
-      <c r="K40" s="463" t="n"/>
-      <c r="L40" s="463" t="n"/>
-      <c r="M40" s="463" t="n"/>
-      <c r="N40" s="463" t="n"/>
-      <c r="O40" s="463" t="n"/>
-      <c r="P40" s="463" t="n"/>
-      <c r="Q40" s="463" t="n"/>
-      <c r="R40" s="463" t="n"/>
-      <c r="S40" s="463" t="n"/>
-      <c r="T40" s="463" t="n"/>
-      <c r="U40" s="463" t="n"/>
-      <c r="V40" s="463" t="n"/>
-      <c r="W40" s="464" t="n"/>
+      <c r="K40" s="464" t="n"/>
+      <c r="L40" s="466" t="inlineStr">
+        <is>
+          <t>etcdの分散合意やTLS証明書の有効期限検証はノード間の時刻同期を前提とするため。</t>
+        </is>
+      </c>
+      <c r="M40" s="467" t="n"/>
+      <c r="N40" s="467" t="n"/>
+      <c r="O40" s="467" t="n"/>
+      <c r="P40" s="467" t="n"/>
+      <c r="Q40" s="467" t="n"/>
+      <c r="R40" s="467" t="n"/>
+      <c r="S40" s="467" t="n"/>
+      <c r="T40" s="467" t="n"/>
+      <c r="U40" s="467" t="n"/>
+      <c r="V40" s="467" t="n"/>
+      <c r="W40" s="468" t="n"/>
       <c r="X40" s="465" t="inlineStr">
         <is>
           <t>※要決定（NTPサーバー）</t>
@@ -10751,7 +10982,6 @@
       <c r="AU40" s="463" t="n"/>
       <c r="AV40" s="464" t="n"/>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="B42" s="461" t="inlineStr">
         <is>
@@ -10773,8 +11003,12 @@
       <c r="H43" s="463" t="n"/>
       <c r="I43" s="463" t="n"/>
       <c r="J43" s="463" t="n"/>
-      <c r="K43" s="463" t="n"/>
-      <c r="L43" s="463" t="n"/>
+      <c r="K43" s="464" t="n"/>
+      <c r="L43" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M43" s="463" t="n"/>
       <c r="N43" s="463" t="n"/>
       <c r="O43" s="463" t="n"/>
@@ -10838,19 +11072,23 @@
       <c r="H44" s="463" t="n"/>
       <c r="I44" s="463" t="n"/>
       <c r="J44" s="463" t="n"/>
-      <c r="K44" s="463" t="n"/>
-      <c r="L44" s="463" t="n"/>
-      <c r="M44" s="463" t="n"/>
-      <c r="N44" s="463" t="n"/>
-      <c r="O44" s="463" t="n"/>
-      <c r="P44" s="463" t="n"/>
-      <c r="Q44" s="463" t="n"/>
-      <c r="R44" s="463" t="n"/>
-      <c r="S44" s="463" t="n"/>
-      <c r="T44" s="463" t="n"/>
-      <c r="U44" s="463" t="n"/>
-      <c r="V44" s="463" t="n"/>
-      <c r="W44" s="464" t="n"/>
+      <c r="K44" s="464" t="n"/>
+      <c r="L44" s="466" t="inlineStr">
+        <is>
+          <t>既知の脆弱性を放置しないよう、セキュリティパッチのみ自動適用するため。</t>
+        </is>
+      </c>
+      <c r="M44" s="467" t="n"/>
+      <c r="N44" s="467" t="n"/>
+      <c r="O44" s="467" t="n"/>
+      <c r="P44" s="467" t="n"/>
+      <c r="Q44" s="467" t="n"/>
+      <c r="R44" s="467" t="n"/>
+      <c r="S44" s="467" t="n"/>
+      <c r="T44" s="467" t="n"/>
+      <c r="U44" s="467" t="n"/>
+      <c r="V44" s="467" t="n"/>
+      <c r="W44" s="468" t="n"/>
       <c r="X44" s="465" t="inlineStr">
         <is>
           <t>■有効（securityのみ）　□無効</t>
@@ -10889,7 +11127,7 @@
       <c r="AU44" s="463" t="n"/>
       <c r="AV44" s="464" t="n"/>
     </row>
-    <row r="45" ht="29" customHeight="1" s="412">
+    <row r="45" ht="58" customHeight="1" s="412">
       <c r="B45" s="465" t="inlineStr">
         <is>
           <t>自動再起動（Automatic-Reboot）</t>
@@ -10903,19 +11141,23 @@
       <c r="H45" s="463" t="n"/>
       <c r="I45" s="463" t="n"/>
       <c r="J45" s="463" t="n"/>
-      <c r="K45" s="463" t="n"/>
-      <c r="L45" s="463" t="n"/>
-      <c r="M45" s="463" t="n"/>
-      <c r="N45" s="463" t="n"/>
-      <c r="O45" s="463" t="n"/>
-      <c r="P45" s="463" t="n"/>
-      <c r="Q45" s="463" t="n"/>
-      <c r="R45" s="463" t="n"/>
-      <c r="S45" s="463" t="n"/>
-      <c r="T45" s="463" t="n"/>
-      <c r="U45" s="463" t="n"/>
-      <c r="V45" s="463" t="n"/>
-      <c r="W45" s="464" t="n"/>
+      <c r="K45" s="464" t="n"/>
+      <c r="L45" s="466" t="inlineStr">
+        <is>
+          <t>自動再起動が可用性設計外で突発的に発生すると、業務Podへ計画外の影響が生じるため、再起動はcordon/drainを伴う計画作業としてのみ実施する。</t>
+        </is>
+      </c>
+      <c r="M45" s="467" t="n"/>
+      <c r="N45" s="467" t="n"/>
+      <c r="O45" s="467" t="n"/>
+      <c r="P45" s="467" t="n"/>
+      <c r="Q45" s="467" t="n"/>
+      <c r="R45" s="467" t="n"/>
+      <c r="S45" s="467" t="n"/>
+      <c r="T45" s="467" t="n"/>
+      <c r="U45" s="467" t="n"/>
+      <c r="V45" s="467" t="n"/>
+      <c r="W45" s="468" t="n"/>
       <c r="X45" s="465" t="inlineStr">
         <is>
           <t>□有効　■無効</t>
@@ -10954,7 +11196,6 @@
       <c r="AU45" s="463" t="n"/>
       <c r="AV45" s="464" t="n"/>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="B47" s="461" t="inlineStr">
         <is>
@@ -10976,8 +11217,12 @@
       <c r="H48" s="463" t="n"/>
       <c r="I48" s="463" t="n"/>
       <c r="J48" s="463" t="n"/>
-      <c r="K48" s="463" t="n"/>
-      <c r="L48" s="463" t="n"/>
+      <c r="K48" s="464" t="n"/>
+      <c r="L48" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M48" s="463" t="n"/>
       <c r="N48" s="463" t="n"/>
       <c r="O48" s="463" t="n"/>
@@ -11027,7 +11272,7 @@
       <c r="AU48" s="463" t="n"/>
       <c r="AV48" s="464" t="n"/>
     </row>
-    <row r="49" ht="29" customHeight="1" s="412">
+    <row r="49" ht="58" customHeight="1" s="412">
       <c r="B49" s="465" t="inlineStr">
         <is>
           <t>カーネルモジュール /etc/modules-load.d/k8s.conf</t>
@@ -11041,19 +11286,23 @@
       <c r="H49" s="463" t="n"/>
       <c r="I49" s="463" t="n"/>
       <c r="J49" s="463" t="n"/>
-      <c r="K49" s="463" t="n"/>
-      <c r="L49" s="463" t="n"/>
-      <c r="M49" s="463" t="n"/>
-      <c r="N49" s="463" t="n"/>
-      <c r="O49" s="463" t="n"/>
-      <c r="P49" s="463" t="n"/>
-      <c r="Q49" s="463" t="n"/>
-      <c r="R49" s="463" t="n"/>
-      <c r="S49" s="463" t="n"/>
-      <c r="T49" s="463" t="n"/>
-      <c r="U49" s="463" t="n"/>
-      <c r="V49" s="463" t="n"/>
-      <c r="W49" s="464" t="n"/>
+      <c r="K49" s="464" t="n"/>
+      <c r="L49" s="466" t="inlineStr">
+        <is>
+          <t>overlayはcontainerdが使用するオーバーレイファイルシステムに、br_netfilterはブリッジ経由パケットのiptables制御に、それぞれ必須となるカーネル機能のため。</t>
+        </is>
+      </c>
+      <c r="M49" s="467" t="n"/>
+      <c r="N49" s="467" t="n"/>
+      <c r="O49" s="467" t="n"/>
+      <c r="P49" s="467" t="n"/>
+      <c r="Q49" s="467" t="n"/>
+      <c r="R49" s="467" t="n"/>
+      <c r="S49" s="467" t="n"/>
+      <c r="T49" s="467" t="n"/>
+      <c r="U49" s="467" t="n"/>
+      <c r="V49" s="467" t="n"/>
+      <c r="W49" s="468" t="n"/>
       <c r="X49" s="465" t="inlineStr">
         <is>
           <t>overlay
@@ -11107,19 +11356,23 @@
       <c r="H50" s="463" t="n"/>
       <c r="I50" s="463" t="n"/>
       <c r="J50" s="463" t="n"/>
-      <c r="K50" s="463" t="n"/>
-      <c r="L50" s="463" t="n"/>
-      <c r="M50" s="463" t="n"/>
-      <c r="N50" s="463" t="n"/>
-      <c r="O50" s="463" t="n"/>
-      <c r="P50" s="463" t="n"/>
-      <c r="Q50" s="463" t="n"/>
-      <c r="R50" s="463" t="n"/>
-      <c r="S50" s="463" t="n"/>
-      <c r="T50" s="463" t="n"/>
-      <c r="U50" s="463" t="n"/>
-      <c r="V50" s="463" t="n"/>
-      <c r="W50" s="464" t="n"/>
+      <c r="K50" s="464" t="n"/>
+      <c r="L50" s="466" t="inlineStr">
+        <is>
+          <t>ip_forwardを有効化しないとノードがルーターとして機能せず、Pod宛通信の転送ができない。bridge-nf-call-iptablesは、CNIが設定するiptablesルールをブリッジ通信にも適用させるための必須設定。</t>
+        </is>
+      </c>
+      <c r="M50" s="467" t="n"/>
+      <c r="N50" s="467" t="n"/>
+      <c r="O50" s="467" t="n"/>
+      <c r="P50" s="467" t="n"/>
+      <c r="Q50" s="467" t="n"/>
+      <c r="R50" s="467" t="n"/>
+      <c r="S50" s="467" t="n"/>
+      <c r="T50" s="467" t="n"/>
+      <c r="U50" s="467" t="n"/>
+      <c r="V50" s="467" t="n"/>
+      <c r="W50" s="468" t="n"/>
       <c r="X50" s="465" t="inlineStr">
         <is>
           <t>net.bridge.bridge-nf-call-iptables=1
@@ -11174,19 +11427,23 @@
       <c r="H51" s="463" t="n"/>
       <c r="I51" s="463" t="n"/>
       <c r="J51" s="463" t="n"/>
-      <c r="K51" s="463" t="n"/>
-      <c r="L51" s="463" t="n"/>
-      <c r="M51" s="463" t="n"/>
-      <c r="N51" s="463" t="n"/>
-      <c r="O51" s="463" t="n"/>
-      <c r="P51" s="463" t="n"/>
-      <c r="Q51" s="463" t="n"/>
-      <c r="R51" s="463" t="n"/>
-      <c r="S51" s="463" t="n"/>
-      <c r="T51" s="463" t="n"/>
-      <c r="U51" s="463" t="n"/>
-      <c r="V51" s="463" t="n"/>
-      <c r="W51" s="464" t="n"/>
+      <c r="K51" s="464" t="n"/>
+      <c r="L51" s="466" t="inlineStr">
+        <is>
+          <t>kubeletはswapが有効なノードでは起動しない（Kubernetesの既定要件）ため。</t>
+        </is>
+      </c>
+      <c r="M51" s="467" t="n"/>
+      <c r="N51" s="467" t="n"/>
+      <c r="O51" s="467" t="n"/>
+      <c r="P51" s="467" t="n"/>
+      <c r="Q51" s="467" t="n"/>
+      <c r="R51" s="467" t="n"/>
+      <c r="S51" s="467" t="n"/>
+      <c r="T51" s="467" t="n"/>
+      <c r="U51" s="467" t="n"/>
+      <c r="V51" s="467" t="n"/>
+      <c r="W51" s="468" t="n"/>
       <c r="X51" s="465" t="inlineStr">
         <is>
           <t>swapoff -a 実施、/etc/fstabのswap行削除</t>
@@ -11225,7 +11482,7 @@
       <c r="AU51" s="463" t="n"/>
       <c r="AV51" s="464" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="43.5" customHeight="1" s="412">
       <c r="B52" s="465" t="inlineStr">
         <is>
           <t>cgroup バージョン</t>
@@ -11239,19 +11496,23 @@
       <c r="H52" s="463" t="n"/>
       <c r="I52" s="463" t="n"/>
       <c r="J52" s="463" t="n"/>
-      <c r="K52" s="463" t="n"/>
-      <c r="L52" s="463" t="n"/>
-      <c r="M52" s="463" t="n"/>
-      <c r="N52" s="463" t="n"/>
-      <c r="O52" s="463" t="n"/>
-      <c r="P52" s="463" t="n"/>
-      <c r="Q52" s="463" t="n"/>
-      <c r="R52" s="463" t="n"/>
-      <c r="S52" s="463" t="n"/>
-      <c r="T52" s="463" t="n"/>
-      <c r="U52" s="463" t="n"/>
-      <c r="V52" s="463" t="n"/>
-      <c r="W52" s="464" t="n"/>
+      <c r="K52" s="464" t="n"/>
+      <c r="L52" s="466" t="inlineStr">
+        <is>
+          <t>kubelet/containerdのリソース管理はcgroup v2を前提として設計されているため。</t>
+        </is>
+      </c>
+      <c r="M52" s="467" t="n"/>
+      <c r="N52" s="467" t="n"/>
+      <c r="O52" s="467" t="n"/>
+      <c r="P52" s="467" t="n"/>
+      <c r="Q52" s="467" t="n"/>
+      <c r="R52" s="467" t="n"/>
+      <c r="S52" s="467" t="n"/>
+      <c r="T52" s="467" t="n"/>
+      <c r="U52" s="467" t="n"/>
+      <c r="V52" s="467" t="n"/>
+      <c r="W52" s="468" t="n"/>
       <c r="X52" s="465" t="inlineStr">
         <is>
           <t>v2（デフォルト維持）</t>
@@ -11290,7 +11551,6 @@
       <c r="AU52" s="463" t="n"/>
       <c r="AV52" s="464" t="n"/>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="B54" s="461" t="inlineStr">
         <is>
@@ -11312,8 +11572,12 @@
       <c r="H55" s="463" t="n"/>
       <c r="I55" s="463" t="n"/>
       <c r="J55" s="463" t="n"/>
-      <c r="K55" s="463" t="n"/>
-      <c r="L55" s="463" t="n"/>
+      <c r="K55" s="464" t="n"/>
+      <c r="L55" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M55" s="463" t="n"/>
       <c r="N55" s="463" t="n"/>
       <c r="O55" s="463" t="n"/>
@@ -11363,7 +11627,7 @@
       <c r="AU55" s="463" t="n"/>
       <c r="AV55" s="464" t="n"/>
     </row>
-    <row r="56" ht="29" customHeight="1" s="412">
+    <row r="56" ht="58" customHeight="1" s="412">
       <c r="B56" s="465" t="inlineStr">
         <is>
           <t>Kubernetes（kubeadm/kubelet/kubectl）</t>
@@ -11377,19 +11641,23 @@
       <c r="H56" s="463" t="n"/>
       <c r="I56" s="463" t="n"/>
       <c r="J56" s="463" t="n"/>
-      <c r="K56" s="463" t="n"/>
-      <c r="L56" s="463" t="n"/>
-      <c r="M56" s="463" t="n"/>
-      <c r="N56" s="463" t="n"/>
-      <c r="O56" s="463" t="n"/>
-      <c r="P56" s="463" t="n"/>
-      <c r="Q56" s="463" t="n"/>
-      <c r="R56" s="463" t="n"/>
-      <c r="S56" s="463" t="n"/>
-      <c r="T56" s="463" t="n"/>
-      <c r="U56" s="463" t="n"/>
-      <c r="V56" s="463" t="n"/>
-      <c r="W56" s="464" t="n"/>
+      <c r="K56" s="464" t="n"/>
+      <c r="L56" s="466" t="inlineStr">
+        <is>
+          <t>クラスタを構築・操作する本体コンポーネント。apt-mark holdでバージョンを固定するのは、自動更新によりノード間でバージョンがばらつき、互換性問題が生じるのを防ぐため。</t>
+        </is>
+      </c>
+      <c r="M56" s="467" t="n"/>
+      <c r="N56" s="467" t="n"/>
+      <c r="O56" s="467" t="n"/>
+      <c r="P56" s="467" t="n"/>
+      <c r="Q56" s="467" t="n"/>
+      <c r="R56" s="467" t="n"/>
+      <c r="S56" s="467" t="n"/>
+      <c r="T56" s="467" t="n"/>
+      <c r="U56" s="467" t="n"/>
+      <c r="V56" s="467" t="n"/>
+      <c r="W56" s="468" t="n"/>
       <c r="X56" s="465" t="inlineStr">
         <is>
           <t>v1.35.x（pkgs.k8s.ioリポジトリ）</t>
@@ -11428,7 +11696,7 @@
       <c r="AU56" s="463" t="n"/>
       <c r="AV56" s="464" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="43.5" customHeight="1" s="412">
       <c r="B57" s="465" t="inlineStr">
         <is>
           <t>containerd</t>
@@ -11442,19 +11710,23 @@
       <c r="H57" s="463" t="n"/>
       <c r="I57" s="463" t="n"/>
       <c r="J57" s="463" t="n"/>
-      <c r="K57" s="463" t="n"/>
-      <c r="L57" s="463" t="n"/>
-      <c r="M57" s="463" t="n"/>
-      <c r="N57" s="463" t="n"/>
-      <c r="O57" s="463" t="n"/>
-      <c r="P57" s="463" t="n"/>
-      <c r="Q57" s="463" t="n"/>
-      <c r="R57" s="463" t="n"/>
-      <c r="S57" s="463" t="n"/>
-      <c r="T57" s="463" t="n"/>
-      <c r="U57" s="463" t="n"/>
-      <c r="V57" s="463" t="n"/>
-      <c r="W57" s="464" t="n"/>
+      <c r="K57" s="464" t="n"/>
+      <c r="L57" s="466" t="inlineStr">
+        <is>
+          <t>kubeletが唯一サポートするCRI（Container Runtime Interface）実装として採用。</t>
+        </is>
+      </c>
+      <c r="M57" s="467" t="n"/>
+      <c r="N57" s="467" t="n"/>
+      <c r="O57" s="467" t="n"/>
+      <c r="P57" s="467" t="n"/>
+      <c r="Q57" s="467" t="n"/>
+      <c r="R57" s="467" t="n"/>
+      <c r="S57" s="467" t="n"/>
+      <c r="T57" s="467" t="n"/>
+      <c r="U57" s="467" t="n"/>
+      <c r="V57" s="467" t="n"/>
+      <c r="W57" s="468" t="n"/>
       <c r="X57" s="465" t="inlineStr">
         <is>
           <t>2.x</t>
@@ -11493,7 +11765,7 @@
       <c r="AU57" s="463" t="n"/>
       <c r="AV57" s="464" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="58" customHeight="1" s="412">
       <c r="B58" s="465" t="inlineStr">
         <is>
           <t>Helm</t>
@@ -11507,19 +11779,23 @@
       <c r="H58" s="463" t="n"/>
       <c r="I58" s="463" t="n"/>
       <c r="J58" s="463" t="n"/>
-      <c r="K58" s="463" t="n"/>
-      <c r="L58" s="463" t="n"/>
-      <c r="M58" s="463" t="n"/>
-      <c r="N58" s="463" t="n"/>
-      <c r="O58" s="463" t="n"/>
-      <c r="P58" s="463" t="n"/>
-      <c r="Q58" s="463" t="n"/>
-      <c r="R58" s="463" t="n"/>
-      <c r="S58" s="463" t="n"/>
-      <c r="T58" s="463" t="n"/>
-      <c r="U58" s="463" t="n"/>
-      <c r="V58" s="463" t="n"/>
-      <c r="W58" s="464" t="n"/>
+      <c r="K58" s="464" t="n"/>
+      <c r="L58" s="466" t="inlineStr">
+        <is>
+          <t>監視スタック（kube-prometheus-stack）やCSI（NetApp Trident）等、本設計で採用するソフトウェアの多くがHelm Chartとして配布されているため。</t>
+        </is>
+      </c>
+      <c r="M58" s="467" t="n"/>
+      <c r="N58" s="467" t="n"/>
+      <c r="O58" s="467" t="n"/>
+      <c r="P58" s="467" t="n"/>
+      <c r="Q58" s="467" t="n"/>
+      <c r="R58" s="467" t="n"/>
+      <c r="S58" s="467" t="n"/>
+      <c r="T58" s="467" t="n"/>
+      <c r="U58" s="467" t="n"/>
+      <c r="V58" s="467" t="n"/>
+      <c r="W58" s="468" t="n"/>
       <c r="X58" s="465" t="inlineStr">
         <is>
           <t>v4.2.x</t>
@@ -11558,7 +11834,7 @@
       <c r="AU58" s="463" t="n"/>
       <c r="AV58" s="464" t="n"/>
     </row>
-    <row r="59" ht="29" customHeight="1" s="412">
+    <row r="59" ht="72.5" customHeight="1" s="412">
       <c r="B59" s="465" t="inlineStr">
         <is>
           <t>nfs-common</t>
@@ -11572,19 +11848,23 @@
       <c r="H59" s="463" t="n"/>
       <c r="I59" s="463" t="n"/>
       <c r="J59" s="463" t="n"/>
-      <c r="K59" s="463" t="n"/>
-      <c r="L59" s="463" t="n"/>
-      <c r="M59" s="463" t="n"/>
-      <c r="N59" s="463" t="n"/>
-      <c r="O59" s="463" t="n"/>
-      <c r="P59" s="463" t="n"/>
-      <c r="Q59" s="463" t="n"/>
-      <c r="R59" s="463" t="n"/>
-      <c r="S59" s="463" t="n"/>
-      <c r="T59" s="463" t="n"/>
-      <c r="U59" s="463" t="n"/>
-      <c r="V59" s="463" t="n"/>
-      <c r="W59" s="464" t="n"/>
+      <c r="K59" s="464" t="n"/>
+      <c r="L59" s="466" t="inlineStr">
+        <is>
+          <t>NetApp Trident（NFSバックエンド）はOS側のNFSクライアント機能を利用してボリュームをマウントするため、事前導入が無いとPersistentVolumeのマウントに失敗する。</t>
+        </is>
+      </c>
+      <c r="M59" s="467" t="n"/>
+      <c r="N59" s="467" t="n"/>
+      <c r="O59" s="467" t="n"/>
+      <c r="P59" s="467" t="n"/>
+      <c r="Q59" s="467" t="n"/>
+      <c r="R59" s="467" t="n"/>
+      <c r="S59" s="467" t="n"/>
+      <c r="T59" s="467" t="n"/>
+      <c r="U59" s="467" t="n"/>
+      <c r="V59" s="467" t="n"/>
+      <c r="W59" s="468" t="n"/>
       <c r="X59" s="465" t="inlineStr">
         <is>
           <t>導入する</t>
@@ -11623,7 +11903,7 @@
       <c r="AU59" s="463" t="n"/>
       <c r="AV59" s="464" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="72.5" customHeight="1" s="412">
       <c r="B60" s="465" t="inlineStr">
         <is>
           <t>NVIDIA Driver / Container Toolkit（Workerのみ）</t>
@@ -11637,19 +11917,23 @@
       <c r="H60" s="463" t="n"/>
       <c r="I60" s="463" t="n"/>
       <c r="J60" s="463" t="n"/>
-      <c r="K60" s="463" t="n"/>
-      <c r="L60" s="463" t="n"/>
-      <c r="M60" s="463" t="n"/>
-      <c r="N60" s="463" t="n"/>
-      <c r="O60" s="463" t="n"/>
-      <c r="P60" s="463" t="n"/>
-      <c r="Q60" s="463" t="n"/>
-      <c r="R60" s="463" t="n"/>
-      <c r="S60" s="463" t="n"/>
-      <c r="T60" s="463" t="n"/>
-      <c r="U60" s="463" t="n"/>
-      <c r="V60" s="463" t="n"/>
-      <c r="W60" s="464" t="n"/>
+      <c r="K60" s="464" t="n"/>
+      <c r="L60" s="466" t="inlineStr">
+        <is>
+          <t>GPUをOS・コンテナ双方から認識・利用可能にするための必須コンポーネント。Driverが無いとOSレベルでGPUを認識できず、Container Toolkitが無いとPodからGPUへアクセスできない。</t>
+        </is>
+      </c>
+      <c r="M60" s="467" t="n"/>
+      <c r="N60" s="467" t="n"/>
+      <c r="O60" s="467" t="n"/>
+      <c r="P60" s="467" t="n"/>
+      <c r="Q60" s="467" t="n"/>
+      <c r="R60" s="467" t="n"/>
+      <c r="S60" s="467" t="n"/>
+      <c r="T60" s="467" t="n"/>
+      <c r="U60" s="467" t="n"/>
+      <c r="V60" s="467" t="n"/>
+      <c r="W60" s="468" t="n"/>
       <c r="X60" s="465" t="inlineStr">
         <is>
           <t>構築時最新の推奨版</t>
@@ -11696,85 +11980,105 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="466" t="inlineStr">
+      <c r="B63" s="469" t="inlineStr">
         <is>
           <t>パスワード・秘密鍵・トークン等の認証情報は本書に記載しない。別途パスワード管理台帳で管理する。</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="466" t="inlineStr">
+      <c r="B64" s="469" t="inlineStr">
         <is>
           <t>「※要決定」の項目はPoC構築開始前に確定させ、本書を更新すること。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="153">
-    <mergeCell ref="B10:W10"/>
+  <mergeCells count="190">
     <mergeCell ref="AE19:AK19"/>
     <mergeCell ref="AL34:AV34"/>
     <mergeCell ref="AL9:AV9"/>
+    <mergeCell ref="B30:K30"/>
+    <mergeCell ref="AE9:AK9"/>
     <mergeCell ref="AE34:AK34"/>
-    <mergeCell ref="AE9:AK9"/>
-    <mergeCell ref="B9:W9"/>
+    <mergeCell ref="L35:W35"/>
     <mergeCell ref="AL36:AV36"/>
+    <mergeCell ref="AL11:AV11"/>
     <mergeCell ref="AE49:AK49"/>
-    <mergeCell ref="AL11:AV11"/>
     <mergeCell ref="AE36:AK36"/>
-    <mergeCell ref="B36:W36"/>
     <mergeCell ref="AE45:AK45"/>
-    <mergeCell ref="B45:W45"/>
+    <mergeCell ref="L25:W25"/>
     <mergeCell ref="X56:AD56"/>
     <mergeCell ref="AE51:AK51"/>
     <mergeCell ref="X43:AD43"/>
+    <mergeCell ref="L60:W60"/>
+    <mergeCell ref="C17:K17"/>
     <mergeCell ref="X40:AD40"/>
+    <mergeCell ref="L22:W22"/>
     <mergeCell ref="AE50:AK50"/>
     <mergeCell ref="AE59:AK59"/>
     <mergeCell ref="AE22:AK22"/>
-    <mergeCell ref="B59:W59"/>
+    <mergeCell ref="L59:W59"/>
     <mergeCell ref="X8:AD8"/>
+    <mergeCell ref="C19:K19"/>
     <mergeCell ref="AE31:AK31"/>
     <mergeCell ref="X17:AD17"/>
-    <mergeCell ref="B31:W31"/>
+    <mergeCell ref="B56:K56"/>
+    <mergeCell ref="B43:K43"/>
     <mergeCell ref="AE5:AV5"/>
-    <mergeCell ref="C18:W18"/>
-    <mergeCell ref="B39:W39"/>
     <mergeCell ref="AL14:AV14"/>
     <mergeCell ref="X19:AD19"/>
-    <mergeCell ref="B48:W48"/>
+    <mergeCell ref="L48:W48"/>
     <mergeCell ref="AL23:AV23"/>
     <mergeCell ref="AE14:AK14"/>
-    <mergeCell ref="B14:W14"/>
+    <mergeCell ref="B8:K8"/>
     <mergeCell ref="AE23:AK23"/>
     <mergeCell ref="AL55:AV55"/>
-    <mergeCell ref="B23:W23"/>
     <mergeCell ref="AL51:AV51"/>
     <mergeCell ref="AL48:AV48"/>
+    <mergeCell ref="B10:K10"/>
     <mergeCell ref="X58:AD58"/>
     <mergeCell ref="X5:AD5"/>
     <mergeCell ref="AE48:AK48"/>
+    <mergeCell ref="L43:W43"/>
     <mergeCell ref="X45:AD45"/>
+    <mergeCell ref="L15:W15"/>
+    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="L24:W24"/>
     <mergeCell ref="X60:AD60"/>
-    <mergeCell ref="B49:W49"/>
+    <mergeCell ref="L18:W18"/>
+    <mergeCell ref="L8:W8"/>
     <mergeCell ref="X44:AD44"/>
+    <mergeCell ref="B36:K36"/>
+    <mergeCell ref="L26:W26"/>
     <mergeCell ref="AL49:AV49"/>
+    <mergeCell ref="X29:AD29"/>
+    <mergeCell ref="B45:K45"/>
+    <mergeCell ref="X31:AD31"/>
     <mergeCell ref="X59:AD59"/>
-    <mergeCell ref="B51:W51"/>
-    <mergeCell ref="X31:AD31"/>
-    <mergeCell ref="B35:W35"/>
-    <mergeCell ref="B50:W50"/>
+    <mergeCell ref="L58:W58"/>
+    <mergeCell ref="L10:W10"/>
+    <mergeCell ref="L50:W50"/>
     <mergeCell ref="AL25:AV25"/>
     <mergeCell ref="X39:AD39"/>
     <mergeCell ref="I5:W5"/>
     <mergeCell ref="X48:AD48"/>
     <mergeCell ref="AE25:AK25"/>
-    <mergeCell ref="B25:W25"/>
+    <mergeCell ref="L34:W34"/>
+    <mergeCell ref="L9:W9"/>
+    <mergeCell ref="B59:K59"/>
+    <mergeCell ref="B31:K31"/>
+    <mergeCell ref="L52:W52"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="AE35:AK35"/>
-    <mergeCell ref="B22:W22"/>
+    <mergeCell ref="L36:W36"/>
+    <mergeCell ref="L11:W11"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="B39:K39"/>
     <mergeCell ref="X16:AD16"/>
+    <mergeCell ref="B48:K48"/>
     <mergeCell ref="AL52:AV52"/>
+    <mergeCell ref="B23:K23"/>
     <mergeCell ref="AL39:AV39"/>
     <mergeCell ref="AE52:AK52"/>
     <mergeCell ref="X18:AD18"/>
@@ -11782,87 +12086,104 @@
     <mergeCell ref="AE39:AK39"/>
     <mergeCell ref="AL29:AV29"/>
     <mergeCell ref="AE29:AK29"/>
-    <mergeCell ref="B29:W29"/>
     <mergeCell ref="AL44:AV44"/>
     <mergeCell ref="AL31:AV31"/>
+    <mergeCell ref="B49:K49"/>
     <mergeCell ref="AL40:AV40"/>
-    <mergeCell ref="C16:W16"/>
     <mergeCell ref="X50:AD50"/>
     <mergeCell ref="AE40:AK40"/>
+    <mergeCell ref="L14:W14"/>
+    <mergeCell ref="AL15:AV15"/>
     <mergeCell ref="X51:AD51"/>
-    <mergeCell ref="AL15:AV15"/>
-    <mergeCell ref="B40:W40"/>
+    <mergeCell ref="L23:W23"/>
     <mergeCell ref="AE15:AK15"/>
+    <mergeCell ref="B51:K51"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B15:W15"/>
     <mergeCell ref="AE24:AK24"/>
-    <mergeCell ref="B55:W55"/>
+    <mergeCell ref="L55:W55"/>
     <mergeCell ref="AE57:AK57"/>
-    <mergeCell ref="B24:W24"/>
     <mergeCell ref="AL50:AV50"/>
+    <mergeCell ref="L51:W51"/>
     <mergeCell ref="X22:AD22"/>
+    <mergeCell ref="B50:K50"/>
     <mergeCell ref="AL26:AV26"/>
     <mergeCell ref="X36:AD36"/>
     <mergeCell ref="AE26:AK26"/>
-    <mergeCell ref="B26:W26"/>
+    <mergeCell ref="B25:K25"/>
     <mergeCell ref="AL16:AV16"/>
     <mergeCell ref="AE16:AK16"/>
     <mergeCell ref="X52:AD52"/>
+    <mergeCell ref="L56:W56"/>
     <mergeCell ref="AL57:AV57"/>
     <mergeCell ref="B2:AV2"/>
+    <mergeCell ref="B22:K22"/>
     <mergeCell ref="AL18:AV18"/>
     <mergeCell ref="AE43:AK43"/>
     <mergeCell ref="AE18:AK18"/>
+    <mergeCell ref="L49:W49"/>
     <mergeCell ref="AE58:AK58"/>
-    <mergeCell ref="B58:W58"/>
-    <mergeCell ref="B52:W52"/>
+    <mergeCell ref="L17:W17"/>
     <mergeCell ref="AL43:AV43"/>
-    <mergeCell ref="B11:W11"/>
-    <mergeCell ref="B60:W60"/>
+    <mergeCell ref="B14:K14"/>
     <mergeCell ref="AL35:AV35"/>
-    <mergeCell ref="B57:W57"/>
+    <mergeCell ref="B29:K29"/>
     <mergeCell ref="X15:AD15"/>
+    <mergeCell ref="L19:W19"/>
     <mergeCell ref="AE44:AK44"/>
     <mergeCell ref="X55:AD55"/>
     <mergeCell ref="X24:AD24"/>
-    <mergeCell ref="B44:W44"/>
-    <mergeCell ref="B34:W34"/>
+    <mergeCell ref="C16:K16"/>
     <mergeCell ref="AL60:AV60"/>
     <mergeCell ref="AE60:AK60"/>
     <mergeCell ref="AL22:AV22"/>
+    <mergeCell ref="B40:K40"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="AL30:AV30"/>
     <mergeCell ref="X35:AD35"/>
+    <mergeCell ref="B15:K15"/>
     <mergeCell ref="AL59:AV59"/>
     <mergeCell ref="AE30:AK30"/>
+    <mergeCell ref="B55:K55"/>
+    <mergeCell ref="B24:K24"/>
     <mergeCell ref="X10:AD10"/>
-    <mergeCell ref="B30:W30"/>
+    <mergeCell ref="L30:W30"/>
+    <mergeCell ref="L39:W39"/>
+    <mergeCell ref="L45:W45"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="AE11:AK11"/>
+    <mergeCell ref="L29:W29"/>
     <mergeCell ref="X9:AD9"/>
+    <mergeCell ref="B26:K26"/>
     <mergeCell ref="AE55:AK55"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="L44:W44"/>
     <mergeCell ref="AL45:AV45"/>
+    <mergeCell ref="L31:W31"/>
+    <mergeCell ref="L40:W40"/>
     <mergeCell ref="X11:AD11"/>
-    <mergeCell ref="C17:W17"/>
     <mergeCell ref="X57:AD57"/>
     <mergeCell ref="AL56:AV56"/>
+    <mergeCell ref="B58:K58"/>
+    <mergeCell ref="B52:K52"/>
     <mergeCell ref="AE56:AK56"/>
-    <mergeCell ref="C19:W19"/>
-    <mergeCell ref="B56:W56"/>
     <mergeCell ref="AL24:AV24"/>
     <mergeCell ref="X34:AD34"/>
-    <mergeCell ref="B43:W43"/>
+    <mergeCell ref="B11:K11"/>
+    <mergeCell ref="B60:K60"/>
     <mergeCell ref="AL8:AV8"/>
+    <mergeCell ref="B57:K57"/>
+    <mergeCell ref="L16:W16"/>
     <mergeCell ref="AL17:AV17"/>
     <mergeCell ref="AE8:AK8"/>
-    <mergeCell ref="B8:W8"/>
     <mergeCell ref="AE17:AK17"/>
     <mergeCell ref="X30:AD30"/>
-    <mergeCell ref="AL19:AV19"/>
+    <mergeCell ref="B44:K44"/>
+    <mergeCell ref="L57:W57"/>
     <mergeCell ref="AL58:AV58"/>
+    <mergeCell ref="B34:K34"/>
     <mergeCell ref="AL10:AV10"/>
     <mergeCell ref="X14:AD14"/>
-    <mergeCell ref="X29:AD29"/>
+    <mergeCell ref="AL19:AV19"/>
     <mergeCell ref="AE10:AK10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11911,8 +12232,12 @@
       <c r="H6" s="463" t="n"/>
       <c r="I6" s="463" t="n"/>
       <c r="J6" s="463" t="n"/>
-      <c r="K6" s="463" t="n"/>
-      <c r="L6" s="463" t="n"/>
+      <c r="K6" s="464" t="n"/>
+      <c r="L6" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M6" s="463" t="n"/>
       <c r="N6" s="463" t="n"/>
       <c r="O6" s="463" t="n"/>
@@ -11958,7 +12283,7 @@
       <c r="AU6" s="463" t="n"/>
       <c r="AV6" s="464" t="n"/>
     </row>
-    <row r="7" ht="29" customHeight="1" s="412">
+    <row r="7" ht="43.5" customHeight="1" s="412">
       <c r="B7" s="465" t="inlineStr">
         <is>
           <t>Kubernetes</t>
@@ -11972,19 +12297,23 @@
       <c r="H7" s="463" t="n"/>
       <c r="I7" s="463" t="n"/>
       <c r="J7" s="463" t="n"/>
-      <c r="K7" s="463" t="n"/>
-      <c r="L7" s="463" t="n"/>
-      <c r="M7" s="463" t="n"/>
-      <c r="N7" s="463" t="n"/>
-      <c r="O7" s="463" t="n"/>
-      <c r="P7" s="463" t="n"/>
-      <c r="Q7" s="463" t="n"/>
-      <c r="R7" s="463" t="n"/>
-      <c r="S7" s="463" t="n"/>
-      <c r="T7" s="463" t="n"/>
-      <c r="U7" s="463" t="n"/>
-      <c r="V7" s="463" t="n"/>
-      <c r="W7" s="464" t="n"/>
+      <c r="K7" s="464" t="n"/>
+      <c r="L7" s="466" t="inlineStr">
+        <is>
+          <t>クラスタが動作するコアのバージョン。本パラメータシート全体の前提となる。</t>
+        </is>
+      </c>
+      <c r="M7" s="467" t="n"/>
+      <c r="N7" s="467" t="n"/>
+      <c r="O7" s="467" t="n"/>
+      <c r="P7" s="467" t="n"/>
+      <c r="Q7" s="467" t="n"/>
+      <c r="R7" s="467" t="n"/>
+      <c r="S7" s="467" t="n"/>
+      <c r="T7" s="467" t="n"/>
+      <c r="U7" s="467" t="n"/>
+      <c r="V7" s="467" t="n"/>
+      <c r="W7" s="468" t="n"/>
       <c r="X7" s="465" t="inlineStr">
         <is>
           <t>v1.35.x（コミュニティ版/kubeadm構築）</t>
@@ -12033,19 +12362,23 @@
       <c r="H8" s="463" t="n"/>
       <c r="I8" s="463" t="n"/>
       <c r="J8" s="463" t="n"/>
-      <c r="K8" s="463" t="n"/>
-      <c r="L8" s="463" t="n"/>
-      <c r="M8" s="463" t="n"/>
-      <c r="N8" s="463" t="n"/>
-      <c r="O8" s="463" t="n"/>
-      <c r="P8" s="463" t="n"/>
-      <c r="Q8" s="463" t="n"/>
-      <c r="R8" s="463" t="n"/>
-      <c r="S8" s="463" t="n"/>
-      <c r="T8" s="463" t="n"/>
-      <c r="U8" s="463" t="n"/>
-      <c r="V8" s="463" t="n"/>
-      <c r="W8" s="464" t="n"/>
+      <c r="K8" s="464" t="n"/>
+      <c r="L8" s="466" t="inlineStr">
+        <is>
+          <t>採用するコンテナランタイムの版数。</t>
+        </is>
+      </c>
+      <c r="M8" s="467" t="n"/>
+      <c r="N8" s="467" t="n"/>
+      <c r="O8" s="467" t="n"/>
+      <c r="P8" s="467" t="n"/>
+      <c r="Q8" s="467" t="n"/>
+      <c r="R8" s="467" t="n"/>
+      <c r="S8" s="467" t="n"/>
+      <c r="T8" s="467" t="n"/>
+      <c r="U8" s="467" t="n"/>
+      <c r="V8" s="467" t="n"/>
+      <c r="W8" s="468" t="n"/>
       <c r="X8" s="465" t="inlineStr">
         <is>
           <t>containerd 2.3.x LTS</t>
@@ -12094,19 +12427,23 @@
       <c r="H9" s="463" t="n"/>
       <c r="I9" s="463" t="n"/>
       <c r="J9" s="463" t="n"/>
-      <c r="K9" s="463" t="n"/>
-      <c r="L9" s="463" t="n"/>
-      <c r="M9" s="463" t="n"/>
-      <c r="N9" s="463" t="n"/>
-      <c r="O9" s="463" t="n"/>
-      <c r="P9" s="463" t="n"/>
-      <c r="Q9" s="463" t="n"/>
-      <c r="R9" s="463" t="n"/>
-      <c r="S9" s="463" t="n"/>
-      <c r="T9" s="463" t="n"/>
-      <c r="U9" s="463" t="n"/>
-      <c r="V9" s="463" t="n"/>
-      <c r="W9" s="464" t="n"/>
+      <c r="K9" s="464" t="n"/>
+      <c r="L9" s="466" t="inlineStr">
+        <is>
+          <t>採用するPodネットワークプラグインの版数。</t>
+        </is>
+      </c>
+      <c r="M9" s="467" t="n"/>
+      <c r="N9" s="467" t="n"/>
+      <c r="O9" s="467" t="n"/>
+      <c r="P9" s="467" t="n"/>
+      <c r="Q9" s="467" t="n"/>
+      <c r="R9" s="467" t="n"/>
+      <c r="S9" s="467" t="n"/>
+      <c r="T9" s="467" t="n"/>
+      <c r="U9" s="467" t="n"/>
+      <c r="V9" s="467" t="n"/>
+      <c r="W9" s="468" t="n"/>
       <c r="X9" s="465" t="inlineStr">
         <is>
           <t>Calico v3.32.x</t>
@@ -12141,7 +12478,7 @@
       <c r="AU9" s="463" t="n"/>
       <c r="AV9" s="464" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="29" customHeight="1" s="412">
       <c r="B10" s="465" t="inlineStr">
         <is>
           <t>CSIドライバー</t>
@@ -12155,19 +12492,23 @@
       <c r="H10" s="463" t="n"/>
       <c r="I10" s="463" t="n"/>
       <c r="J10" s="463" t="n"/>
-      <c r="K10" s="463" t="n"/>
-      <c r="L10" s="463" t="n"/>
-      <c r="M10" s="463" t="n"/>
-      <c r="N10" s="463" t="n"/>
-      <c r="O10" s="463" t="n"/>
-      <c r="P10" s="463" t="n"/>
-      <c r="Q10" s="463" t="n"/>
-      <c r="R10" s="463" t="n"/>
-      <c r="S10" s="463" t="n"/>
-      <c r="T10" s="463" t="n"/>
-      <c r="U10" s="463" t="n"/>
-      <c r="V10" s="463" t="n"/>
-      <c r="W10" s="464" t="n"/>
+      <c r="K10" s="464" t="n"/>
+      <c r="L10" s="466" t="inlineStr">
+        <is>
+          <t>採用する外部ストレージ連携ドライバの版数。</t>
+        </is>
+      </c>
+      <c r="M10" s="467" t="n"/>
+      <c r="N10" s="467" t="n"/>
+      <c r="O10" s="467" t="n"/>
+      <c r="P10" s="467" t="n"/>
+      <c r="Q10" s="467" t="n"/>
+      <c r="R10" s="467" t="n"/>
+      <c r="S10" s="467" t="n"/>
+      <c r="T10" s="467" t="n"/>
+      <c r="U10" s="467" t="n"/>
+      <c r="V10" s="467" t="n"/>
+      <c r="W10" s="468" t="n"/>
       <c r="X10" s="465" t="inlineStr">
         <is>
           <t>NetApp Trident v26.06</t>
@@ -12216,19 +12557,23 @@
       <c r="H11" s="463" t="n"/>
       <c r="I11" s="463" t="n"/>
       <c r="J11" s="463" t="n"/>
-      <c r="K11" s="463" t="n"/>
-      <c r="L11" s="463" t="n"/>
-      <c r="M11" s="463" t="n"/>
-      <c r="N11" s="463" t="n"/>
-      <c r="O11" s="463" t="n"/>
-      <c r="P11" s="463" t="n"/>
-      <c r="Q11" s="463" t="n"/>
-      <c r="R11" s="463" t="n"/>
-      <c r="S11" s="463" t="n"/>
-      <c r="T11" s="463" t="n"/>
-      <c r="U11" s="463" t="n"/>
-      <c r="V11" s="463" t="n"/>
-      <c r="W11" s="464" t="n"/>
+      <c r="K11" s="464" t="n"/>
+      <c r="L11" s="466" t="inlineStr">
+        <is>
+          <t>採用する監視ソフトウェアスタック。</t>
+        </is>
+      </c>
+      <c r="M11" s="467" t="n"/>
+      <c r="N11" s="467" t="n"/>
+      <c r="O11" s="467" t="n"/>
+      <c r="P11" s="467" t="n"/>
+      <c r="Q11" s="467" t="n"/>
+      <c r="R11" s="467" t="n"/>
+      <c r="S11" s="467" t="n"/>
+      <c r="T11" s="467" t="n"/>
+      <c r="U11" s="467" t="n"/>
+      <c r="V11" s="467" t="n"/>
+      <c r="W11" s="468" t="n"/>
       <c r="X11" s="465" t="inlineStr">
         <is>
           <t>kube-prometheus-stack（Helmチャート）</t>
@@ -12284,8 +12629,12 @@
       <c r="H14" s="463" t="n"/>
       <c r="I14" s="463" t="n"/>
       <c r="J14" s="463" t="n"/>
-      <c r="K14" s="463" t="n"/>
-      <c r="L14" s="463" t="n"/>
+      <c r="K14" s="464" t="n"/>
+      <c r="L14" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M14" s="463" t="n"/>
       <c r="N14" s="463" t="n"/>
       <c r="O14" s="463" t="n"/>
@@ -12335,7 +12684,7 @@
       <c r="AU14" s="463" t="n"/>
       <c r="AV14" s="464" t="n"/>
     </row>
-    <row r="15" ht="29" customHeight="1" s="412">
+    <row r="15" ht="58" customHeight="1" s="412">
       <c r="B15" s="465" t="inlineStr">
         <is>
           <t>SystemdCgroup</t>
@@ -12349,19 +12698,23 @@
       <c r="H15" s="463" t="n"/>
       <c r="I15" s="463" t="n"/>
       <c r="J15" s="463" t="n"/>
-      <c r="K15" s="463" t="n"/>
-      <c r="L15" s="463" t="n"/>
-      <c r="M15" s="463" t="n"/>
-      <c r="N15" s="463" t="n"/>
-      <c r="O15" s="463" t="n"/>
-      <c r="P15" s="463" t="n"/>
-      <c r="Q15" s="463" t="n"/>
-      <c r="R15" s="463" t="n"/>
-      <c r="S15" s="463" t="n"/>
-      <c r="T15" s="463" t="n"/>
-      <c r="U15" s="463" t="n"/>
-      <c r="V15" s="463" t="n"/>
-      <c r="W15" s="464" t="n"/>
+      <c r="K15" s="464" t="n"/>
+      <c r="L15" s="466" t="inlineStr">
+        <is>
+          <t>kubeletの既定cgroupドライバ（systemd）とcontainerd側の設定が一致していないと、リソース管理が二重管理状態となりノードが不安定化する既知の問題があるため統一する。</t>
+        </is>
+      </c>
+      <c r="M15" s="467" t="n"/>
+      <c r="N15" s="467" t="n"/>
+      <c r="O15" s="467" t="n"/>
+      <c r="P15" s="467" t="n"/>
+      <c r="Q15" s="467" t="n"/>
+      <c r="R15" s="467" t="n"/>
+      <c r="S15" s="467" t="n"/>
+      <c r="T15" s="467" t="n"/>
+      <c r="U15" s="467" t="n"/>
+      <c r="V15" s="467" t="n"/>
+      <c r="W15" s="468" t="n"/>
       <c r="X15" s="465" t="inlineStr">
         <is>
           <t>true</t>
@@ -12400,7 +12753,7 @@
       <c r="AU15" s="463" t="n"/>
       <c r="AV15" s="464" t="n"/>
     </row>
-    <row r="16" ht="29" customHeight="1" s="412">
+    <row r="16" ht="43.5" customHeight="1" s="412">
       <c r="B16" s="465" t="inlineStr">
         <is>
           <t>sandbox image</t>
@@ -12414,19 +12767,23 @@
       <c r="H16" s="463" t="n"/>
       <c r="I16" s="463" t="n"/>
       <c r="J16" s="463" t="n"/>
-      <c r="K16" s="463" t="n"/>
-      <c r="L16" s="463" t="n"/>
-      <c r="M16" s="463" t="n"/>
-      <c r="N16" s="463" t="n"/>
-      <c r="O16" s="463" t="n"/>
-      <c r="P16" s="463" t="n"/>
-      <c r="Q16" s="463" t="n"/>
-      <c r="R16" s="463" t="n"/>
-      <c r="S16" s="463" t="n"/>
-      <c r="T16" s="463" t="n"/>
-      <c r="U16" s="463" t="n"/>
-      <c r="V16" s="463" t="n"/>
-      <c r="W16" s="464" t="n"/>
+      <c r="K16" s="464" t="n"/>
+      <c r="L16" s="466" t="inlineStr">
+        <is>
+          <t>kubeadmが期待するpauseイメージのバージョンとcontainerdの既定が食い違うと、警告や非互換につながるため明示固定する。</t>
+        </is>
+      </c>
+      <c r="M16" s="467" t="n"/>
+      <c r="N16" s="467" t="n"/>
+      <c r="O16" s="467" t="n"/>
+      <c r="P16" s="467" t="n"/>
+      <c r="Q16" s="467" t="n"/>
+      <c r="R16" s="467" t="n"/>
+      <c r="S16" s="467" t="n"/>
+      <c r="T16" s="467" t="n"/>
+      <c r="U16" s="467" t="n"/>
+      <c r="V16" s="467" t="n"/>
+      <c r="W16" s="468" t="n"/>
       <c r="X16" s="465" t="inlineStr">
         <is>
           <t>registry.k8s.io/pause:3.10</t>
@@ -12465,7 +12822,7 @@
       <c r="AU16" s="463" t="n"/>
       <c r="AV16" s="464" t="n"/>
     </row>
-    <row r="17" ht="29" customHeight="1" s="412">
+    <row r="17" ht="43.5" customHeight="1" s="412">
       <c r="B17" s="465" t="inlineStr">
         <is>
           <t>レジストリミラー</t>
@@ -12479,19 +12836,23 @@
       <c r="H17" s="463" t="n"/>
       <c r="I17" s="463" t="n"/>
       <c r="J17" s="463" t="n"/>
-      <c r="K17" s="463" t="n"/>
-      <c r="L17" s="463" t="n"/>
-      <c r="M17" s="463" t="n"/>
-      <c r="N17" s="463" t="n"/>
-      <c r="O17" s="463" t="n"/>
-      <c r="P17" s="463" t="n"/>
-      <c r="Q17" s="463" t="n"/>
-      <c r="R17" s="463" t="n"/>
-      <c r="S17" s="463" t="n"/>
-      <c r="T17" s="463" t="n"/>
-      <c r="U17" s="463" t="n"/>
-      <c r="V17" s="463" t="n"/>
-      <c r="W17" s="464" t="n"/>
+      <c r="K17" s="464" t="n"/>
+      <c r="L17" s="466" t="inlineStr">
+        <is>
+          <t>Docker Hubの未認証pull回数制限に抵触した場合、コンテナイメージの取得自体が失敗するようになるため、必要に応じてミラーを導入する。</t>
+        </is>
+      </c>
+      <c r="M17" s="467" t="n"/>
+      <c r="N17" s="467" t="n"/>
+      <c r="O17" s="467" t="n"/>
+      <c r="P17" s="467" t="n"/>
+      <c r="Q17" s="467" t="n"/>
+      <c r="R17" s="467" t="n"/>
+      <c r="S17" s="467" t="n"/>
+      <c r="T17" s="467" t="n"/>
+      <c r="U17" s="467" t="n"/>
+      <c r="V17" s="467" t="n"/>
+      <c r="W17" s="468" t="n"/>
       <c r="X17" s="465" t="inlineStr">
         <is>
           <t>設定なし（Docker Hub直接参照）</t>
@@ -12551,8 +12912,12 @@
       <c r="H20" s="463" t="n"/>
       <c r="I20" s="463" t="n"/>
       <c r="J20" s="463" t="n"/>
-      <c r="K20" s="463" t="n"/>
-      <c r="L20" s="463" t="n"/>
+      <c r="K20" s="464" t="n"/>
+      <c r="L20" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M20" s="463" t="n"/>
       <c r="N20" s="463" t="n"/>
       <c r="O20" s="463" t="n"/>
@@ -12602,7 +12967,7 @@
       <c r="AU20" s="463" t="n"/>
       <c r="AV20" s="464" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="43.5" customHeight="1" s="412">
       <c r="B21" s="465" t="inlineStr">
         <is>
           <t>kubernetesVersion</t>
@@ -12616,19 +12981,23 @@
       <c r="H21" s="463" t="n"/>
       <c r="I21" s="463" t="n"/>
       <c r="J21" s="463" t="n"/>
-      <c r="K21" s="463" t="n"/>
-      <c r="L21" s="463" t="n"/>
-      <c r="M21" s="463" t="n"/>
-      <c r="N21" s="463" t="n"/>
-      <c r="O21" s="463" t="n"/>
-      <c r="P21" s="463" t="n"/>
-      <c r="Q21" s="463" t="n"/>
-      <c r="R21" s="463" t="n"/>
-      <c r="S21" s="463" t="n"/>
-      <c r="T21" s="463" t="n"/>
-      <c r="U21" s="463" t="n"/>
-      <c r="V21" s="463" t="n"/>
-      <c r="W21" s="464" t="n"/>
+      <c r="K21" s="464" t="n"/>
+      <c r="L21" s="466" t="inlineStr">
+        <is>
+          <t>構築するクラスタのKubernetesバージョンを明示し、意図しないバージョンでの構築を防ぐため。</t>
+        </is>
+      </c>
+      <c r="M21" s="467" t="n"/>
+      <c r="N21" s="467" t="n"/>
+      <c r="O21" s="467" t="n"/>
+      <c r="P21" s="467" t="n"/>
+      <c r="Q21" s="467" t="n"/>
+      <c r="R21" s="467" t="n"/>
+      <c r="S21" s="467" t="n"/>
+      <c r="T21" s="467" t="n"/>
+      <c r="U21" s="467" t="n"/>
+      <c r="V21" s="467" t="n"/>
+      <c r="W21" s="468" t="n"/>
       <c r="X21" s="465" t="inlineStr">
         <is>
           <t>v1.35.x</t>
@@ -12667,7 +13036,7 @@
       <c r="AU21" s="463" t="n"/>
       <c r="AV21" s="464" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="29" customHeight="1" s="412">
       <c r="B22" s="465" t="inlineStr">
         <is>
           <t>clusterName</t>
@@ -12681,19 +13050,23 @@
       <c r="H22" s="463" t="n"/>
       <c r="I22" s="463" t="n"/>
       <c r="J22" s="463" t="n"/>
-      <c r="K22" s="463" t="n"/>
-      <c r="L22" s="463" t="n"/>
-      <c r="M22" s="463" t="n"/>
-      <c r="N22" s="463" t="n"/>
-      <c r="O22" s="463" t="n"/>
-      <c r="P22" s="463" t="n"/>
-      <c r="Q22" s="463" t="n"/>
-      <c r="R22" s="463" t="n"/>
-      <c r="S22" s="463" t="n"/>
-      <c r="T22" s="463" t="n"/>
-      <c r="U22" s="463" t="n"/>
-      <c r="V22" s="463" t="n"/>
-      <c r="W22" s="464" t="n"/>
+      <c r="K22" s="464" t="n"/>
+      <c r="L22" s="466" t="inlineStr">
+        <is>
+          <t>kubeconfigのcontext名等、クラスタ識別に用いられる。</t>
+        </is>
+      </c>
+      <c r="M22" s="467" t="n"/>
+      <c r="N22" s="467" t="n"/>
+      <c r="O22" s="467" t="n"/>
+      <c r="P22" s="467" t="n"/>
+      <c r="Q22" s="467" t="n"/>
+      <c r="R22" s="467" t="n"/>
+      <c r="S22" s="467" t="n"/>
+      <c r="T22" s="467" t="n"/>
+      <c r="U22" s="467" t="n"/>
+      <c r="V22" s="467" t="n"/>
+      <c r="W22" s="468" t="n"/>
       <c r="X22" s="465" t="inlineStr">
         <is>
           <t>kubernetes</t>
@@ -12732,7 +13105,7 @@
       <c r="AU22" s="463" t="n"/>
       <c r="AV22" s="464" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="43.5" customHeight="1" s="412">
       <c r="B23" s="465" t="inlineStr">
         <is>
           <t>controlPlaneEndpoint</t>
@@ -12746,19 +13119,23 @@
       <c r="H23" s="463" t="n"/>
       <c r="I23" s="463" t="n"/>
       <c r="J23" s="463" t="n"/>
-      <c r="K23" s="463" t="n"/>
-      <c r="L23" s="463" t="n"/>
-      <c r="M23" s="463" t="n"/>
-      <c r="N23" s="463" t="n"/>
-      <c r="O23" s="463" t="n"/>
-      <c r="P23" s="463" t="n"/>
-      <c r="Q23" s="463" t="n"/>
-      <c r="R23" s="463" t="n"/>
-      <c r="S23" s="463" t="n"/>
-      <c r="T23" s="463" t="n"/>
-      <c r="U23" s="463" t="n"/>
-      <c r="V23" s="463" t="n"/>
-      <c r="W23" s="464" t="n"/>
+      <c r="K23" s="464" t="n"/>
+      <c r="L23" s="466" t="inlineStr">
+        <is>
+          <t>HA構成の全Control Planeを指す共通アドレス。構築後の変更は極めて困難なため、事前確定が必須。</t>
+        </is>
+      </c>
+      <c r="M23" s="467" t="n"/>
+      <c r="N23" s="467" t="n"/>
+      <c r="O23" s="467" t="n"/>
+      <c r="P23" s="467" t="n"/>
+      <c r="Q23" s="467" t="n"/>
+      <c r="R23" s="467" t="n"/>
+      <c r="S23" s="467" t="n"/>
+      <c r="T23" s="467" t="n"/>
+      <c r="U23" s="467" t="n"/>
+      <c r="V23" s="467" t="n"/>
+      <c r="W23" s="468" t="n"/>
       <c r="X23" s="465" t="inlineStr">
         <is>
           <t>※要決定（外部LB VIP:6443）</t>
@@ -12797,7 +13174,7 @@
       <c r="AU23" s="463" t="n"/>
       <c r="AV23" s="464" t="n"/>
     </row>
-    <row r="24" ht="29" customHeight="1" s="412">
+    <row r="24" ht="43.5" customHeight="1" s="412">
       <c r="B24" s="465" t="inlineStr">
         <is>
           <t>networking.podSubnet</t>
@@ -12811,19 +13188,23 @@
       <c r="H24" s="463" t="n"/>
       <c r="I24" s="463" t="n"/>
       <c r="J24" s="463" t="n"/>
-      <c r="K24" s="463" t="n"/>
-      <c r="L24" s="463" t="n"/>
-      <c r="M24" s="463" t="n"/>
-      <c r="N24" s="463" t="n"/>
-      <c r="O24" s="463" t="n"/>
-      <c r="P24" s="463" t="n"/>
-      <c r="Q24" s="463" t="n"/>
-      <c r="R24" s="463" t="n"/>
-      <c r="S24" s="463" t="n"/>
-      <c r="T24" s="463" t="n"/>
-      <c r="U24" s="463" t="n"/>
-      <c r="V24" s="463" t="n"/>
-      <c r="W24" s="464" t="n"/>
+      <c r="K24" s="464" t="n"/>
+      <c r="L24" s="466" t="inlineStr">
+        <is>
+          <t>CalicoのIPPoolと一致させる必要がある。構築後の変更にはクラスタ再構築が必要となるため事前確定必須。</t>
+        </is>
+      </c>
+      <c r="M24" s="467" t="n"/>
+      <c r="N24" s="467" t="n"/>
+      <c r="O24" s="467" t="n"/>
+      <c r="P24" s="467" t="n"/>
+      <c r="Q24" s="467" t="n"/>
+      <c r="R24" s="467" t="n"/>
+      <c r="S24" s="467" t="n"/>
+      <c r="T24" s="467" t="n"/>
+      <c r="U24" s="467" t="n"/>
+      <c r="V24" s="467" t="n"/>
+      <c r="W24" s="468" t="n"/>
       <c r="X24" s="465" t="inlineStr">
         <is>
           <t>192.168.0.0/16</t>
@@ -12862,7 +13243,7 @@
       <c r="AU24" s="463" t="n"/>
       <c r="AV24" s="464" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="43.5" customHeight="1" s="412">
       <c r="B25" s="465" t="inlineStr">
         <is>
           <t>networking.serviceSubnet</t>
@@ -12876,19 +13257,23 @@
       <c r="H25" s="463" t="n"/>
       <c r="I25" s="463" t="n"/>
       <c r="J25" s="463" t="n"/>
-      <c r="K25" s="463" t="n"/>
-      <c r="L25" s="463" t="n"/>
-      <c r="M25" s="463" t="n"/>
-      <c r="N25" s="463" t="n"/>
-      <c r="O25" s="463" t="n"/>
-      <c r="P25" s="463" t="n"/>
-      <c r="Q25" s="463" t="n"/>
-      <c r="R25" s="463" t="n"/>
-      <c r="S25" s="463" t="n"/>
-      <c r="T25" s="463" t="n"/>
-      <c r="U25" s="463" t="n"/>
-      <c r="V25" s="463" t="n"/>
-      <c r="W25" s="464" t="n"/>
+      <c r="K25" s="464" t="n"/>
+      <c r="L25" s="466" t="inlineStr">
+        <is>
+          <t>ClusterIP Serviceに割り当てるIPアドレス空間。Podネットワークと重複しないよう事前確定する。</t>
+        </is>
+      </c>
+      <c r="M25" s="467" t="n"/>
+      <c r="N25" s="467" t="n"/>
+      <c r="O25" s="467" t="n"/>
+      <c r="P25" s="467" t="n"/>
+      <c r="Q25" s="467" t="n"/>
+      <c r="R25" s="467" t="n"/>
+      <c r="S25" s="467" t="n"/>
+      <c r="T25" s="467" t="n"/>
+      <c r="U25" s="467" t="n"/>
+      <c r="V25" s="467" t="n"/>
+      <c r="W25" s="468" t="n"/>
       <c r="X25" s="465" t="inlineStr">
         <is>
           <t>10.96.0.0/12</t>
@@ -12927,7 +13312,7 @@
       <c r="AU25" s="463" t="n"/>
       <c r="AV25" s="464" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="43.5" customHeight="1" s="412">
       <c r="B26" s="465" t="inlineStr">
         <is>
           <t>networking.dnsDomain</t>
@@ -12941,19 +13326,23 @@
       <c r="H26" s="463" t="n"/>
       <c r="I26" s="463" t="n"/>
       <c r="J26" s="463" t="n"/>
-      <c r="K26" s="463" t="n"/>
-      <c r="L26" s="463" t="n"/>
-      <c r="M26" s="463" t="n"/>
-      <c r="N26" s="463" t="n"/>
-      <c r="O26" s="463" t="n"/>
-      <c r="P26" s="463" t="n"/>
-      <c r="Q26" s="463" t="n"/>
-      <c r="R26" s="463" t="n"/>
-      <c r="S26" s="463" t="n"/>
-      <c r="T26" s="463" t="n"/>
-      <c r="U26" s="463" t="n"/>
-      <c r="V26" s="463" t="n"/>
-      <c r="W26" s="464" t="n"/>
+      <c r="K26" s="464" t="n"/>
+      <c r="L26" s="466" t="inlineStr">
+        <is>
+          <t>クラスタ内DNSのドメインサフィックス。Service名前解決（&lt;svc&gt;.&lt;ns&gt;.svc.cluster.local）の基準となる。</t>
+        </is>
+      </c>
+      <c r="M26" s="467" t="n"/>
+      <c r="N26" s="467" t="n"/>
+      <c r="O26" s="467" t="n"/>
+      <c r="P26" s="467" t="n"/>
+      <c r="Q26" s="467" t="n"/>
+      <c r="R26" s="467" t="n"/>
+      <c r="S26" s="467" t="n"/>
+      <c r="T26" s="467" t="n"/>
+      <c r="U26" s="467" t="n"/>
+      <c r="V26" s="467" t="n"/>
+      <c r="W26" s="468" t="n"/>
       <c r="X26" s="465" t="inlineStr">
         <is>
           <t>cluster.local</t>
@@ -12992,7 +13381,7 @@
       <c r="AU26" s="463" t="n"/>
       <c r="AV26" s="464" t="n"/>
     </row>
-    <row r="27" ht="29" customHeight="1" s="412">
+    <row r="27" ht="43.5" customHeight="1" s="412">
       <c r="B27" s="465" t="inlineStr">
         <is>
           <t>etcd構成</t>
@@ -13006,19 +13395,23 @@
       <c r="H27" s="463" t="n"/>
       <c r="I27" s="463" t="n"/>
       <c r="J27" s="463" t="n"/>
-      <c r="K27" s="463" t="n"/>
-      <c r="L27" s="463" t="n"/>
-      <c r="M27" s="463" t="n"/>
-      <c r="N27" s="463" t="n"/>
-      <c r="O27" s="463" t="n"/>
-      <c r="P27" s="463" t="n"/>
-      <c r="Q27" s="463" t="n"/>
-      <c r="R27" s="463" t="n"/>
-      <c r="S27" s="463" t="n"/>
-      <c r="T27" s="463" t="n"/>
-      <c r="U27" s="463" t="n"/>
-      <c r="V27" s="463" t="n"/>
-      <c r="W27" s="464" t="n"/>
+      <c r="K27" s="464" t="n"/>
+      <c r="L27" s="466" t="inlineStr">
+        <is>
+          <t>スプリットブレイン防止のため、Control Plane 3台でetcdを冗長化する構成方式（基本設計書2.1.4）。</t>
+        </is>
+      </c>
+      <c r="M27" s="467" t="n"/>
+      <c r="N27" s="467" t="n"/>
+      <c r="O27" s="467" t="n"/>
+      <c r="P27" s="467" t="n"/>
+      <c r="Q27" s="467" t="n"/>
+      <c r="R27" s="467" t="n"/>
+      <c r="S27" s="467" t="n"/>
+      <c r="T27" s="467" t="n"/>
+      <c r="U27" s="467" t="n"/>
+      <c r="V27" s="467" t="n"/>
+      <c r="W27" s="468" t="n"/>
       <c r="X27" s="465" t="inlineStr">
         <is>
           <t>stacked（Control Plane同居）</t>
@@ -13057,7 +13450,7 @@
       <c r="AU27" s="463" t="n"/>
       <c r="AV27" s="464" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="29" customHeight="1" s="412">
       <c r="B28" s="465" t="inlineStr">
         <is>
           <t>imageRepository</t>
@@ -13071,19 +13464,23 @@
       <c r="H28" s="463" t="n"/>
       <c r="I28" s="463" t="n"/>
       <c r="J28" s="463" t="n"/>
-      <c r="K28" s="463" t="n"/>
-      <c r="L28" s="463" t="n"/>
-      <c r="M28" s="463" t="n"/>
-      <c r="N28" s="463" t="n"/>
-      <c r="O28" s="463" t="n"/>
-      <c r="P28" s="463" t="n"/>
-      <c r="Q28" s="463" t="n"/>
-      <c r="R28" s="463" t="n"/>
-      <c r="S28" s="463" t="n"/>
-      <c r="T28" s="463" t="n"/>
-      <c r="U28" s="463" t="n"/>
-      <c r="V28" s="463" t="n"/>
-      <c r="W28" s="464" t="n"/>
+      <c r="K28" s="464" t="n"/>
+      <c r="L28" s="466" t="inlineStr">
+        <is>
+          <t>kubeadmが管理コンポーネントのイメージを取得するレジストリ。</t>
+        </is>
+      </c>
+      <c r="M28" s="467" t="n"/>
+      <c r="N28" s="467" t="n"/>
+      <c r="O28" s="467" t="n"/>
+      <c r="P28" s="467" t="n"/>
+      <c r="Q28" s="467" t="n"/>
+      <c r="R28" s="467" t="n"/>
+      <c r="S28" s="467" t="n"/>
+      <c r="T28" s="467" t="n"/>
+      <c r="U28" s="467" t="n"/>
+      <c r="V28" s="467" t="n"/>
+      <c r="W28" s="468" t="n"/>
       <c r="X28" s="465" t="inlineStr">
         <is>
           <t>registry.k8s.io</t>
@@ -13143,8 +13540,12 @@
       <c r="H31" s="463" t="n"/>
       <c r="I31" s="463" t="n"/>
       <c r="J31" s="463" t="n"/>
-      <c r="K31" s="463" t="n"/>
-      <c r="L31" s="463" t="n"/>
+      <c r="K31" s="464" t="n"/>
+      <c r="L31" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M31" s="463" t="n"/>
       <c r="N31" s="463" t="n"/>
       <c r="O31" s="463" t="n"/>
@@ -13194,7 +13595,7 @@
       <c r="AU31" s="463" t="n"/>
       <c r="AV31" s="464" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="29" customHeight="1" s="412">
       <c r="B32" s="465" t="inlineStr">
         <is>
           <t>cgroupDriver</t>
@@ -13208,19 +13609,23 @@
       <c r="H32" s="463" t="n"/>
       <c r="I32" s="463" t="n"/>
       <c r="J32" s="463" t="n"/>
-      <c r="K32" s="463" t="n"/>
-      <c r="L32" s="463" t="n"/>
-      <c r="M32" s="463" t="n"/>
-      <c r="N32" s="463" t="n"/>
-      <c r="O32" s="463" t="n"/>
-      <c r="P32" s="463" t="n"/>
-      <c r="Q32" s="463" t="n"/>
-      <c r="R32" s="463" t="n"/>
-      <c r="S32" s="463" t="n"/>
-      <c r="T32" s="463" t="n"/>
-      <c r="U32" s="463" t="n"/>
-      <c r="V32" s="463" t="n"/>
-      <c r="W32" s="464" t="n"/>
+      <c r="K32" s="464" t="n"/>
+      <c r="L32" s="466" t="inlineStr">
+        <is>
+          <t>containerd側の設定と一致させないと、リソース管理の不整合が生じるため。</t>
+        </is>
+      </c>
+      <c r="M32" s="467" t="n"/>
+      <c r="N32" s="467" t="n"/>
+      <c r="O32" s="467" t="n"/>
+      <c r="P32" s="467" t="n"/>
+      <c r="Q32" s="467" t="n"/>
+      <c r="R32" s="467" t="n"/>
+      <c r="S32" s="467" t="n"/>
+      <c r="T32" s="467" t="n"/>
+      <c r="U32" s="467" t="n"/>
+      <c r="V32" s="467" t="n"/>
+      <c r="W32" s="468" t="n"/>
       <c r="X32" s="465" t="inlineStr">
         <is>
           <t>systemd</t>
@@ -13259,7 +13664,7 @@
       <c r="AU32" s="463" t="n"/>
       <c r="AV32" s="464" t="n"/>
     </row>
-    <row r="33" ht="29" customHeight="1" s="412">
+    <row r="33" ht="58" customHeight="1" s="412">
       <c r="B33" s="465" t="inlineStr">
         <is>
           <t>maxPods</t>
@@ -13273,19 +13678,23 @@
       <c r="H33" s="463" t="n"/>
       <c r="I33" s="463" t="n"/>
       <c r="J33" s="463" t="n"/>
-      <c r="K33" s="463" t="n"/>
-      <c r="L33" s="463" t="n"/>
-      <c r="M33" s="463" t="n"/>
-      <c r="N33" s="463" t="n"/>
-      <c r="O33" s="463" t="n"/>
-      <c r="P33" s="463" t="n"/>
-      <c r="Q33" s="463" t="n"/>
-      <c r="R33" s="463" t="n"/>
-      <c r="S33" s="463" t="n"/>
-      <c r="T33" s="463" t="n"/>
-      <c r="U33" s="463" t="n"/>
-      <c r="V33" s="463" t="n"/>
-      <c r="W33" s="464" t="n"/>
+      <c r="K33" s="464" t="n"/>
+      <c r="L33" s="466" t="inlineStr">
+        <is>
+          <t>1ノードに配置可能なPod数の上限。Pod CIDRのblockSizeと整合していないと、割り当て可能なPod IP数を超えてPodがスケジュールされずエラーとなる。</t>
+        </is>
+      </c>
+      <c r="M33" s="467" t="n"/>
+      <c r="N33" s="467" t="n"/>
+      <c r="O33" s="467" t="n"/>
+      <c r="P33" s="467" t="n"/>
+      <c r="Q33" s="467" t="n"/>
+      <c r="R33" s="467" t="n"/>
+      <c r="S33" s="467" t="n"/>
+      <c r="T33" s="467" t="n"/>
+      <c r="U33" s="467" t="n"/>
+      <c r="V33" s="467" t="n"/>
+      <c r="W33" s="468" t="n"/>
       <c r="X33" s="465" t="inlineStr">
         <is>
           <t>110</t>
@@ -13324,7 +13733,7 @@
       <c r="AU33" s="463" t="n"/>
       <c r="AV33" s="464" t="n"/>
     </row>
-    <row r="34" ht="29" customHeight="1" s="412">
+    <row r="34" ht="43.5" customHeight="1" s="412">
       <c r="B34" s="465" t="inlineStr">
         <is>
           <t>systemReserved / kubeReserved</t>
@@ -13338,19 +13747,23 @@
       <c r="H34" s="463" t="n"/>
       <c r="I34" s="463" t="n"/>
       <c r="J34" s="463" t="n"/>
-      <c r="K34" s="463" t="n"/>
-      <c r="L34" s="463" t="n"/>
-      <c r="M34" s="463" t="n"/>
-      <c r="N34" s="463" t="n"/>
-      <c r="O34" s="463" t="n"/>
-      <c r="P34" s="463" t="n"/>
-      <c r="Q34" s="463" t="n"/>
-      <c r="R34" s="463" t="n"/>
-      <c r="S34" s="463" t="n"/>
-      <c r="T34" s="463" t="n"/>
-      <c r="U34" s="463" t="n"/>
-      <c r="V34" s="463" t="n"/>
-      <c r="W34" s="464" t="n"/>
+      <c r="K34" s="464" t="n"/>
+      <c r="L34" s="466" t="inlineStr">
+        <is>
+          <t>OS・kubelet自体が使用するリソースをPodへ割り当てないよう予約することで、ノードリソース枯渇によるノード自体の不安定化を防ぐため。</t>
+        </is>
+      </c>
+      <c r="M34" s="467" t="n"/>
+      <c r="N34" s="467" t="n"/>
+      <c r="O34" s="467" t="n"/>
+      <c r="P34" s="467" t="n"/>
+      <c r="Q34" s="467" t="n"/>
+      <c r="R34" s="467" t="n"/>
+      <c r="S34" s="467" t="n"/>
+      <c r="T34" s="467" t="n"/>
+      <c r="U34" s="467" t="n"/>
+      <c r="V34" s="467" t="n"/>
+      <c r="W34" s="468" t="n"/>
       <c r="X34" s="465" t="inlineStr">
         <is>
           <t>※要決定</t>
@@ -13389,7 +13802,7 @@
       <c r="AU34" s="463" t="n"/>
       <c r="AV34" s="464" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="29" customHeight="1" s="412">
       <c r="B35" s="465" t="inlineStr">
         <is>
           <t>evictionHard</t>
@@ -13403,19 +13816,23 @@
       <c r="H35" s="463" t="n"/>
       <c r="I35" s="463" t="n"/>
       <c r="J35" s="463" t="n"/>
-      <c r="K35" s="463" t="n"/>
-      <c r="L35" s="463" t="n"/>
-      <c r="M35" s="463" t="n"/>
-      <c r="N35" s="463" t="n"/>
-      <c r="O35" s="463" t="n"/>
-      <c r="P35" s="463" t="n"/>
-      <c r="Q35" s="463" t="n"/>
-      <c r="R35" s="463" t="n"/>
-      <c r="S35" s="463" t="n"/>
-      <c r="T35" s="463" t="n"/>
-      <c r="U35" s="463" t="n"/>
-      <c r="V35" s="463" t="n"/>
-      <c r="W35" s="464" t="n"/>
+      <c r="K35" s="464" t="n"/>
+      <c r="L35" s="466" t="inlineStr">
+        <is>
+          <t>ノードのリソース逼迫時に低優先度Podを退避させ、ノード全体のクラッシュを防ぐための閾値。</t>
+        </is>
+      </c>
+      <c r="M35" s="467" t="n"/>
+      <c r="N35" s="467" t="n"/>
+      <c r="O35" s="467" t="n"/>
+      <c r="P35" s="467" t="n"/>
+      <c r="Q35" s="467" t="n"/>
+      <c r="R35" s="467" t="n"/>
+      <c r="S35" s="467" t="n"/>
+      <c r="T35" s="467" t="n"/>
+      <c r="U35" s="467" t="n"/>
+      <c r="V35" s="467" t="n"/>
+      <c r="W35" s="468" t="n"/>
       <c r="X35" s="465" t="inlineStr">
         <is>
           <t>デフォルト値を使用</t>
@@ -13475,8 +13892,12 @@
       <c r="H38" s="463" t="n"/>
       <c r="I38" s="463" t="n"/>
       <c r="J38" s="463" t="n"/>
-      <c r="K38" s="463" t="n"/>
-      <c r="L38" s="463" t="n"/>
+      <c r="K38" s="464" t="n"/>
+      <c r="L38" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M38" s="463" t="n"/>
       <c r="N38" s="463" t="n"/>
       <c r="O38" s="463" t="n"/>
@@ -13526,7 +13947,7 @@
       <c r="AU38" s="463" t="n"/>
       <c r="AV38" s="464" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="43.5" customHeight="1" s="412">
       <c r="B39" s="465" t="inlineStr">
         <is>
           <t>セキュアポート</t>
@@ -13540,19 +13961,23 @@
       <c r="H39" s="463" t="n"/>
       <c r="I39" s="463" t="n"/>
       <c r="J39" s="463" t="n"/>
-      <c r="K39" s="463" t="n"/>
-      <c r="L39" s="463" t="n"/>
-      <c r="M39" s="463" t="n"/>
-      <c r="N39" s="463" t="n"/>
-      <c r="O39" s="463" t="n"/>
-      <c r="P39" s="463" t="n"/>
-      <c r="Q39" s="463" t="n"/>
-      <c r="R39" s="463" t="n"/>
-      <c r="S39" s="463" t="n"/>
-      <c r="T39" s="463" t="n"/>
-      <c r="U39" s="463" t="n"/>
-      <c r="V39" s="463" t="n"/>
-      <c r="W39" s="464" t="n"/>
+      <c r="K39" s="464" t="n"/>
+      <c r="L39" s="466" t="inlineStr">
+        <is>
+          <t>kubectl等がAPIサーバーへ接続する際の待受ポート。外部LBのバックエンドポートと一致させる必要がある。</t>
+        </is>
+      </c>
+      <c r="M39" s="467" t="n"/>
+      <c r="N39" s="467" t="n"/>
+      <c r="O39" s="467" t="n"/>
+      <c r="P39" s="467" t="n"/>
+      <c r="Q39" s="467" t="n"/>
+      <c r="R39" s="467" t="n"/>
+      <c r="S39" s="467" t="n"/>
+      <c r="T39" s="467" t="n"/>
+      <c r="U39" s="467" t="n"/>
+      <c r="V39" s="467" t="n"/>
+      <c r="W39" s="468" t="n"/>
       <c r="X39" s="465" t="inlineStr">
         <is>
           <t>6443</t>
@@ -13591,7 +14016,7 @@
       <c r="AU39" s="463" t="n"/>
       <c r="AV39" s="464" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="58" customHeight="1" s="412">
       <c r="B40" s="465" t="inlineStr">
         <is>
           <t>認可モード（authorization-mode）</t>
@@ -13605,19 +14030,23 @@
       <c r="H40" s="463" t="n"/>
       <c r="I40" s="463" t="n"/>
       <c r="J40" s="463" t="n"/>
-      <c r="K40" s="463" t="n"/>
-      <c r="L40" s="463" t="n"/>
-      <c r="M40" s="463" t="n"/>
-      <c r="N40" s="463" t="n"/>
-      <c r="O40" s="463" t="n"/>
-      <c r="P40" s="463" t="n"/>
-      <c r="Q40" s="463" t="n"/>
-      <c r="R40" s="463" t="n"/>
-      <c r="S40" s="463" t="n"/>
-      <c r="T40" s="463" t="n"/>
-      <c r="U40" s="463" t="n"/>
-      <c r="V40" s="463" t="n"/>
-      <c r="W40" s="464" t="n"/>
+      <c r="K40" s="464" t="n"/>
+      <c r="L40" s="466" t="inlineStr">
+        <is>
+          <t>Nodeモードでkubeletが自ノード関連リソースのみ操作できるよう制限し、RBACで利用者ごとの権限を制御する、二段構えのアクセス制御を実現するため。</t>
+        </is>
+      </c>
+      <c r="M40" s="467" t="n"/>
+      <c r="N40" s="467" t="n"/>
+      <c r="O40" s="467" t="n"/>
+      <c r="P40" s="467" t="n"/>
+      <c r="Q40" s="467" t="n"/>
+      <c r="R40" s="467" t="n"/>
+      <c r="S40" s="467" t="n"/>
+      <c r="T40" s="467" t="n"/>
+      <c r="U40" s="467" t="n"/>
+      <c r="V40" s="467" t="n"/>
+      <c r="W40" s="468" t="n"/>
       <c r="X40" s="465" t="inlineStr">
         <is>
           <t>Node,RBAC</t>
@@ -13677,8 +14106,12 @@
       <c r="H43" s="463" t="n"/>
       <c r="I43" s="463" t="n"/>
       <c r="J43" s="463" t="n"/>
-      <c r="K43" s="463" t="n"/>
-      <c r="L43" s="463" t="n"/>
+      <c r="K43" s="464" t="n"/>
+      <c r="L43" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M43" s="463" t="n"/>
       <c r="N43" s="463" t="n"/>
       <c r="O43" s="463" t="n"/>
@@ -13728,7 +14161,7 @@
       <c r="AU43" s="463" t="n"/>
       <c r="AV43" s="464" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="29" customHeight="1" s="412">
       <c r="B44" s="465" t="inlineStr">
         <is>
           <t>インストール方式</t>
@@ -13742,19 +14175,23 @@
       <c r="H44" s="463" t="n"/>
       <c r="I44" s="463" t="n"/>
       <c r="J44" s="463" t="n"/>
-      <c r="K44" s="463" t="n"/>
-      <c r="L44" s="463" t="n"/>
-      <c r="M44" s="463" t="n"/>
-      <c r="N44" s="463" t="n"/>
-      <c r="O44" s="463" t="n"/>
-      <c r="P44" s="463" t="n"/>
-      <c r="Q44" s="463" t="n"/>
-      <c r="R44" s="463" t="n"/>
-      <c r="S44" s="463" t="n"/>
-      <c r="T44" s="463" t="n"/>
-      <c r="U44" s="463" t="n"/>
-      <c r="V44" s="463" t="n"/>
-      <c r="W44" s="464" t="n"/>
+      <c r="K44" s="464" t="n"/>
+      <c r="L44" s="466" t="inlineStr">
+        <is>
+          <t>Operatorパターンにより設定変更・アップグレードを容易にするため。</t>
+        </is>
+      </c>
+      <c r="M44" s="467" t="n"/>
+      <c r="N44" s="467" t="n"/>
+      <c r="O44" s="467" t="n"/>
+      <c r="P44" s="467" t="n"/>
+      <c r="Q44" s="467" t="n"/>
+      <c r="R44" s="467" t="n"/>
+      <c r="S44" s="467" t="n"/>
+      <c r="T44" s="467" t="n"/>
+      <c r="U44" s="467" t="n"/>
+      <c r="V44" s="467" t="n"/>
+      <c r="W44" s="468" t="n"/>
       <c r="X44" s="465" t="inlineStr">
         <is>
           <t>Tigera Operator</t>
@@ -13793,7 +14230,7 @@
       <c r="AU44" s="463" t="n"/>
       <c r="AV44" s="464" t="n"/>
     </row>
-    <row r="45" ht="29" customHeight="1" s="412">
+    <row r="45" ht="58" customHeight="1" s="412">
       <c r="B45" s="465" t="inlineStr">
         <is>
           <t>カプセル化方式</t>
@@ -13807,19 +14244,23 @@
       <c r="H45" s="463" t="n"/>
       <c r="I45" s="463" t="n"/>
       <c r="J45" s="463" t="n"/>
-      <c r="K45" s="463" t="n"/>
-      <c r="L45" s="463" t="n"/>
-      <c r="M45" s="463" t="n"/>
-      <c r="N45" s="463" t="n"/>
-      <c r="O45" s="463" t="n"/>
-      <c r="P45" s="463" t="n"/>
-      <c r="Q45" s="463" t="n"/>
-      <c r="R45" s="463" t="n"/>
-      <c r="S45" s="463" t="n"/>
-      <c r="T45" s="463" t="n"/>
-      <c r="U45" s="463" t="n"/>
-      <c r="V45" s="463" t="n"/>
-      <c r="W45" s="464" t="n"/>
+      <c r="K45" s="464" t="n"/>
+      <c r="L45" s="466" t="inlineStr">
+        <is>
+          <t>Pod間通信の転送方式。ノード間ネットワーク構成（同一L2セグメントか等）に応じて選択する必要があり、誤った方式だとPod間通信が到達しない、または性能が劣化する。</t>
+        </is>
+      </c>
+      <c r="M45" s="467" t="n"/>
+      <c r="N45" s="467" t="n"/>
+      <c r="O45" s="467" t="n"/>
+      <c r="P45" s="467" t="n"/>
+      <c r="Q45" s="467" t="n"/>
+      <c r="R45" s="467" t="n"/>
+      <c r="S45" s="467" t="n"/>
+      <c r="T45" s="467" t="n"/>
+      <c r="U45" s="467" t="n"/>
+      <c r="V45" s="467" t="n"/>
+      <c r="W45" s="468" t="n"/>
       <c r="X45" s="465" t="inlineStr">
         <is>
           <t>VXLAN（※要決定）</t>
@@ -13858,7 +14299,7 @@
       <c r="AU45" s="463" t="n"/>
       <c r="AV45" s="464" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="43.5" customHeight="1" s="412">
       <c r="B46" s="465" t="inlineStr">
         <is>
           <t>IPPool CIDR</t>
@@ -13872,19 +14313,23 @@
       <c r="H46" s="463" t="n"/>
       <c r="I46" s="463" t="n"/>
       <c r="J46" s="463" t="n"/>
-      <c r="K46" s="463" t="n"/>
-      <c r="L46" s="463" t="n"/>
-      <c r="M46" s="463" t="n"/>
-      <c r="N46" s="463" t="n"/>
-      <c r="O46" s="463" t="n"/>
-      <c r="P46" s="463" t="n"/>
-      <c r="Q46" s="463" t="n"/>
-      <c r="R46" s="463" t="n"/>
-      <c r="S46" s="463" t="n"/>
-      <c r="T46" s="463" t="n"/>
-      <c r="U46" s="463" t="n"/>
-      <c r="V46" s="463" t="n"/>
-      <c r="W46" s="464" t="n"/>
+      <c r="K46" s="464" t="n"/>
+      <c r="L46" s="466" t="inlineStr">
+        <is>
+          <t>PodへのIPアドレス払い出し範囲。kubeadmのpodSubnetと一致していないと、Podに正しくIPが割り当たらない。</t>
+        </is>
+      </c>
+      <c r="M46" s="467" t="n"/>
+      <c r="N46" s="467" t="n"/>
+      <c r="O46" s="467" t="n"/>
+      <c r="P46" s="467" t="n"/>
+      <c r="Q46" s="467" t="n"/>
+      <c r="R46" s="467" t="n"/>
+      <c r="S46" s="467" t="n"/>
+      <c r="T46" s="467" t="n"/>
+      <c r="U46" s="467" t="n"/>
+      <c r="V46" s="467" t="n"/>
+      <c r="W46" s="468" t="n"/>
       <c r="X46" s="465" t="inlineStr">
         <is>
           <t>192.168.0.0/16</t>
@@ -13937,19 +14382,23 @@
       <c r="H47" s="463" t="n"/>
       <c r="I47" s="463" t="n"/>
       <c r="J47" s="463" t="n"/>
-      <c r="K47" s="463" t="n"/>
-      <c r="L47" s="463" t="n"/>
-      <c r="M47" s="463" t="n"/>
-      <c r="N47" s="463" t="n"/>
-      <c r="O47" s="463" t="n"/>
-      <c r="P47" s="463" t="n"/>
-      <c r="Q47" s="463" t="n"/>
-      <c r="R47" s="463" t="n"/>
-      <c r="S47" s="463" t="n"/>
-      <c r="T47" s="463" t="n"/>
-      <c r="U47" s="463" t="n"/>
-      <c r="V47" s="463" t="n"/>
-      <c r="W47" s="464" t="n"/>
+      <c r="K47" s="464" t="n"/>
+      <c r="L47" s="466" t="inlineStr">
+        <is>
+          <t>1ノードに割り当てるIPアドレスブロックのサイズ。ノードあたりの最大Pod数に直結する。</t>
+        </is>
+      </c>
+      <c r="M47" s="467" t="n"/>
+      <c r="N47" s="467" t="n"/>
+      <c r="O47" s="467" t="n"/>
+      <c r="P47" s="467" t="n"/>
+      <c r="Q47" s="467" t="n"/>
+      <c r="R47" s="467" t="n"/>
+      <c r="S47" s="467" t="n"/>
+      <c r="T47" s="467" t="n"/>
+      <c r="U47" s="467" t="n"/>
+      <c r="V47" s="467" t="n"/>
+      <c r="W47" s="468" t="n"/>
       <c r="X47" s="465" t="inlineStr">
         <is>
           <t>/26</t>
@@ -13988,7 +14437,7 @@
       <c r="AU47" s="463" t="n"/>
       <c r="AV47" s="464" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="58" customHeight="1" s="412">
       <c r="B48" s="465" t="inlineStr">
         <is>
           <t>natOutgoing</t>
@@ -14002,19 +14451,23 @@
       <c r="H48" s="463" t="n"/>
       <c r="I48" s="463" t="n"/>
       <c r="J48" s="463" t="n"/>
-      <c r="K48" s="463" t="n"/>
-      <c r="L48" s="463" t="n"/>
-      <c r="M48" s="463" t="n"/>
-      <c r="N48" s="463" t="n"/>
-      <c r="O48" s="463" t="n"/>
-      <c r="P48" s="463" t="n"/>
-      <c r="Q48" s="463" t="n"/>
-      <c r="R48" s="463" t="n"/>
-      <c r="S48" s="463" t="n"/>
-      <c r="T48" s="463" t="n"/>
-      <c r="U48" s="463" t="n"/>
-      <c r="V48" s="463" t="n"/>
-      <c r="W48" s="464" t="n"/>
+      <c r="K48" s="464" t="n"/>
+      <c r="L48" s="466" t="inlineStr">
+        <is>
+          <t>Podからクラスタ外部への通信で送信元IPをノードIPにSNATしないと、外部ネットワーク側でPodのIPレンジを経路制御できない場合に通信が到達しない。</t>
+        </is>
+      </c>
+      <c r="M48" s="467" t="n"/>
+      <c r="N48" s="467" t="n"/>
+      <c r="O48" s="467" t="n"/>
+      <c r="P48" s="467" t="n"/>
+      <c r="Q48" s="467" t="n"/>
+      <c r="R48" s="467" t="n"/>
+      <c r="S48" s="467" t="n"/>
+      <c r="T48" s="467" t="n"/>
+      <c r="U48" s="467" t="n"/>
+      <c r="V48" s="467" t="n"/>
+      <c r="W48" s="468" t="n"/>
       <c r="X48" s="465" t="inlineStr">
         <is>
           <t>■有効　□無効</t>
@@ -14074,8 +14527,12 @@
       <c r="H51" s="463" t="n"/>
       <c r="I51" s="463" t="n"/>
       <c r="J51" s="463" t="n"/>
-      <c r="K51" s="463" t="n"/>
-      <c r="L51" s="463" t="n"/>
+      <c r="K51" s="464" t="n"/>
+      <c r="L51" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M51" s="463" t="n"/>
       <c r="N51" s="463" t="n"/>
       <c r="O51" s="463" t="n"/>
@@ -14125,7 +14582,7 @@
       <c r="AU51" s="463" t="n"/>
       <c r="AV51" s="464" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="43.5" customHeight="1" s="412">
       <c r="B52" s="465" t="inlineStr">
         <is>
           <t>バックエンド種別</t>
@@ -14139,19 +14596,23 @@
       <c r="H52" s="463" t="n"/>
       <c r="I52" s="463" t="n"/>
       <c r="J52" s="463" t="n"/>
-      <c r="K52" s="463" t="n"/>
-      <c r="L52" s="463" t="n"/>
-      <c r="M52" s="463" t="n"/>
-      <c r="N52" s="463" t="n"/>
-      <c r="O52" s="463" t="n"/>
-      <c r="P52" s="463" t="n"/>
-      <c r="Q52" s="463" t="n"/>
-      <c r="R52" s="463" t="n"/>
-      <c r="S52" s="463" t="n"/>
-      <c r="T52" s="463" t="n"/>
-      <c r="U52" s="463" t="n"/>
-      <c r="V52" s="463" t="n"/>
-      <c r="W52" s="464" t="n"/>
+      <c r="K52" s="464" t="n"/>
+      <c r="L52" s="466" t="inlineStr">
+        <is>
+          <t>Tridentが接続する実ストレージのプロトコルを決定する設定。外部ストレージ側の構成と一致させる必要がある。</t>
+        </is>
+      </c>
+      <c r="M52" s="467" t="n"/>
+      <c r="N52" s="467" t="n"/>
+      <c r="O52" s="467" t="n"/>
+      <c r="P52" s="467" t="n"/>
+      <c r="Q52" s="467" t="n"/>
+      <c r="R52" s="467" t="n"/>
+      <c r="S52" s="467" t="n"/>
+      <c r="T52" s="467" t="n"/>
+      <c r="U52" s="467" t="n"/>
+      <c r="V52" s="467" t="n"/>
+      <c r="W52" s="468" t="n"/>
       <c r="X52" s="465" t="inlineStr">
         <is>
           <t>ONTAP NAS（NFS）※要決定</t>
@@ -14190,7 +14651,7 @@
       <c r="AU52" s="463" t="n"/>
       <c r="AV52" s="464" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="29" customHeight="1" s="412">
       <c r="B53" s="465" t="inlineStr">
         <is>
           <t>StorageClass名</t>
@@ -14204,19 +14665,23 @@
       <c r="H53" s="463" t="n"/>
       <c r="I53" s="463" t="n"/>
       <c r="J53" s="463" t="n"/>
-      <c r="K53" s="463" t="n"/>
-      <c r="L53" s="463" t="n"/>
-      <c r="M53" s="463" t="n"/>
-      <c r="N53" s="463" t="n"/>
-      <c r="O53" s="463" t="n"/>
-      <c r="P53" s="463" t="n"/>
-      <c r="Q53" s="463" t="n"/>
-      <c r="R53" s="463" t="n"/>
-      <c r="S53" s="463" t="n"/>
-      <c r="T53" s="463" t="n"/>
-      <c r="U53" s="463" t="n"/>
-      <c r="V53" s="463" t="n"/>
-      <c r="W53" s="464" t="n"/>
+      <c r="K53" s="464" t="n"/>
+      <c r="L53" s="466" t="inlineStr">
+        <is>
+          <t>PVCがストレージを要求する際に参照するテンプレート名。</t>
+        </is>
+      </c>
+      <c r="M53" s="467" t="n"/>
+      <c r="N53" s="467" t="n"/>
+      <c r="O53" s="467" t="n"/>
+      <c r="P53" s="467" t="n"/>
+      <c r="Q53" s="467" t="n"/>
+      <c r="R53" s="467" t="n"/>
+      <c r="S53" s="467" t="n"/>
+      <c r="T53" s="467" t="n"/>
+      <c r="U53" s="467" t="n"/>
+      <c r="V53" s="467" t="n"/>
+      <c r="W53" s="468" t="n"/>
       <c r="X53" s="465" t="inlineStr">
         <is>
           <t>netapp-nas（例）</t>
@@ -14255,7 +14720,7 @@
       <c r="AU53" s="463" t="n"/>
       <c r="AV53" s="464" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="43.5" customHeight="1" s="412">
       <c r="B54" s="465" t="inlineStr">
         <is>
           <t>reclaimPolicy</t>
@@ -14269,19 +14734,23 @@
       <c r="H54" s="463" t="n"/>
       <c r="I54" s="463" t="n"/>
       <c r="J54" s="463" t="n"/>
-      <c r="K54" s="463" t="n"/>
-      <c r="L54" s="463" t="n"/>
-      <c r="M54" s="463" t="n"/>
-      <c r="N54" s="463" t="n"/>
-      <c r="O54" s="463" t="n"/>
-      <c r="P54" s="463" t="n"/>
-      <c r="Q54" s="463" t="n"/>
-      <c r="R54" s="463" t="n"/>
-      <c r="S54" s="463" t="n"/>
-      <c r="T54" s="463" t="n"/>
-      <c r="U54" s="463" t="n"/>
-      <c r="V54" s="463" t="n"/>
-      <c r="W54" s="464" t="n"/>
+      <c r="K54" s="464" t="n"/>
+      <c r="L54" s="466" t="inlineStr">
+        <is>
+          <t>PVC削除時に実データを自動削除するか保持するかを決める設定。誤削除対策が必要な場合はRetainを検討する。</t>
+        </is>
+      </c>
+      <c r="M54" s="467" t="n"/>
+      <c r="N54" s="467" t="n"/>
+      <c r="O54" s="467" t="n"/>
+      <c r="P54" s="467" t="n"/>
+      <c r="Q54" s="467" t="n"/>
+      <c r="R54" s="467" t="n"/>
+      <c r="S54" s="467" t="n"/>
+      <c r="T54" s="467" t="n"/>
+      <c r="U54" s="467" t="n"/>
+      <c r="V54" s="467" t="n"/>
+      <c r="W54" s="468" t="n"/>
       <c r="X54" s="465" t="inlineStr">
         <is>
           <t>Delete</t>
@@ -14320,7 +14789,7 @@
       <c r="AU54" s="463" t="n"/>
       <c r="AV54" s="464" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="58" customHeight="1" s="412">
       <c r="B55" s="465" t="inlineStr">
         <is>
           <t>volumeBindingMode</t>
@@ -14334,19 +14803,23 @@
       <c r="H55" s="463" t="n"/>
       <c r="I55" s="463" t="n"/>
       <c r="J55" s="463" t="n"/>
-      <c r="K55" s="463" t="n"/>
-      <c r="L55" s="463" t="n"/>
-      <c r="M55" s="463" t="n"/>
-      <c r="N55" s="463" t="n"/>
-      <c r="O55" s="463" t="n"/>
-      <c r="P55" s="463" t="n"/>
-      <c r="Q55" s="463" t="n"/>
-      <c r="R55" s="463" t="n"/>
-      <c r="S55" s="463" t="n"/>
-      <c r="T55" s="463" t="n"/>
-      <c r="U55" s="463" t="n"/>
-      <c r="V55" s="463" t="n"/>
-      <c r="W55" s="464" t="n"/>
+      <c r="K55" s="464" t="n"/>
+      <c r="L55" s="466" t="inlineStr">
+        <is>
+          <t>PVをいつ作成するか（PVC作成時 or Podスケジュール後）を決める設定。トポロジー制約がある場合はWaitForFirstConsumerが必要になる。</t>
+        </is>
+      </c>
+      <c r="M55" s="467" t="n"/>
+      <c r="N55" s="467" t="n"/>
+      <c r="O55" s="467" t="n"/>
+      <c r="P55" s="467" t="n"/>
+      <c r="Q55" s="467" t="n"/>
+      <c r="R55" s="467" t="n"/>
+      <c r="S55" s="467" t="n"/>
+      <c r="T55" s="467" t="n"/>
+      <c r="U55" s="467" t="n"/>
+      <c r="V55" s="467" t="n"/>
+      <c r="W55" s="468" t="n"/>
       <c r="X55" s="465" t="inlineStr">
         <is>
           <t>Immediate</t>
@@ -14385,7 +14858,7 @@
       <c r="AU55" s="463" t="n"/>
       <c r="AV55" s="464" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="29" customHeight="1" s="412">
       <c r="B56" s="465" t="inlineStr">
         <is>
           <t>allowVolumeExpansion</t>
@@ -14399,19 +14872,23 @@
       <c r="H56" s="463" t="n"/>
       <c r="I56" s="463" t="n"/>
       <c r="J56" s="463" t="n"/>
-      <c r="K56" s="463" t="n"/>
-      <c r="L56" s="463" t="n"/>
-      <c r="M56" s="463" t="n"/>
-      <c r="N56" s="463" t="n"/>
-      <c r="O56" s="463" t="n"/>
-      <c r="P56" s="463" t="n"/>
-      <c r="Q56" s="463" t="n"/>
-      <c r="R56" s="463" t="n"/>
-      <c r="S56" s="463" t="n"/>
-      <c r="T56" s="463" t="n"/>
-      <c r="U56" s="463" t="n"/>
-      <c r="V56" s="463" t="n"/>
-      <c r="W56" s="464" t="n"/>
+      <c r="K56" s="464" t="n"/>
+      <c r="L56" s="466" t="inlineStr">
+        <is>
+          <t>運用開始後にデータ量が増加した際、PVCサイズを拡張できるようにするため。</t>
+        </is>
+      </c>
+      <c r="M56" s="467" t="n"/>
+      <c r="N56" s="467" t="n"/>
+      <c r="O56" s="467" t="n"/>
+      <c r="P56" s="467" t="n"/>
+      <c r="Q56" s="467" t="n"/>
+      <c r="R56" s="467" t="n"/>
+      <c r="S56" s="467" t="n"/>
+      <c r="T56" s="467" t="n"/>
+      <c r="U56" s="467" t="n"/>
+      <c r="V56" s="467" t="n"/>
+      <c r="W56" s="468" t="n"/>
       <c r="X56" s="465" t="inlineStr">
         <is>
           <t>true</t>
@@ -14471,8 +14948,12 @@
       <c r="H59" s="463" t="n"/>
       <c r="I59" s="463" t="n"/>
       <c r="J59" s="463" t="n"/>
-      <c r="K59" s="463" t="n"/>
-      <c r="L59" s="463" t="n"/>
+      <c r="K59" s="464" t="n"/>
+      <c r="L59" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M59" s="463" t="n"/>
       <c r="N59" s="463" t="n"/>
       <c r="O59" s="463" t="n"/>
@@ -14522,7 +15003,7 @@
       <c r="AU59" s="463" t="n"/>
       <c r="AV59" s="464" t="n"/>
     </row>
-    <row r="60" ht="29" customHeight="1" s="412">
+    <row r="60" ht="58" customHeight="1" s="412">
       <c r="B60" s="465" t="inlineStr">
         <is>
           <t>NVIDIA Device Plugin</t>
@@ -14536,19 +15017,23 @@
       <c r="H60" s="463" t="n"/>
       <c r="I60" s="463" t="n"/>
       <c r="J60" s="463" t="n"/>
-      <c r="K60" s="463" t="n"/>
-      <c r="L60" s="463" t="n"/>
-      <c r="M60" s="463" t="n"/>
-      <c r="N60" s="463" t="n"/>
-      <c r="O60" s="463" t="n"/>
-      <c r="P60" s="463" t="n"/>
-      <c r="Q60" s="463" t="n"/>
-      <c r="R60" s="463" t="n"/>
-      <c r="S60" s="463" t="n"/>
-      <c r="T60" s="463" t="n"/>
-      <c r="U60" s="463" t="n"/>
-      <c r="V60" s="463" t="n"/>
-      <c r="W60" s="464" t="n"/>
+      <c r="K60" s="464" t="n"/>
+      <c r="L60" s="466" t="inlineStr">
+        <is>
+          <t>kubeletは標準ではGPUをリソースとして認識しない。Device Pluginを介して初めて、PodのrequestsやlimitsにGPUを指定できるようになるため。</t>
+        </is>
+      </c>
+      <c r="M60" s="467" t="n"/>
+      <c r="N60" s="467" t="n"/>
+      <c r="O60" s="467" t="n"/>
+      <c r="P60" s="467" t="n"/>
+      <c r="Q60" s="467" t="n"/>
+      <c r="R60" s="467" t="n"/>
+      <c r="S60" s="467" t="n"/>
+      <c r="T60" s="467" t="n"/>
+      <c r="U60" s="467" t="n"/>
+      <c r="V60" s="467" t="n"/>
+      <c r="W60" s="468" t="n"/>
       <c r="X60" s="465" t="inlineStr">
         <is>
           <t>DaemonSetとして導入</t>
@@ -14587,7 +15072,7 @@
       <c r="AU60" s="463" t="n"/>
       <c r="AV60" s="464" t="n"/>
     </row>
-    <row r="61" ht="29" customHeight="1" s="412">
+    <row r="61" ht="43.5" customHeight="1" s="412">
       <c r="B61" s="465" t="inlineStr">
         <is>
           <t>GPUノードtaint</t>
@@ -14601,19 +15086,23 @@
       <c r="H61" s="463" t="n"/>
       <c r="I61" s="463" t="n"/>
       <c r="J61" s="463" t="n"/>
-      <c r="K61" s="463" t="n"/>
-      <c r="L61" s="463" t="n"/>
-      <c r="M61" s="463" t="n"/>
-      <c r="N61" s="463" t="n"/>
-      <c r="O61" s="463" t="n"/>
-      <c r="P61" s="463" t="n"/>
-      <c r="Q61" s="463" t="n"/>
-      <c r="R61" s="463" t="n"/>
-      <c r="S61" s="463" t="n"/>
-      <c r="T61" s="463" t="n"/>
-      <c r="U61" s="463" t="n"/>
-      <c r="V61" s="463" t="n"/>
-      <c r="W61" s="464" t="n"/>
+      <c r="K61" s="464" t="n"/>
+      <c r="L61" s="466" t="inlineStr">
+        <is>
+          <t>GPUを使わない一般業務PodがGPU搭載ノードに配置され、貴重なGPUリソースを占有してしまうのを防ぐため。</t>
+        </is>
+      </c>
+      <c r="M61" s="467" t="n"/>
+      <c r="N61" s="467" t="n"/>
+      <c r="O61" s="467" t="n"/>
+      <c r="P61" s="467" t="n"/>
+      <c r="Q61" s="467" t="n"/>
+      <c r="R61" s="467" t="n"/>
+      <c r="S61" s="467" t="n"/>
+      <c r="T61" s="467" t="n"/>
+      <c r="U61" s="467" t="n"/>
+      <c r="V61" s="467" t="n"/>
+      <c r="W61" s="468" t="n"/>
       <c r="X61" s="465" t="inlineStr">
         <is>
           <t>nvidia.com/gpu=present:NoSchedule（※要決定）</t>
@@ -14673,8 +15162,12 @@
       <c r="H64" s="463" t="n"/>
       <c r="I64" s="463" t="n"/>
       <c r="J64" s="463" t="n"/>
-      <c r="K64" s="463" t="n"/>
-      <c r="L64" s="463" t="n"/>
+      <c r="K64" s="464" t="n"/>
+      <c r="L64" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M64" s="463" t="n"/>
       <c r="N64" s="463" t="n"/>
       <c r="O64" s="463" t="n"/>
@@ -14720,7 +15213,7 @@
       <c r="AU64" s="463" t="n"/>
       <c r="AV64" s="464" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="29" customHeight="1" s="412">
       <c r="B65" s="465" t="inlineStr">
         <is>
           <t>kube-system</t>
@@ -14734,19 +15227,23 @@
       <c r="H65" s="463" t="n"/>
       <c r="I65" s="463" t="n"/>
       <c r="J65" s="463" t="n"/>
-      <c r="K65" s="463" t="n"/>
-      <c r="L65" s="463" t="n"/>
-      <c r="M65" s="463" t="n"/>
-      <c r="N65" s="463" t="n"/>
-      <c r="O65" s="463" t="n"/>
-      <c r="P65" s="463" t="n"/>
-      <c r="Q65" s="463" t="n"/>
-      <c r="R65" s="463" t="n"/>
-      <c r="S65" s="463" t="n"/>
-      <c r="T65" s="463" t="n"/>
-      <c r="U65" s="463" t="n"/>
-      <c r="V65" s="463" t="n"/>
-      <c r="W65" s="464" t="n"/>
+      <c r="K65" s="464" t="n"/>
+      <c r="L65" s="466" t="inlineStr">
+        <is>
+          <t>Kubernetes自身の管理コンポーネントを配置する、システム標準のNamespace。</t>
+        </is>
+      </c>
+      <c r="M65" s="467" t="n"/>
+      <c r="N65" s="467" t="n"/>
+      <c r="O65" s="467" t="n"/>
+      <c r="P65" s="467" t="n"/>
+      <c r="Q65" s="467" t="n"/>
+      <c r="R65" s="467" t="n"/>
+      <c r="S65" s="467" t="n"/>
+      <c r="T65" s="467" t="n"/>
+      <c r="U65" s="467" t="n"/>
+      <c r="V65" s="467" t="n"/>
+      <c r="W65" s="468" t="n"/>
       <c r="X65" s="465" t="inlineStr">
         <is>
           <t>クラスタ管理コンポーネント</t>
@@ -14795,19 +15292,23 @@
       <c r="H66" s="463" t="n"/>
       <c r="I66" s="463" t="n"/>
       <c r="J66" s="463" t="n"/>
-      <c r="K66" s="463" t="n"/>
-      <c r="L66" s="463" t="n"/>
-      <c r="M66" s="463" t="n"/>
-      <c r="N66" s="463" t="n"/>
-      <c r="O66" s="463" t="n"/>
-      <c r="P66" s="463" t="n"/>
-      <c r="Q66" s="463" t="n"/>
-      <c r="R66" s="463" t="n"/>
-      <c r="S66" s="463" t="n"/>
-      <c r="T66" s="463" t="n"/>
-      <c r="U66" s="463" t="n"/>
-      <c r="V66" s="463" t="n"/>
-      <c r="W66" s="464" t="n"/>
+      <c r="K66" s="464" t="n"/>
+      <c r="L66" s="466" t="inlineStr">
+        <is>
+          <t>監視スタックを他ワークロードと分離し、RBAC権限の適用単位とするため。</t>
+        </is>
+      </c>
+      <c r="M66" s="467" t="n"/>
+      <c r="N66" s="467" t="n"/>
+      <c r="O66" s="467" t="n"/>
+      <c r="P66" s="467" t="n"/>
+      <c r="Q66" s="467" t="n"/>
+      <c r="R66" s="467" t="n"/>
+      <c r="S66" s="467" t="n"/>
+      <c r="T66" s="467" t="n"/>
+      <c r="U66" s="467" t="n"/>
+      <c r="V66" s="467" t="n"/>
+      <c r="W66" s="468" t="n"/>
       <c r="X66" s="465" t="inlineStr">
         <is>
           <t>監視スタック（kube-prometheus-stack）</t>
@@ -14842,7 +15343,7 @@
       <c r="AU66" s="463" t="n"/>
       <c r="AV66" s="464" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="43.5" customHeight="1" s="412">
       <c r="B67" s="465" t="inlineStr">
         <is>
           <t>ai-training</t>
@@ -14856,19 +15357,23 @@
       <c r="H67" s="463" t="n"/>
       <c r="I67" s="463" t="n"/>
       <c r="J67" s="463" t="n"/>
-      <c r="K67" s="463" t="n"/>
-      <c r="L67" s="463" t="n"/>
-      <c r="M67" s="463" t="n"/>
-      <c r="N67" s="463" t="n"/>
-      <c r="O67" s="463" t="n"/>
-      <c r="P67" s="463" t="n"/>
-      <c r="Q67" s="463" t="n"/>
-      <c r="R67" s="463" t="n"/>
-      <c r="S67" s="463" t="n"/>
-      <c r="T67" s="463" t="n"/>
-      <c r="U67" s="463" t="n"/>
-      <c r="V67" s="463" t="n"/>
-      <c r="W67" s="464" t="n"/>
+      <c r="K67" s="464" t="n"/>
+      <c r="L67" s="466" t="inlineStr">
+        <is>
+          <t>AI学習ワークロードを他用途と分離し、ResourceQuota等を独立して適用できるようにするため。</t>
+        </is>
+      </c>
+      <c r="M67" s="467" t="n"/>
+      <c r="N67" s="467" t="n"/>
+      <c r="O67" s="467" t="n"/>
+      <c r="P67" s="467" t="n"/>
+      <c r="Q67" s="467" t="n"/>
+      <c r="R67" s="467" t="n"/>
+      <c r="S67" s="467" t="n"/>
+      <c r="T67" s="467" t="n"/>
+      <c r="U67" s="467" t="n"/>
+      <c r="V67" s="467" t="n"/>
+      <c r="W67" s="468" t="n"/>
       <c r="X67" s="465" t="inlineStr">
         <is>
           <t>AI学習ジョブ・前処理バッチ（例）</t>
@@ -14917,19 +15422,23 @@
       <c r="H68" s="463" t="n"/>
       <c r="I68" s="463" t="n"/>
       <c r="J68" s="463" t="n"/>
-      <c r="K68" s="463" t="n"/>
-      <c r="L68" s="463" t="n"/>
-      <c r="M68" s="463" t="n"/>
-      <c r="N68" s="463" t="n"/>
-      <c r="O68" s="463" t="n"/>
-      <c r="P68" s="463" t="n"/>
-      <c r="Q68" s="463" t="n"/>
-      <c r="R68" s="463" t="n"/>
-      <c r="S68" s="463" t="n"/>
-      <c r="T68" s="463" t="n"/>
-      <c r="U68" s="463" t="n"/>
-      <c r="V68" s="463" t="n"/>
-      <c r="W68" s="464" t="n"/>
+      <c r="K68" s="464" t="n"/>
+      <c r="L68" s="466" t="inlineStr">
+        <is>
+          <t>分析ワークロードを他用途と分離するため。</t>
+        </is>
+      </c>
+      <c r="M68" s="467" t="n"/>
+      <c r="N68" s="467" t="n"/>
+      <c r="O68" s="467" t="n"/>
+      <c r="P68" s="467" t="n"/>
+      <c r="Q68" s="467" t="n"/>
+      <c r="R68" s="467" t="n"/>
+      <c r="S68" s="467" t="n"/>
+      <c r="T68" s="467" t="n"/>
+      <c r="U68" s="467" t="n"/>
+      <c r="V68" s="467" t="n"/>
+      <c r="W68" s="468" t="n"/>
       <c r="X68" s="465" t="inlineStr">
         <is>
           <t>分析環境・実験管理・API（例）</t>
@@ -14985,8 +15494,12 @@
       <c r="H71" s="463" t="n"/>
       <c r="I71" s="463" t="n"/>
       <c r="J71" s="463" t="n"/>
-      <c r="K71" s="463" t="n"/>
-      <c r="L71" s="463" t="n"/>
+      <c r="K71" s="464" t="n"/>
+      <c r="L71" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M71" s="463" t="n"/>
       <c r="N71" s="463" t="n"/>
       <c r="O71" s="463" t="n"/>
@@ -15032,7 +15545,7 @@
       <c r="AU71" s="463" t="n"/>
       <c r="AV71" s="464" t="n"/>
     </row>
-    <row r="72" ht="29" customHeight="1" s="412">
+    <row r="72" ht="43.5" customHeight="1" s="412">
       <c r="B72" s="465" t="inlineStr">
         <is>
           <t>Kubernetes管理者</t>
@@ -15046,19 +15559,23 @@
       <c r="H72" s="463" t="n"/>
       <c r="I72" s="463" t="n"/>
       <c r="J72" s="463" t="n"/>
-      <c r="K72" s="463" t="n"/>
-      <c r="L72" s="463" t="n"/>
-      <c r="M72" s="463" t="n"/>
-      <c r="N72" s="463" t="n"/>
-      <c r="O72" s="463" t="n"/>
-      <c r="P72" s="463" t="n"/>
-      <c r="Q72" s="463" t="n"/>
-      <c r="R72" s="463" t="n"/>
-      <c r="S72" s="463" t="n"/>
-      <c r="T72" s="463" t="n"/>
-      <c r="U72" s="463" t="n"/>
-      <c r="V72" s="463" t="n"/>
-      <c r="W72" s="464" t="n"/>
+      <c r="K72" s="464" t="n"/>
+      <c r="L72" s="466" t="inlineStr">
+        <is>
+          <t>cluster-admin相当の強い権限を持つ操作者を限定することで、誤操作・権限濫用のリスクを最小化するため（最小権限の原則）。</t>
+        </is>
+      </c>
+      <c r="M72" s="467" t="n"/>
+      <c r="N72" s="467" t="n"/>
+      <c r="O72" s="467" t="n"/>
+      <c r="P72" s="467" t="n"/>
+      <c r="Q72" s="467" t="n"/>
+      <c r="R72" s="467" t="n"/>
+      <c r="S72" s="467" t="n"/>
+      <c r="T72" s="467" t="n"/>
+      <c r="U72" s="467" t="n"/>
+      <c r="V72" s="467" t="n"/>
+      <c r="W72" s="468" t="n"/>
       <c r="X72" s="465" t="inlineStr">
         <is>
           <t>cluster-admin（ClusterRole）</t>
@@ -15093,7 +15610,7 @@
       <c r="AU72" s="463" t="n"/>
       <c r="AV72" s="464" t="n"/>
     </row>
-    <row r="73" ht="29" customHeight="1" s="412">
+    <row r="73" ht="43.5" customHeight="1" s="412">
       <c r="B73" s="465" t="inlineStr">
         <is>
           <t>運用担当者</t>
@@ -15107,19 +15624,23 @@
       <c r="H73" s="463" t="n"/>
       <c r="I73" s="463" t="n"/>
       <c r="J73" s="463" t="n"/>
-      <c r="K73" s="463" t="n"/>
-      <c r="L73" s="463" t="n"/>
-      <c r="M73" s="463" t="n"/>
-      <c r="N73" s="463" t="n"/>
-      <c r="O73" s="463" t="n"/>
-      <c r="P73" s="463" t="n"/>
-      <c r="Q73" s="463" t="n"/>
-      <c r="R73" s="463" t="n"/>
-      <c r="S73" s="463" t="n"/>
-      <c r="T73" s="463" t="n"/>
-      <c r="U73" s="463" t="n"/>
-      <c r="V73" s="463" t="n"/>
-      <c r="W73" s="464" t="n"/>
+      <c r="K73" s="464" t="n"/>
+      <c r="L73" s="466" t="inlineStr">
+        <is>
+          <t>Namespace単位の操作権限に限定することで、意図しない他Namespaceへの影響を防ぐため。</t>
+        </is>
+      </c>
+      <c r="M73" s="467" t="n"/>
+      <c r="N73" s="467" t="n"/>
+      <c r="O73" s="467" t="n"/>
+      <c r="P73" s="467" t="n"/>
+      <c r="Q73" s="467" t="n"/>
+      <c r="R73" s="467" t="n"/>
+      <c r="S73" s="467" t="n"/>
+      <c r="T73" s="467" t="n"/>
+      <c r="U73" s="467" t="n"/>
+      <c r="V73" s="467" t="n"/>
+      <c r="W73" s="468" t="n"/>
       <c r="X73" s="465" t="inlineStr">
         <is>
           <t>Namespace単位のadmin（RoleBinding）</t>
@@ -15154,7 +15675,7 @@
       <c r="AU73" s="463" t="n"/>
       <c r="AV73" s="464" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="29" customHeight="1" s="412">
       <c r="B74" s="465" t="inlineStr">
         <is>
           <t>アプリ利用者</t>
@@ -15168,19 +15689,23 @@
       <c r="H74" s="463" t="n"/>
       <c r="I74" s="463" t="n"/>
       <c r="J74" s="463" t="n"/>
-      <c r="K74" s="463" t="n"/>
-      <c r="L74" s="463" t="n"/>
-      <c r="M74" s="463" t="n"/>
-      <c r="N74" s="463" t="n"/>
-      <c r="O74" s="463" t="n"/>
-      <c r="P74" s="463" t="n"/>
-      <c r="Q74" s="463" t="n"/>
-      <c r="R74" s="463" t="n"/>
-      <c r="S74" s="463" t="n"/>
-      <c r="T74" s="463" t="n"/>
-      <c r="U74" s="463" t="n"/>
-      <c r="V74" s="463" t="n"/>
-      <c r="W74" s="464" t="n"/>
+      <c r="K74" s="464" t="n"/>
+      <c r="L74" s="466" t="inlineStr">
+        <is>
+          <t>参照のみの権限とすることで、意図しないリソース変更を防ぐため。</t>
+        </is>
+      </c>
+      <c r="M74" s="467" t="n"/>
+      <c r="N74" s="467" t="n"/>
+      <c r="O74" s="467" t="n"/>
+      <c r="P74" s="467" t="n"/>
+      <c r="Q74" s="467" t="n"/>
+      <c r="R74" s="467" t="n"/>
+      <c r="S74" s="467" t="n"/>
+      <c r="T74" s="467" t="n"/>
+      <c r="U74" s="467" t="n"/>
+      <c r="V74" s="467" t="n"/>
+      <c r="W74" s="468" t="n"/>
       <c r="X74" s="465" t="inlineStr">
         <is>
           <t>view（閲覧権限）</t>
@@ -15215,7 +15740,7 @@
       <c r="AU74" s="463" t="n"/>
       <c r="AV74" s="464" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="29" customHeight="1" s="412">
       <c r="B75" s="465" t="inlineStr">
         <is>
           <t>監視用ServiceAccount</t>
@@ -15229,19 +15754,23 @@
       <c r="H75" s="463" t="n"/>
       <c r="I75" s="463" t="n"/>
       <c r="J75" s="463" t="n"/>
-      <c r="K75" s="463" t="n"/>
-      <c r="L75" s="463" t="n"/>
-      <c r="M75" s="463" t="n"/>
-      <c r="N75" s="463" t="n"/>
-      <c r="O75" s="463" t="n"/>
-      <c r="P75" s="463" t="n"/>
-      <c r="Q75" s="463" t="n"/>
-      <c r="R75" s="463" t="n"/>
-      <c r="S75" s="463" t="n"/>
-      <c r="T75" s="463" t="n"/>
-      <c r="U75" s="463" t="n"/>
-      <c r="V75" s="463" t="n"/>
-      <c r="W75" s="464" t="n"/>
+      <c r="K75" s="464" t="n"/>
+      <c r="L75" s="466" t="inlineStr">
+        <is>
+          <t>監視コンポーネントはメトリクス参照のみでよく、それ以上の権限を持たせる必要が無いため。</t>
+        </is>
+      </c>
+      <c r="M75" s="467" t="n"/>
+      <c r="N75" s="467" t="n"/>
+      <c r="O75" s="467" t="n"/>
+      <c r="P75" s="467" t="n"/>
+      <c r="Q75" s="467" t="n"/>
+      <c r="R75" s="467" t="n"/>
+      <c r="S75" s="467" t="n"/>
+      <c r="T75" s="467" t="n"/>
+      <c r="U75" s="467" t="n"/>
+      <c r="V75" s="467" t="n"/>
+      <c r="W75" s="468" t="n"/>
       <c r="X75" s="465" t="inlineStr">
         <is>
           <t>view相当（参照系のみ）</t>
@@ -15297,8 +15826,12 @@
       <c r="H78" s="463" t="n"/>
       <c r="I78" s="463" t="n"/>
       <c r="J78" s="463" t="n"/>
-      <c r="K78" s="463" t="n"/>
-      <c r="L78" s="463" t="n"/>
+      <c r="K78" s="464" t="n"/>
+      <c r="L78" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M78" s="463" t="n"/>
       <c r="N78" s="463" t="n"/>
       <c r="O78" s="463" t="n"/>
@@ -15348,7 +15881,7 @@
       <c r="AU78" s="463" t="n"/>
       <c r="AV78" s="464" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="43.5" customHeight="1" s="412">
       <c r="B79" s="465" t="inlineStr">
         <is>
           <t>デプロイ方式 / Namespace</t>
@@ -15362,19 +15895,23 @@
       <c r="H79" s="463" t="n"/>
       <c r="I79" s="463" t="n"/>
       <c r="J79" s="463" t="n"/>
-      <c r="K79" s="463" t="n"/>
-      <c r="L79" s="463" t="n"/>
-      <c r="M79" s="463" t="n"/>
-      <c r="N79" s="463" t="n"/>
-      <c r="O79" s="463" t="n"/>
-      <c r="P79" s="463" t="n"/>
-      <c r="Q79" s="463" t="n"/>
-      <c r="R79" s="463" t="n"/>
-      <c r="S79" s="463" t="n"/>
-      <c r="T79" s="463" t="n"/>
-      <c r="U79" s="463" t="n"/>
-      <c r="V79" s="463" t="n"/>
-      <c r="W79" s="464" t="n"/>
+      <c r="K79" s="464" t="n"/>
+      <c r="L79" s="466" t="inlineStr">
+        <is>
+          <t>Helm Chartとして一括デプロイすることで、監視に必要な複数コンポーネントの導入・アップグレードを一元管理するため。</t>
+        </is>
+      </c>
+      <c r="M79" s="467" t="n"/>
+      <c r="N79" s="467" t="n"/>
+      <c r="O79" s="467" t="n"/>
+      <c r="P79" s="467" t="n"/>
+      <c r="Q79" s="467" t="n"/>
+      <c r="R79" s="467" t="n"/>
+      <c r="S79" s="467" t="n"/>
+      <c r="T79" s="467" t="n"/>
+      <c r="U79" s="467" t="n"/>
+      <c r="V79" s="467" t="n"/>
+      <c r="W79" s="468" t="n"/>
       <c r="X79" s="465" t="inlineStr">
         <is>
           <t>Helmチャート / monitoring</t>
@@ -15413,7 +15950,7 @@
       <c r="AU79" s="463" t="n"/>
       <c r="AV79" s="464" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="43.5" customHeight="1" s="412">
       <c r="B80" s="465" t="inlineStr">
         <is>
           <t>Prometheusメトリクス保存期間</t>
@@ -15427,19 +15964,23 @@
       <c r="H80" s="463" t="n"/>
       <c r="I80" s="463" t="n"/>
       <c r="J80" s="463" t="n"/>
-      <c r="K80" s="463" t="n"/>
-      <c r="L80" s="463" t="n"/>
-      <c r="M80" s="463" t="n"/>
-      <c r="N80" s="463" t="n"/>
-      <c r="O80" s="463" t="n"/>
-      <c r="P80" s="463" t="n"/>
-      <c r="Q80" s="463" t="n"/>
-      <c r="R80" s="463" t="n"/>
-      <c r="S80" s="463" t="n"/>
-      <c r="T80" s="463" t="n"/>
-      <c r="U80" s="463" t="n"/>
-      <c r="V80" s="463" t="n"/>
-      <c r="W80" s="464" t="n"/>
+      <c r="K80" s="464" t="n"/>
+      <c r="L80" s="466" t="inlineStr">
+        <is>
+          <t>長すぎると必要ストレージ容量が増大し、短すぎると障害調査に必要な過去データが失われるため、要件に応じたバランスが必要。</t>
+        </is>
+      </c>
+      <c r="M80" s="467" t="n"/>
+      <c r="N80" s="467" t="n"/>
+      <c r="O80" s="467" t="n"/>
+      <c r="P80" s="467" t="n"/>
+      <c r="Q80" s="467" t="n"/>
+      <c r="R80" s="467" t="n"/>
+      <c r="S80" s="467" t="n"/>
+      <c r="T80" s="467" t="n"/>
+      <c r="U80" s="467" t="n"/>
+      <c r="V80" s="467" t="n"/>
+      <c r="W80" s="468" t="n"/>
       <c r="X80" s="465" t="inlineStr">
         <is>
           <t>15d（※要決定）</t>
@@ -15478,7 +16019,7 @@
       <c r="AU80" s="463" t="n"/>
       <c r="AV80" s="464" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="43.5" customHeight="1" s="412">
       <c r="B81" s="465" t="inlineStr">
         <is>
           <t>Prometheus用PVサイズ</t>
@@ -15492,19 +16033,23 @@
       <c r="H81" s="463" t="n"/>
       <c r="I81" s="463" t="n"/>
       <c r="J81" s="463" t="n"/>
-      <c r="K81" s="463" t="n"/>
-      <c r="L81" s="463" t="n"/>
-      <c r="M81" s="463" t="n"/>
-      <c r="N81" s="463" t="n"/>
-      <c r="O81" s="463" t="n"/>
-      <c r="P81" s="463" t="n"/>
-      <c r="Q81" s="463" t="n"/>
-      <c r="R81" s="463" t="n"/>
-      <c r="S81" s="463" t="n"/>
-      <c r="T81" s="463" t="n"/>
-      <c r="U81" s="463" t="n"/>
-      <c r="V81" s="463" t="n"/>
-      <c r="W81" s="464" t="n"/>
+      <c r="K81" s="464" t="n"/>
+      <c r="L81" s="466" t="inlineStr">
+        <is>
+          <t>保存期間・ノード数・Pod数から見積もる必要がある容量。不足するとメトリクス収集が停止するリスクがある。</t>
+        </is>
+      </c>
+      <c r="M81" s="467" t="n"/>
+      <c r="N81" s="467" t="n"/>
+      <c r="O81" s="467" t="n"/>
+      <c r="P81" s="467" t="n"/>
+      <c r="Q81" s="467" t="n"/>
+      <c r="R81" s="467" t="n"/>
+      <c r="S81" s="467" t="n"/>
+      <c r="T81" s="467" t="n"/>
+      <c r="U81" s="467" t="n"/>
+      <c r="V81" s="467" t="n"/>
+      <c r="W81" s="468" t="n"/>
       <c r="X81" s="465" t="inlineStr">
         <is>
           <t>100GB（※要決定）</t>
@@ -15543,7 +16088,7 @@
       <c r="AU81" s="463" t="n"/>
       <c r="AV81" s="464" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="43.5" customHeight="1" s="412">
       <c r="B82" s="465" t="inlineStr">
         <is>
           <t>Alertmanager通知先</t>
@@ -15557,19 +16102,23 @@
       <c r="H82" s="463" t="n"/>
       <c r="I82" s="463" t="n"/>
       <c r="J82" s="463" t="n"/>
-      <c r="K82" s="463" t="n"/>
-      <c r="L82" s="463" t="n"/>
-      <c r="M82" s="463" t="n"/>
-      <c r="N82" s="463" t="n"/>
-      <c r="O82" s="463" t="n"/>
-      <c r="P82" s="463" t="n"/>
-      <c r="Q82" s="463" t="n"/>
-      <c r="R82" s="463" t="n"/>
-      <c r="S82" s="463" t="n"/>
-      <c r="T82" s="463" t="n"/>
-      <c r="U82" s="463" t="n"/>
-      <c r="V82" s="463" t="n"/>
-      <c r="W82" s="464" t="n"/>
+      <c r="K82" s="464" t="n"/>
+      <c r="L82" s="466" t="inlineStr">
+        <is>
+          <t>アラートルールが定義されていても、通知先の設定が誤っていると障害発生時に運用担当者が気づけないため。</t>
+        </is>
+      </c>
+      <c r="M82" s="467" t="n"/>
+      <c r="N82" s="467" t="n"/>
+      <c r="O82" s="467" t="n"/>
+      <c r="P82" s="467" t="n"/>
+      <c r="Q82" s="467" t="n"/>
+      <c r="R82" s="467" t="n"/>
+      <c r="S82" s="467" t="n"/>
+      <c r="T82" s="467" t="n"/>
+      <c r="U82" s="467" t="n"/>
+      <c r="V82" s="467" t="n"/>
+      <c r="W82" s="468" t="n"/>
       <c r="X82" s="465" t="inlineStr">
         <is>
           <t>メール（SMTPサーバー/宛先は※要決定）</t>
@@ -15608,7 +16157,7 @@
       <c r="AU82" s="463" t="n"/>
       <c r="AV82" s="464" t="n"/>
     </row>
-    <row r="83" ht="29" customHeight="1" s="412">
+    <row r="83" ht="43.5" customHeight="1" s="412">
       <c r="B83" s="465" t="inlineStr">
         <is>
           <t>DCGM Exporter</t>
@@ -15622,19 +16171,23 @@
       <c r="H83" s="463" t="n"/>
       <c r="I83" s="463" t="n"/>
       <c r="J83" s="463" t="n"/>
-      <c r="K83" s="463" t="n"/>
-      <c r="L83" s="463" t="n"/>
-      <c r="M83" s="463" t="n"/>
-      <c r="N83" s="463" t="n"/>
-      <c r="O83" s="463" t="n"/>
-      <c r="P83" s="463" t="n"/>
-      <c r="Q83" s="463" t="n"/>
-      <c r="R83" s="463" t="n"/>
-      <c r="S83" s="463" t="n"/>
-      <c r="T83" s="463" t="n"/>
-      <c r="U83" s="463" t="n"/>
-      <c r="V83" s="463" t="n"/>
-      <c r="W83" s="464" t="n"/>
+      <c r="K83" s="464" t="n"/>
+      <c r="L83" s="466" t="inlineStr">
+        <is>
+          <t>標準の監視スタックにはGPU固有のメトリクス（使用率・温度等）を収集する仕組みが含まれていないため、別途追加が必要。</t>
+        </is>
+      </c>
+      <c r="M83" s="467" t="n"/>
+      <c r="N83" s="467" t="n"/>
+      <c r="O83" s="467" t="n"/>
+      <c r="P83" s="467" t="n"/>
+      <c r="Q83" s="467" t="n"/>
+      <c r="R83" s="467" t="n"/>
+      <c r="S83" s="467" t="n"/>
+      <c r="T83" s="467" t="n"/>
+      <c r="U83" s="467" t="n"/>
+      <c r="V83" s="467" t="n"/>
+      <c r="W83" s="468" t="n"/>
       <c r="X83" s="465" t="inlineStr">
         <is>
           <t>Worker Nodeのみ配置（nodeSelector/toleration）</t>
@@ -15694,8 +16247,12 @@
       <c r="H86" s="463" t="n"/>
       <c r="I86" s="463" t="n"/>
       <c r="J86" s="463" t="n"/>
-      <c r="K86" s="463" t="n"/>
-      <c r="L86" s="463" t="n"/>
+      <c r="K86" s="464" t="n"/>
+      <c r="L86" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M86" s="463" t="n"/>
       <c r="N86" s="463" t="n"/>
       <c r="O86" s="463" t="n"/>
@@ -15759,19 +16316,23 @@
       <c r="H87" s="463" t="n"/>
       <c r="I87" s="463" t="n"/>
       <c r="J87" s="463" t="n"/>
-      <c r="K87" s="463" t="n"/>
-      <c r="L87" s="463" t="n"/>
-      <c r="M87" s="463" t="n"/>
-      <c r="N87" s="463" t="n"/>
-      <c r="O87" s="463" t="n"/>
-      <c r="P87" s="463" t="n"/>
-      <c r="Q87" s="463" t="n"/>
-      <c r="R87" s="463" t="n"/>
-      <c r="S87" s="463" t="n"/>
-      <c r="T87" s="463" t="n"/>
-      <c r="U87" s="463" t="n"/>
-      <c r="V87" s="463" t="n"/>
-      <c r="W87" s="464" t="n"/>
+      <c r="K87" s="464" t="n"/>
+      <c r="L87" s="466" t="inlineStr">
+        <is>
+          <t>業務PodがControl Planeに配置されると、クラスタ管理機能のリソースを圧迫し、クラスタ全体の安定性に影響するため、配置を制限する。</t>
+        </is>
+      </c>
+      <c r="M87" s="467" t="n"/>
+      <c r="N87" s="467" t="n"/>
+      <c r="O87" s="467" t="n"/>
+      <c r="P87" s="467" t="n"/>
+      <c r="Q87" s="467" t="n"/>
+      <c r="R87" s="467" t="n"/>
+      <c r="S87" s="467" t="n"/>
+      <c r="T87" s="467" t="n"/>
+      <c r="U87" s="467" t="n"/>
+      <c r="V87" s="467" t="n"/>
+      <c r="W87" s="468" t="n"/>
       <c r="X87" s="465" t="inlineStr">
         <is>
           <t>node-role.kubernetes.io/control-plane:NoSchedule（維持）</t>
@@ -15810,7 +16371,7 @@
       <c r="AU87" s="463" t="n"/>
       <c r="AV87" s="464" t="n"/>
     </row>
-    <row r="88" ht="29" customHeight="1" s="412">
+    <row r="88" ht="43.5" customHeight="1" s="412">
       <c r="B88" s="465" t="inlineStr">
         <is>
           <t>業務Podのrequests/limits</t>
@@ -15824,19 +16385,23 @@
       <c r="H88" s="463" t="n"/>
       <c r="I88" s="463" t="n"/>
       <c r="J88" s="463" t="n"/>
-      <c r="K88" s="463" t="n"/>
-      <c r="L88" s="463" t="n"/>
-      <c r="M88" s="463" t="n"/>
-      <c r="N88" s="463" t="n"/>
-      <c r="O88" s="463" t="n"/>
-      <c r="P88" s="463" t="n"/>
-      <c r="Q88" s="463" t="n"/>
-      <c r="R88" s="463" t="n"/>
-      <c r="S88" s="463" t="n"/>
-      <c r="T88" s="463" t="n"/>
-      <c r="U88" s="463" t="n"/>
-      <c r="V88" s="463" t="n"/>
-      <c r="W88" s="464" t="n"/>
+      <c r="K88" s="464" t="n"/>
+      <c r="L88" s="466" t="inlineStr">
+        <is>
+          <t>設定が無いとノードリソースの消費が予測不能になり、他Podへ影響するリソース枯渇やスケジューリング判断の誤りにつながるため。</t>
+        </is>
+      </c>
+      <c r="M88" s="467" t="n"/>
+      <c r="N88" s="467" t="n"/>
+      <c r="O88" s="467" t="n"/>
+      <c r="P88" s="467" t="n"/>
+      <c r="Q88" s="467" t="n"/>
+      <c r="R88" s="467" t="n"/>
+      <c r="S88" s="467" t="n"/>
+      <c r="T88" s="467" t="n"/>
+      <c r="U88" s="467" t="n"/>
+      <c r="V88" s="467" t="n"/>
+      <c r="W88" s="468" t="n"/>
       <c r="X88" s="465" t="inlineStr">
         <is>
           <t>全Podで設定必須</t>
@@ -15875,7 +16440,7 @@
       <c r="AU88" s="463" t="n"/>
       <c r="AV88" s="464" t="n"/>
     </row>
-    <row r="89" ht="29" customHeight="1" s="412">
+    <row r="89" ht="43.5" customHeight="1" s="412">
       <c r="B89" s="465" t="inlineStr">
         <is>
           <t>Pod Anti-Affinity</t>
@@ -15889,19 +16454,23 @@
       <c r="H89" s="463" t="n"/>
       <c r="I89" s="463" t="n"/>
       <c r="J89" s="463" t="n"/>
-      <c r="K89" s="463" t="n"/>
-      <c r="L89" s="463" t="n"/>
-      <c r="M89" s="463" t="n"/>
-      <c r="N89" s="463" t="n"/>
-      <c r="O89" s="463" t="n"/>
-      <c r="P89" s="463" t="n"/>
-      <c r="Q89" s="463" t="n"/>
-      <c r="R89" s="463" t="n"/>
-      <c r="S89" s="463" t="n"/>
-      <c r="T89" s="463" t="n"/>
-      <c r="U89" s="463" t="n"/>
-      <c r="V89" s="463" t="n"/>
-      <c r="W89" s="464" t="n"/>
+      <c r="K89" s="464" t="n"/>
+      <c r="L89" s="466" t="inlineStr">
+        <is>
+          <t>同一DeploymentのPodが同一ノードに集中して配置されると、そのノード障害時にサービス全断となるため、分散配置で可用性を確保する。</t>
+        </is>
+      </c>
+      <c r="M89" s="467" t="n"/>
+      <c r="N89" s="467" t="n"/>
+      <c r="O89" s="467" t="n"/>
+      <c r="P89" s="467" t="n"/>
+      <c r="Q89" s="467" t="n"/>
+      <c r="R89" s="467" t="n"/>
+      <c r="S89" s="467" t="n"/>
+      <c r="T89" s="467" t="n"/>
+      <c r="U89" s="467" t="n"/>
+      <c r="V89" s="467" t="n"/>
+      <c r="W89" s="468" t="n"/>
       <c r="X89" s="465" t="inlineStr">
         <is>
           <t>同一DeploymentのPodをWorker間で分散</t>
@@ -15961,8 +16530,12 @@
       <c r="H92" s="463" t="n"/>
       <c r="I92" s="463" t="n"/>
       <c r="J92" s="463" t="n"/>
-      <c r="K92" s="463" t="n"/>
-      <c r="L92" s="463" t="n"/>
+      <c r="K92" s="464" t="n"/>
+      <c r="L92" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M92" s="463" t="n"/>
       <c r="N92" s="463" t="n"/>
       <c r="O92" s="463" t="n"/>
@@ -16012,7 +16585,7 @@
       <c r="AU92" s="463" t="n"/>
       <c r="AV92" s="464" t="n"/>
     </row>
-    <row r="93" ht="29" customHeight="1" s="412">
+    <row r="93" ht="43.5" customHeight="1" s="412">
       <c r="B93" s="465" t="inlineStr">
         <is>
           <t>etcdスナップショット</t>
@@ -16026,19 +16599,23 @@
       <c r="H93" s="463" t="n"/>
       <c r="I93" s="463" t="n"/>
       <c r="J93" s="463" t="n"/>
-      <c r="K93" s="463" t="n"/>
-      <c r="L93" s="463" t="n"/>
-      <c r="M93" s="463" t="n"/>
-      <c r="N93" s="463" t="n"/>
-      <c r="O93" s="463" t="n"/>
-      <c r="P93" s="463" t="n"/>
-      <c r="Q93" s="463" t="n"/>
-      <c r="R93" s="463" t="n"/>
-      <c r="S93" s="463" t="n"/>
-      <c r="T93" s="463" t="n"/>
-      <c r="U93" s="463" t="n"/>
-      <c r="V93" s="463" t="n"/>
-      <c r="W93" s="464" t="n"/>
+      <c r="K93" s="464" t="n"/>
+      <c r="L93" s="466" t="inlineStr">
+        <is>
+          <t>etcdにはクラスタの全リソース定義が格納されており、これが失われるとクラスタが復旧不能になるため、定期的なバックアップが必須となる。</t>
+        </is>
+      </c>
+      <c r="M93" s="467" t="n"/>
+      <c r="N93" s="467" t="n"/>
+      <c r="O93" s="467" t="n"/>
+      <c r="P93" s="467" t="n"/>
+      <c r="Q93" s="467" t="n"/>
+      <c r="R93" s="467" t="n"/>
+      <c r="S93" s="467" t="n"/>
+      <c r="T93" s="467" t="n"/>
+      <c r="U93" s="467" t="n"/>
+      <c r="V93" s="467" t="n"/>
+      <c r="W93" s="468" t="n"/>
       <c r="X93" s="465" t="inlineStr">
         <is>
           <t>etcdctl snapshot save / 毎日00:00</t>
@@ -16077,7 +16654,7 @@
       <c r="AU93" s="463" t="n"/>
       <c r="AV93" s="464" t="n"/>
     </row>
-    <row r="94">
+    <row r="94" ht="58" customHeight="1" s="412">
       <c r="B94" s="465" t="inlineStr">
         <is>
           <t>OSバックアップ</t>
@@ -16091,19 +16668,23 @@
       <c r="H94" s="463" t="n"/>
       <c r="I94" s="463" t="n"/>
       <c r="J94" s="463" t="n"/>
-      <c r="K94" s="463" t="n"/>
-      <c r="L94" s="463" t="n"/>
-      <c r="M94" s="463" t="n"/>
-      <c r="N94" s="463" t="n"/>
-      <c r="O94" s="463" t="n"/>
-      <c r="P94" s="463" t="n"/>
-      <c r="Q94" s="463" t="n"/>
-      <c r="R94" s="463" t="n"/>
-      <c r="S94" s="463" t="n"/>
-      <c r="T94" s="463" t="n"/>
-      <c r="U94" s="463" t="n"/>
-      <c r="V94" s="463" t="n"/>
-      <c r="W94" s="464" t="n"/>
+      <c r="K94" s="464" t="n"/>
+      <c r="L94" s="466" t="inlineStr">
+        <is>
+          <t>etcdバックアップはクラスタの構成情報のみが対象であり、OS自体の障害（ディスク故障等）はカバーしないため、別途OS層のバックアップが必要となる。</t>
+        </is>
+      </c>
+      <c r="M94" s="467" t="n"/>
+      <c r="N94" s="467" t="n"/>
+      <c r="O94" s="467" t="n"/>
+      <c r="P94" s="467" t="n"/>
+      <c r="Q94" s="467" t="n"/>
+      <c r="R94" s="467" t="n"/>
+      <c r="S94" s="467" t="n"/>
+      <c r="T94" s="467" t="n"/>
+      <c r="U94" s="467" t="n"/>
+      <c r="V94" s="467" t="n"/>
+      <c r="W94" s="468" t="n"/>
       <c r="X94" s="465" t="inlineStr">
         <is>
           <t>外部バックアップソフトウェアによる日次取得</t>
@@ -16150,272 +16731,337 @@
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="466" t="inlineStr">
+      <c r="B97" s="469" t="inlineStr">
         <is>
           <t>controlPlaneEndpoint・podSubnet・serviceSubnetは構築後に変更できないため、構築前に必ず確定させること。</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="466" t="inlineStr">
+      <c r="B98" s="469" t="inlineStr">
         <is>
           <t>「※要決定」項目は入門コース質問一覧の回答および詳細設計で確定させ、本書を更新すること。</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="466" t="inlineStr">
+      <c r="B99" s="469" t="inlineStr">
         <is>
           <t>認証情報（Grafana管理者パスワード等）は本書に記載せず、別途パスワード管理台帳で管理する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="245">
+  <mergeCells count="310">
+    <mergeCell ref="AE34:AK34"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="B72:K72"/>
+    <mergeCell ref="AE31:AK31"/>
+    <mergeCell ref="AL72:AV72"/>
+    <mergeCell ref="AL14:AV14"/>
+    <mergeCell ref="B17:K17"/>
+    <mergeCell ref="L32:W32"/>
+    <mergeCell ref="B88:K88"/>
+    <mergeCell ref="B82:K82"/>
+    <mergeCell ref="L47:W47"/>
+    <mergeCell ref="B83:K83"/>
+    <mergeCell ref="AL27:AV27"/>
+    <mergeCell ref="X7:AK7"/>
+    <mergeCell ref="X21:AD21"/>
+    <mergeCell ref="AL25:AV25"/>
+    <mergeCell ref="L52:W52"/>
+    <mergeCell ref="X23:AD23"/>
+    <mergeCell ref="X73:AK73"/>
+    <mergeCell ref="X16:AD16"/>
+    <mergeCell ref="X87:AD87"/>
+    <mergeCell ref="AE52:AK52"/>
+    <mergeCell ref="AE39:AK39"/>
+    <mergeCell ref="AL38:AV38"/>
+    <mergeCell ref="L78:W78"/>
+    <mergeCell ref="AE53:AK53"/>
+    <mergeCell ref="X93:AD93"/>
+    <mergeCell ref="AL40:AV40"/>
+    <mergeCell ref="AL15:AV15"/>
+    <mergeCell ref="L55:W55"/>
+    <mergeCell ref="B25:K25"/>
+    <mergeCell ref="B22:K22"/>
+    <mergeCell ref="B93:K93"/>
+    <mergeCell ref="B86:K86"/>
+    <mergeCell ref="AL93:AV93"/>
+    <mergeCell ref="AL43:AV43"/>
+    <mergeCell ref="AL35:AV35"/>
+    <mergeCell ref="L66:W66"/>
+    <mergeCell ref="X10:AK10"/>
+    <mergeCell ref="B38:K38"/>
+    <mergeCell ref="X24:AD24"/>
+    <mergeCell ref="L53:W53"/>
+    <mergeCell ref="X89:AD89"/>
+    <mergeCell ref="L68:W68"/>
+    <mergeCell ref="AE60:AK60"/>
+    <mergeCell ref="X88:AD88"/>
+    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="X26:AD26"/>
+    <mergeCell ref="B15:K15"/>
+    <mergeCell ref="AL59:AV59"/>
+    <mergeCell ref="AL46:AV46"/>
+    <mergeCell ref="B33:K33"/>
+    <mergeCell ref="AE80:AK80"/>
+    <mergeCell ref="B79:K79"/>
+    <mergeCell ref="AL61:AV61"/>
+    <mergeCell ref="AE55:AK55"/>
+    <mergeCell ref="X27:AD27"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="L79:W79"/>
+    <mergeCell ref="B81:K81"/>
+    <mergeCell ref="AE46:AK46"/>
+    <mergeCell ref="L21:W21"/>
+    <mergeCell ref="L81:W81"/>
+    <mergeCell ref="AL56:AV56"/>
+    <mergeCell ref="L16:W16"/>
+    <mergeCell ref="B34:K34"/>
+    <mergeCell ref="X20:AD20"/>
+    <mergeCell ref="B28:K28"/>
+    <mergeCell ref="X14:AD14"/>
     <mergeCell ref="X38:AD38"/>
-    <mergeCell ref="X94:AD94"/>
-    <mergeCell ref="B10:W10"/>
     <mergeCell ref="AL34:AV34"/>
     <mergeCell ref="AL9:AV9"/>
+    <mergeCell ref="B92:K92"/>
+    <mergeCell ref="L74:W74"/>
+    <mergeCell ref="L92:W92"/>
+    <mergeCell ref="AL11:AV11"/>
+    <mergeCell ref="B94:K94"/>
+    <mergeCell ref="AE51:AK51"/>
+    <mergeCell ref="B54:K54"/>
+    <mergeCell ref="X40:AD40"/>
+    <mergeCell ref="L6:W6"/>
+    <mergeCell ref="B56:K56"/>
+    <mergeCell ref="B43:K43"/>
+    <mergeCell ref="AE21:AK21"/>
+    <mergeCell ref="AE92:AK92"/>
+    <mergeCell ref="AE23:AK23"/>
+    <mergeCell ref="X75:AK75"/>
+    <mergeCell ref="AL64:AV64"/>
+    <mergeCell ref="AL51:AV51"/>
+    <mergeCell ref="AE87:AK87"/>
+    <mergeCell ref="L87:W87"/>
+    <mergeCell ref="X45:AD45"/>
+    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="L24:W24"/>
+    <mergeCell ref="L89:W89"/>
+    <mergeCell ref="L88:W88"/>
+    <mergeCell ref="X59:AD59"/>
+    <mergeCell ref="L26:W26"/>
+    <mergeCell ref="X46:AD46"/>
+    <mergeCell ref="B75:K75"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="B31:K31"/>
+    <mergeCell ref="AL75:AV75"/>
+    <mergeCell ref="X65:AK65"/>
+    <mergeCell ref="B39:K39"/>
+    <mergeCell ref="AL52:AV52"/>
+    <mergeCell ref="AL39:AV39"/>
+    <mergeCell ref="B65:K65"/>
+    <mergeCell ref="L14:W14"/>
+    <mergeCell ref="X51:AD51"/>
+    <mergeCell ref="AE24:AK24"/>
+    <mergeCell ref="AL65:AV65"/>
+    <mergeCell ref="AE89:AK89"/>
+    <mergeCell ref="AE26:AK26"/>
+    <mergeCell ref="AL7:AV7"/>
+    <mergeCell ref="B2:AV2"/>
+    <mergeCell ref="X61:AD61"/>
+    <mergeCell ref="L27:W27"/>
+    <mergeCell ref="AL83:AV83"/>
+    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="AL20:AV20"/>
+    <mergeCell ref="AE44:AK44"/>
+    <mergeCell ref="B78:K78"/>
+    <mergeCell ref="X71:AK71"/>
+    <mergeCell ref="AL60:AV60"/>
+    <mergeCell ref="AL22:AV22"/>
+    <mergeCell ref="AL78:AV78"/>
+    <mergeCell ref="B55:K55"/>
+    <mergeCell ref="L45:W45"/>
+    <mergeCell ref="AL80:AV80"/>
+    <mergeCell ref="X66:AK66"/>
+    <mergeCell ref="L38:W38"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="L40:W40"/>
+    <mergeCell ref="AE32:AK32"/>
+    <mergeCell ref="B71:K71"/>
+    <mergeCell ref="AE47:AK47"/>
+    <mergeCell ref="B52:K52"/>
+    <mergeCell ref="AL71:AV71"/>
+    <mergeCell ref="AL33:AV33"/>
+    <mergeCell ref="B60:K60"/>
+    <mergeCell ref="AL8:AV8"/>
+    <mergeCell ref="AL73:AV73"/>
+    <mergeCell ref="B53:K53"/>
+    <mergeCell ref="AL10:AV10"/>
+    <mergeCell ref="L93:W93"/>
     <mergeCell ref="AL74:AV74"/>
-    <mergeCell ref="AE34:AK34"/>
-    <mergeCell ref="B9:W9"/>
-    <mergeCell ref="B74:W74"/>
-    <mergeCell ref="AE83:AK83"/>
-    <mergeCell ref="X54:AD54"/>
-    <mergeCell ref="B68:W68"/>
-    <mergeCell ref="B83:W83"/>
-    <mergeCell ref="AL11:AV11"/>
+    <mergeCell ref="L35:W35"/>
+    <mergeCell ref="B80:K80"/>
     <mergeCell ref="X8:AK8"/>
     <mergeCell ref="AE45:AK45"/>
-    <mergeCell ref="B45:W45"/>
-    <mergeCell ref="X56:AD56"/>
-    <mergeCell ref="AE51:AK51"/>
     <mergeCell ref="AL86:AV86"/>
     <mergeCell ref="AE20:AK20"/>
-    <mergeCell ref="X43:AD43"/>
-    <mergeCell ref="X40:AD40"/>
-    <mergeCell ref="B75:W75"/>
     <mergeCell ref="AL28:AV28"/>
-    <mergeCell ref="B47:W47"/>
     <mergeCell ref="AE59:AK59"/>
     <mergeCell ref="AE22:AK22"/>
-    <mergeCell ref="B59:W59"/>
-    <mergeCell ref="AE31:AK31"/>
+    <mergeCell ref="L59:W59"/>
     <mergeCell ref="X74:AK74"/>
+    <mergeCell ref="L46:W46"/>
+    <mergeCell ref="X17:AD17"/>
     <mergeCell ref="X68:AK68"/>
-    <mergeCell ref="X17:AD17"/>
-    <mergeCell ref="B31:W31"/>
-    <mergeCell ref="B46:W46"/>
     <mergeCell ref="AL21:AV21"/>
-    <mergeCell ref="AL72:AV72"/>
     <mergeCell ref="X82:AD82"/>
-    <mergeCell ref="AE21:AK21"/>
-    <mergeCell ref="AE92:AK92"/>
-    <mergeCell ref="B21:W21"/>
-    <mergeCell ref="B86:W86"/>
-    <mergeCell ref="B39:W39"/>
-    <mergeCell ref="AL14:AV14"/>
-    <mergeCell ref="B48:W48"/>
+    <mergeCell ref="L61:W61"/>
+    <mergeCell ref="L48:W48"/>
     <mergeCell ref="AL23:AV23"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="X83:AD83"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="AL54:AV54"/>
+    <mergeCell ref="AE48:AK48"/>
+    <mergeCell ref="L43:W43"/>
+    <mergeCell ref="B74:K74"/>
+    <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="B68:K68"/>
+    <mergeCell ref="AL89:AV89"/>
+    <mergeCell ref="L34:W34"/>
+    <mergeCell ref="L9:W9"/>
+    <mergeCell ref="B21:K21"/>
+    <mergeCell ref="L11:W11"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="L67:W67"/>
+    <mergeCell ref="AE61:AK61"/>
+    <mergeCell ref="B87:K87"/>
+    <mergeCell ref="AL94:AV94"/>
+    <mergeCell ref="AL44:AV44"/>
+    <mergeCell ref="AL31:AV31"/>
+    <mergeCell ref="B51:K51"/>
+    <mergeCell ref="L64:W64"/>
+    <mergeCell ref="L51:W51"/>
+    <mergeCell ref="X22:AD22"/>
+    <mergeCell ref="AL26:AV26"/>
+    <mergeCell ref="X86:AD86"/>
+    <mergeCell ref="AE16:AK16"/>
+    <mergeCell ref="AE43:AK43"/>
+    <mergeCell ref="L17:W17"/>
+    <mergeCell ref="L82:W82"/>
+    <mergeCell ref="X15:AD15"/>
+    <mergeCell ref="L75:W75"/>
+    <mergeCell ref="X33:AD33"/>
+    <mergeCell ref="X79:AD79"/>
+    <mergeCell ref="X35:AD35"/>
+    <mergeCell ref="B24:K24"/>
+    <mergeCell ref="L39:W39"/>
+    <mergeCell ref="X81:AD81"/>
+    <mergeCell ref="B89:K89"/>
+    <mergeCell ref="B32:K32"/>
+    <mergeCell ref="B26:K26"/>
+    <mergeCell ref="AL45:AV45"/>
+    <mergeCell ref="AL32:AV32"/>
+    <mergeCell ref="L72:W72"/>
+    <mergeCell ref="AL47:AV47"/>
+    <mergeCell ref="B27:K27"/>
+    <mergeCell ref="L65:W65"/>
+    <mergeCell ref="X34:AD34"/>
+    <mergeCell ref="X28:AD28"/>
+    <mergeCell ref="L7:W7"/>
+    <mergeCell ref="X92:AD92"/>
+    <mergeCell ref="AE17:AK17"/>
+    <mergeCell ref="B44:K44"/>
+    <mergeCell ref="AE88:AK88"/>
+    <mergeCell ref="AE82:AK82"/>
+    <mergeCell ref="X94:AD94"/>
+    <mergeCell ref="AE83:AK83"/>
+    <mergeCell ref="L83:W83"/>
+    <mergeCell ref="B20:K20"/>
+    <mergeCell ref="X54:AD54"/>
+    <mergeCell ref="L20:W20"/>
+    <mergeCell ref="L25:W25"/>
+    <mergeCell ref="X56:AD56"/>
+    <mergeCell ref="X43:AD43"/>
+    <mergeCell ref="L60:W60"/>
+    <mergeCell ref="L22:W22"/>
+    <mergeCell ref="L80:W80"/>
     <mergeCell ref="AE14:AK14"/>
-    <mergeCell ref="B14:W14"/>
-    <mergeCell ref="AE23:AK23"/>
     <mergeCell ref="AL55:AV55"/>
-    <mergeCell ref="B23:W23"/>
-    <mergeCell ref="AL64:AV64"/>
-    <mergeCell ref="X75:AK75"/>
-    <mergeCell ref="X83:AD83"/>
-    <mergeCell ref="AL51:AV51"/>
     <mergeCell ref="AE78:AK78"/>
     <mergeCell ref="AL48:AV48"/>
-    <mergeCell ref="AL54:AV54"/>
-    <mergeCell ref="AE87:AK87"/>
-    <mergeCell ref="B78:W78"/>
-    <mergeCell ref="AL10:AV10"/>
-    <mergeCell ref="B87:W87"/>
-    <mergeCell ref="AE48:AK48"/>
-    <mergeCell ref="X45:AD45"/>
-    <mergeCell ref="X60:AD60"/>
-    <mergeCell ref="B65:W65"/>
-    <mergeCell ref="B33:W33"/>
+    <mergeCell ref="L15:W15"/>
+    <mergeCell ref="L71:W71"/>
+    <mergeCell ref="L33:W33"/>
+    <mergeCell ref="L8:W8"/>
+    <mergeCell ref="L73:W73"/>
     <mergeCell ref="X44:AD44"/>
-    <mergeCell ref="X59:AD59"/>
-    <mergeCell ref="AL27:AV27"/>
-    <mergeCell ref="B51:W51"/>
+    <mergeCell ref="B45:K45"/>
     <mergeCell ref="X31:AD31"/>
-    <mergeCell ref="X46:AD46"/>
     <mergeCell ref="AE27:AK27"/>
-    <mergeCell ref="X7:AK7"/>
-    <mergeCell ref="AL89:AV89"/>
-    <mergeCell ref="X21:AD21"/>
-    <mergeCell ref="B35:W35"/>
-    <mergeCell ref="AL25:AV25"/>
+    <mergeCell ref="L10:W10"/>
     <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="B47:K47"/>
     <mergeCell ref="AE25:AK25"/>
-    <mergeCell ref="B25:W25"/>
+    <mergeCell ref="B59:K59"/>
     <mergeCell ref="AL66:AV66"/>
-    <mergeCell ref="AL75:AV75"/>
-    <mergeCell ref="X23:AD23"/>
+    <mergeCell ref="B46:K46"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="AE35:AK35"/>
     <mergeCell ref="AL53:AV53"/>
-    <mergeCell ref="B66:W66"/>
-    <mergeCell ref="X65:AK65"/>
     <mergeCell ref="AE93:AK93"/>
-    <mergeCell ref="B27:W27"/>
-    <mergeCell ref="B22:W22"/>
-    <mergeCell ref="X73:AK73"/>
-    <mergeCell ref="B93:W93"/>
     <mergeCell ref="AL68:AV68"/>
-    <mergeCell ref="X16:AD16"/>
-    <mergeCell ref="X87:AD87"/>
-    <mergeCell ref="AL52:AV52"/>
+    <mergeCell ref="B48:K48"/>
+    <mergeCell ref="L86:W86"/>
     <mergeCell ref="AL67:AV67"/>
-    <mergeCell ref="AL39:AV39"/>
-    <mergeCell ref="AE52:AK52"/>
-    <mergeCell ref="AE61:AK61"/>
-    <mergeCell ref="B67:W67"/>
-    <mergeCell ref="AE39:AK39"/>
-    <mergeCell ref="B61:W61"/>
-    <mergeCell ref="AL38:AV38"/>
-    <mergeCell ref="AL94:AV94"/>
+    <mergeCell ref="L28:W28"/>
+    <mergeCell ref="B73:K73"/>
     <mergeCell ref="AE38:AK38"/>
-    <mergeCell ref="B38:W38"/>
-    <mergeCell ref="AL44:AV44"/>
     <mergeCell ref="AL79:AV79"/>
-    <mergeCell ref="AL31:AV31"/>
-    <mergeCell ref="AE53:AK53"/>
-    <mergeCell ref="X93:AD93"/>
-    <mergeCell ref="AL40:AV40"/>
     <mergeCell ref="AE40:AK40"/>
-    <mergeCell ref="X51:AD51"/>
-    <mergeCell ref="AL15:AV15"/>
-    <mergeCell ref="B40:W40"/>
+    <mergeCell ref="L23:W23"/>
     <mergeCell ref="AL81:AV81"/>
     <mergeCell ref="AE15:AK15"/>
     <mergeCell ref="AE86:AK86"/>
-    <mergeCell ref="B15:W15"/>
-    <mergeCell ref="AE24:AK24"/>
-    <mergeCell ref="B55:W55"/>
     <mergeCell ref="X67:AK67"/>
-    <mergeCell ref="B24:W24"/>
-    <mergeCell ref="AL65:AV65"/>
-    <mergeCell ref="B64:W64"/>
-    <mergeCell ref="AE89:AK89"/>
-    <mergeCell ref="B89:W89"/>
-    <mergeCell ref="X22:AD22"/>
-    <mergeCell ref="AL26:AV26"/>
     <mergeCell ref="AE79:AK79"/>
-    <mergeCell ref="B79:W79"/>
-    <mergeCell ref="AE26:AK26"/>
-    <mergeCell ref="B32:W32"/>
-    <mergeCell ref="AL7:AV7"/>
-    <mergeCell ref="B26:W26"/>
+    <mergeCell ref="L54:W54"/>
     <mergeCell ref="AL16:AV16"/>
     <mergeCell ref="AE94:AK94"/>
-    <mergeCell ref="X86:AD86"/>
-    <mergeCell ref="B7:W7"/>
-    <mergeCell ref="AE16:AK16"/>
     <mergeCell ref="AE81:AK81"/>
-    <mergeCell ref="B16:W16"/>
+    <mergeCell ref="B66:K66"/>
     <mergeCell ref="X52:AD52"/>
-    <mergeCell ref="B81:W81"/>
-    <mergeCell ref="B2:AV2"/>
-    <mergeCell ref="X61:AD61"/>
-    <mergeCell ref="B71:W71"/>
-    <mergeCell ref="AE43:AK43"/>
+    <mergeCell ref="L56:W56"/>
     <mergeCell ref="X64:AK64"/>
-    <mergeCell ref="B52:W52"/>
-    <mergeCell ref="AL93:AV93"/>
     <mergeCell ref="X78:AD78"/>
     <mergeCell ref="AE33:AK33"/>
-    <mergeCell ref="AL43:AV43"/>
+    <mergeCell ref="B67:K67"/>
     <mergeCell ref="X53:AD53"/>
-    <mergeCell ref="B11:W11"/>
+    <mergeCell ref="B61:K61"/>
     <mergeCell ref="X47:AD47"/>
-    <mergeCell ref="AL83:AV83"/>
-    <mergeCell ref="B60:W60"/>
     <mergeCell ref="AL92:AV92"/>
-    <mergeCell ref="AL35:AV35"/>
-    <mergeCell ref="X10:AK10"/>
-    <mergeCell ref="X15:AD15"/>
-    <mergeCell ref="AL20:AV20"/>
-    <mergeCell ref="AE44:AK44"/>
     <mergeCell ref="X55:AD55"/>
-    <mergeCell ref="X24:AD24"/>
-    <mergeCell ref="B44:W44"/>
-    <mergeCell ref="B53:W53"/>
-    <mergeCell ref="X33:AD33"/>
-    <mergeCell ref="X89:AD89"/>
     <mergeCell ref="AE28:AK28"/>
-    <mergeCell ref="B34:W34"/>
     <mergeCell ref="X9:AK9"/>
-    <mergeCell ref="AL60:AV60"/>
-    <mergeCell ref="B28:W28"/>
-    <mergeCell ref="X71:AK71"/>
-    <mergeCell ref="X79:AD79"/>
-    <mergeCell ref="AE60:AK60"/>
-    <mergeCell ref="AL22:AV22"/>
-    <mergeCell ref="AL78:AV78"/>
-    <mergeCell ref="X88:AD88"/>
-    <mergeCell ref="X26:AD26"/>
-    <mergeCell ref="X35:AD35"/>
-    <mergeCell ref="AL59:AV59"/>
     <mergeCell ref="AL6:AV6"/>
     <mergeCell ref="X11:AK11"/>
-    <mergeCell ref="B92:W92"/>
-    <mergeCell ref="AL46:AV46"/>
-    <mergeCell ref="X81:AD81"/>
+    <mergeCell ref="B64:K64"/>
     <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="AL80:AV80"/>
-    <mergeCell ref="B6:W6"/>
-    <mergeCell ref="B20:W20"/>
-    <mergeCell ref="AE80:AK80"/>
-    <mergeCell ref="X66:AK66"/>
-    <mergeCell ref="AL61:AV61"/>
-    <mergeCell ref="B80:W80"/>
-    <mergeCell ref="B94:W94"/>
-    <mergeCell ref="AE55:AK55"/>
-    <mergeCell ref="X27:AD27"/>
-    <mergeCell ref="AL45:AV45"/>
-    <mergeCell ref="AL32:AV32"/>
+    <mergeCell ref="L94:W94"/>
+    <mergeCell ref="L44:W44"/>
+    <mergeCell ref="B16:K16"/>
+    <mergeCell ref="L31:W31"/>
     <mergeCell ref="AE54:AK54"/>
-    <mergeCell ref="AE32:AK32"/>
-    <mergeCell ref="B54:W54"/>
-    <mergeCell ref="AE46:AK46"/>
-    <mergeCell ref="B72:W72"/>
-    <mergeCell ref="AL47:AV47"/>
-    <mergeCell ref="AL56:AV56"/>
     <mergeCell ref="AL87:AV87"/>
-    <mergeCell ref="AE47:AK47"/>
     <mergeCell ref="X6:AK6"/>
     <mergeCell ref="AE56:AK56"/>
-    <mergeCell ref="B56:W56"/>
-    <mergeCell ref="AL71:AV71"/>
     <mergeCell ref="AL24:AV24"/>
-    <mergeCell ref="X34:AD34"/>
-    <mergeCell ref="B43:W43"/>
-    <mergeCell ref="X28:AD28"/>
-    <mergeCell ref="AL33:AV33"/>
-    <mergeCell ref="AL8:AV8"/>
+    <mergeCell ref="B11:K11"/>
     <mergeCell ref="AL17:AV17"/>
-    <mergeCell ref="AL73:AV73"/>
     <mergeCell ref="AL88:AV88"/>
     <mergeCell ref="AL82:AV82"/>
-    <mergeCell ref="B8:W8"/>
-    <mergeCell ref="AE17:AK17"/>
-    <mergeCell ref="AE88:AK88"/>
-    <mergeCell ref="X92:AD92"/>
-    <mergeCell ref="B17:W17"/>
-    <mergeCell ref="B73:W73"/>
-    <mergeCell ref="AE82:AK82"/>
     <mergeCell ref="X72:AK72"/>
-    <mergeCell ref="B88:W88"/>
-    <mergeCell ref="B82:W82"/>
-    <mergeCell ref="X20:AD20"/>
-    <mergeCell ref="X14:AD14"/>
     <mergeCell ref="X80:AD80"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16457,8 +17103,12 @@
       <c r="H5" s="463" t="n"/>
       <c r="I5" s="463" t="n"/>
       <c r="J5" s="463" t="n"/>
-      <c r="K5" s="463" t="n"/>
-      <c r="L5" s="463" t="n"/>
+      <c r="K5" s="464" t="n"/>
+      <c r="L5" s="462" t="inlineStr">
+        <is>
+          <t>目的・解説（なぜこの設定が必要か）</t>
+        </is>
+      </c>
       <c r="M5" s="463" t="n"/>
       <c r="N5" s="463" t="n"/>
       <c r="O5" s="463" t="n"/>
@@ -16504,7 +17154,7 @@
       <c r="AU5" s="463" t="n"/>
       <c r="AV5" s="464" t="n"/>
     </row>
-    <row r="6" ht="29" customHeight="1" s="412">
+    <row r="6" ht="43.5" customHeight="1" s="412">
       <c r="B6" s="465" t="inlineStr">
         <is>
           <t>サービス一覧（全ノード）</t>
@@ -16518,19 +17168,23 @@
       <c r="H6" s="463" t="n"/>
       <c r="I6" s="463" t="n"/>
       <c r="J6" s="463" t="n"/>
-      <c r="K6" s="463" t="n"/>
-      <c r="L6" s="463" t="n"/>
-      <c r="M6" s="463" t="n"/>
-      <c r="N6" s="463" t="n"/>
-      <c r="O6" s="463" t="n"/>
-      <c r="P6" s="463" t="n"/>
-      <c r="Q6" s="463" t="n"/>
-      <c r="R6" s="463" t="n"/>
-      <c r="S6" s="463" t="n"/>
-      <c r="T6" s="463" t="n"/>
-      <c r="U6" s="463" t="n"/>
-      <c r="V6" s="463" t="n"/>
-      <c r="W6" s="464" t="n"/>
+      <c r="K6" s="464" t="n"/>
+      <c r="L6" s="466" t="inlineStr">
+        <is>
+          <t>構築完了時点の状態を記録することで、以後の変更管理・障害発生時の切り分け（何が変わったか）の基準とするため。</t>
+        </is>
+      </c>
+      <c r="M6" s="467" t="n"/>
+      <c r="N6" s="467" t="n"/>
+      <c r="O6" s="467" t="n"/>
+      <c r="P6" s="467" t="n"/>
+      <c r="Q6" s="467" t="n"/>
+      <c r="R6" s="467" t="n"/>
+      <c r="S6" s="467" t="n"/>
+      <c r="T6" s="467" t="n"/>
+      <c r="U6" s="467" t="n"/>
+      <c r="V6" s="467" t="n"/>
+      <c r="W6" s="468" t="n"/>
       <c r="X6" s="465" t="inlineStr">
         <is>
           <t>systemctl list-unit-files の採取結果を転記</t>
@@ -16565,7 +17219,7 @@
       <c r="AU6" s="463" t="n"/>
       <c r="AV6" s="464" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="29" customHeight="1" s="412">
       <c r="B7" s="465" t="inlineStr">
         <is>
           <t>インストール済みパッケージ一覧（全ノード）</t>
@@ -16579,19 +17233,23 @@
       <c r="H7" s="463" t="n"/>
       <c r="I7" s="463" t="n"/>
       <c r="J7" s="463" t="n"/>
-      <c r="K7" s="463" t="n"/>
-      <c r="L7" s="463" t="n"/>
-      <c r="M7" s="463" t="n"/>
-      <c r="N7" s="463" t="n"/>
-      <c r="O7" s="463" t="n"/>
-      <c r="P7" s="463" t="n"/>
-      <c r="Q7" s="463" t="n"/>
-      <c r="R7" s="463" t="n"/>
-      <c r="S7" s="463" t="n"/>
-      <c r="T7" s="463" t="n"/>
-      <c r="U7" s="463" t="n"/>
-      <c r="V7" s="463" t="n"/>
-      <c r="W7" s="464" t="n"/>
+      <c r="K7" s="464" t="n"/>
+      <c r="L7" s="466" t="inlineStr">
+        <is>
+          <t>同上。導入済みパッケージ・バージョンの記録。</t>
+        </is>
+      </c>
+      <c r="M7" s="467" t="n"/>
+      <c r="N7" s="467" t="n"/>
+      <c r="O7" s="467" t="n"/>
+      <c r="P7" s="467" t="n"/>
+      <c r="Q7" s="467" t="n"/>
+      <c r="R7" s="467" t="n"/>
+      <c r="S7" s="467" t="n"/>
+      <c r="T7" s="467" t="n"/>
+      <c r="U7" s="467" t="n"/>
+      <c r="V7" s="467" t="n"/>
+      <c r="W7" s="468" t="n"/>
       <c r="X7" s="465" t="inlineStr">
         <is>
           <t>dpkg -l の採取結果を転記</t>
@@ -16640,19 +17298,23 @@
       <c r="H8" s="463" t="n"/>
       <c r="I8" s="463" t="n"/>
       <c r="J8" s="463" t="n"/>
-      <c r="K8" s="463" t="n"/>
-      <c r="L8" s="463" t="n"/>
-      <c r="M8" s="463" t="n"/>
-      <c r="N8" s="463" t="n"/>
-      <c r="O8" s="463" t="n"/>
-      <c r="P8" s="463" t="n"/>
-      <c r="Q8" s="463" t="n"/>
-      <c r="R8" s="463" t="n"/>
-      <c r="S8" s="463" t="n"/>
-      <c r="T8" s="463" t="n"/>
-      <c r="U8" s="463" t="n"/>
-      <c r="V8" s="463" t="n"/>
-      <c r="W8" s="464" t="n"/>
+      <c r="K8" s="464" t="n"/>
+      <c r="L8" s="466" t="inlineStr">
+        <is>
+          <t>同上。クラスタバージョン・ノード状態の記録。</t>
+        </is>
+      </c>
+      <c r="M8" s="467" t="n"/>
+      <c r="N8" s="467" t="n"/>
+      <c r="O8" s="467" t="n"/>
+      <c r="P8" s="467" t="n"/>
+      <c r="Q8" s="467" t="n"/>
+      <c r="R8" s="467" t="n"/>
+      <c r="S8" s="467" t="n"/>
+      <c r="T8" s="467" t="n"/>
+      <c r="U8" s="467" t="n"/>
+      <c r="V8" s="467" t="n"/>
+      <c r="W8" s="468" t="n"/>
       <c r="X8" s="465" t="inlineStr">
         <is>
           <t>kubectl get nodes -o wide / kubectl version の採取結果を転記</t>
@@ -16701,19 +17363,23 @@
       <c r="H9" s="463" t="n"/>
       <c r="I9" s="463" t="n"/>
       <c r="J9" s="463" t="n"/>
-      <c r="K9" s="463" t="n"/>
-      <c r="L9" s="463" t="n"/>
-      <c r="M9" s="463" t="n"/>
-      <c r="N9" s="463" t="n"/>
-      <c r="O9" s="463" t="n"/>
-      <c r="P9" s="463" t="n"/>
-      <c r="Q9" s="463" t="n"/>
-      <c r="R9" s="463" t="n"/>
-      <c r="S9" s="463" t="n"/>
-      <c r="T9" s="463" t="n"/>
-      <c r="U9" s="463" t="n"/>
-      <c r="V9" s="463" t="n"/>
-      <c r="W9" s="464" t="n"/>
+      <c r="K9" s="464" t="n"/>
+      <c r="L9" s="466" t="inlineStr">
+        <is>
+          <t>同上。導入済みソフトウェアの版数記録。</t>
+        </is>
+      </c>
+      <c r="M9" s="467" t="n"/>
+      <c r="N9" s="467" t="n"/>
+      <c r="O9" s="467" t="n"/>
+      <c r="P9" s="467" t="n"/>
+      <c r="Q9" s="467" t="n"/>
+      <c r="R9" s="467" t="n"/>
+      <c r="S9" s="467" t="n"/>
+      <c r="T9" s="467" t="n"/>
+      <c r="U9" s="467" t="n"/>
+      <c r="V9" s="467" t="n"/>
+      <c r="W9" s="468" t="n"/>
       <c r="X9" s="465" t="inlineStr">
         <is>
           <t>helm list -A の採取結果を転記</t>
@@ -16749,23 +17415,28 @@
       <c r="AV9" s="464" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="21">
+    <mergeCell ref="X9:AK9"/>
+    <mergeCell ref="AL9:AV9"/>
+    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="L5:W5"/>
+    <mergeCell ref="AL6:AV6"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="L8:W8"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="X8:AK8"/>
+    <mergeCell ref="X7:AK7"/>
+    <mergeCell ref="AL7:AV7"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="L9:W9"/>
+    <mergeCell ref="B2:AV2"/>
+    <mergeCell ref="L6:W6"/>
+    <mergeCell ref="X6:AK6"/>
+    <mergeCell ref="X5:AK5"/>
     <mergeCell ref="AL5:AV5"/>
-    <mergeCell ref="X9:AK9"/>
-    <mergeCell ref="X8:AK8"/>
-    <mergeCell ref="B2:AV2"/>
+    <mergeCell ref="L7:W7"/>
     <mergeCell ref="AL8:AV8"/>
-    <mergeCell ref="B5:W5"/>
-    <mergeCell ref="X7:AK7"/>
-    <mergeCell ref="AL9:AV9"/>
-    <mergeCell ref="B8:W8"/>
-    <mergeCell ref="X6:AK6"/>
-    <mergeCell ref="AL7:AV7"/>
-    <mergeCell ref="AL6:AV6"/>
-    <mergeCell ref="B9:W9"/>
-    <mergeCell ref="X5:AK5"/>
-    <mergeCell ref="B7:W7"/>
-    <mergeCell ref="B6:W6"/>
+    <mergeCell ref="B8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
